--- a/indicadores/ARG-ESS_out.xlsx
+++ b/indicadores/ARG-ESS_out.xlsx
@@ -110,7 +110,7 @@
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">arodriguez</t>
+    <t xml:space="preserve">pcohan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>

--- a/indicadores/ARG-ESS_out.xlsx
+++ b/indicadores/ARG-ESS_out.xlsx
@@ -110,7 +110,7 @@
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">arodriguez</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>

--- a/indicadores/ARG-ESS_out.xlsx
+++ b/indicadores/ARG-ESS_out.xlsx
@@ -104,13 +104,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">25/03/2026</t>
+    <t xml:space="preserve">26/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">arodriguez</t>
+    <t xml:space="preserve">pcohan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1235,7 +1235,7 @@
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.602000954237363</v>
+        <v>0.601501539331679</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1293,7 +1293,7 @@
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.362405148902696</v>
+        <v>0.361804101818379</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1363,7 +1363,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.00443934477492296</v>
+        <v>0.00398766920287295</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1393,7 +1393,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.872886719811067</v>
+        <v>0.867273272632357</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -9786,7 +9786,7 @@
         <v>220</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.0815979852971059</v>
+        <v>-0.0812621140331287</v>
       </c>
     </row>
     <row r="6">
@@ -9794,7 +9794,7 @@
         <v>221</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0407428209864884</v>
+        <v>0.0399445287858748</v>
       </c>
     </row>
     <row r="7">
@@ -9802,7 +9802,7 @@
         <v>222</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.237940744114264</v>
+        <v>0.236943660235123</v>
       </c>
     </row>
     <row r="8">
@@ -9810,7 +9810,7 @@
         <v>223</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.459336174439361</v>
+        <v>0.458798346550569</v>
       </c>
     </row>
     <row r="9">
@@ -9818,7 +9818,7 @@
         <v>224</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.602000954237363</v>
+        <v>0.601501539331679</v>
       </c>
     </row>
     <row r="10">
@@ -9826,7 +9826,7 @@
         <v>225</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.569511480077779</v>
+        <v>0.569256970325015</v>
       </c>
     </row>
     <row r="11">
@@ -9834,7 +9834,7 @@
         <v>226</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.402312998981605</v>
+        <v>0.402295996359951</v>
       </c>
     </row>
     <row r="12">
@@ -9842,7 +9842,7 @@
         <v>227</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.224930587462334</v>
+        <v>0.225080821265488</v>
       </c>
     </row>
     <row r="13">
@@ -9850,7 +9850,7 @@
         <v>228</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.104548935264558</v>
+        <v>0.105141084266131</v>
       </c>
     </row>
     <row r="14">

--- a/indicadores/ARG-ESS_out.xlsx
+++ b/indicadores/ARG-ESS_out.xlsx
@@ -1235,7 +1235,7 @@
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.601501539331679</v>
+        <v>0.601910742305836</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1293,7 +1293,7 @@
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.361804101818379</v>
+        <v>0.362296541703163</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1363,7 +1363,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.00398766920287295</v>
+        <v>0.00395619748110876</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1393,7 +1393,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.867273272632357</v>
+        <v>0.866596808626046</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -9786,7 +9786,7 @@
         <v>220</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.0812621140331287</v>
+        <v>-0.0810352050436087</v>
       </c>
     </row>
     <row r="6">
@@ -9794,7 +9794,7 @@
         <v>221</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0399445287858748</v>
+        <v>0.0402500140844762</v>
       </c>
     </row>
     <row r="7">
@@ -9802,7 +9802,7 @@
         <v>222</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.236943660235123</v>
+        <v>0.236767051253355</v>
       </c>
     </row>
     <row r="8">
@@ -9810,7 +9810,7 @@
         <v>223</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.458798346550569</v>
+        <v>0.458724293738252</v>
       </c>
     </row>
     <row r="9">
@@ -9818,7 +9818,7 @@
         <v>224</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.601501539331679</v>
+        <v>0.601910742305836</v>
       </c>
     </row>
     <row r="10">
@@ -9826,7 +9826,7 @@
         <v>225</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.569256970325015</v>
+        <v>0.569788141883</v>
       </c>
     </row>
     <row r="11">
@@ -9834,7 +9834,7 @@
         <v>226</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.402295996359951</v>
+        <v>0.402808807113062</v>
       </c>
     </row>
     <row r="12">
@@ -9842,7 +9842,7 @@
         <v>227</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.225080821265488</v>
+        <v>0.22543289538925</v>
       </c>
     </row>
     <row r="13">
@@ -9850,7 +9850,7 @@
         <v>228</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.105141084266131</v>
+        <v>0.10540561531832</v>
       </c>
     </row>
     <row r="14">

--- a/indicadores/ARG-ESS_out.xlsx
+++ b/indicadores/ARG-ESS_out.xlsx
@@ -9908,4 +9908,237 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
+    <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
+    <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5dd4176-d247-4204-85b8-921214f3ccea" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="01529062-7a8b-4d76-943d-e0db5644ee6d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="359b39ce-e1f9-4933-8424-33b611e6fdcd" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c9b73259-0823-4f05-8927-4a40ee49fbe1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="359b39ce-e1f9-4933-8424-33b611e6fdcd">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64EE0691-6624-4D5D-990D-043CFB93874C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{319E09E3-5999-4BA9-AE4E-1088A538FE25}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A42C381E-09B7-4873-8485-7490A963766E}"/>
 </file>
--- a/indicadores/ARG-ESS_out.xlsx
+++ b/indicadores/ARG-ESS_out.xlsx
@@ -104,13 +104,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">26/03/2026</t>
+    <t xml:space="preserve">30/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">arodriguez</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1235,7 +1235,7 @@
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.601910742305836</v>
+        <v>0.579327025860819</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1293,7 +1293,7 @@
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.362296541703163</v>
+        <v>0.335619802892742</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1363,7 +1363,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.00395619748110876</v>
+        <v>0.0050691223722586</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1393,7 +1393,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.866596808626046</v>
+        <v>0.821075588484585</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1662,10 +1662,10 @@
         <v>1760.64557739452</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>1781.56169523646</v>
+        <v>1781.56185434975</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>1729.66080475502</v>
+        <v>1729.66080478652</v>
       </c>
       <c r="K2" s="11" t="n">
         <v>1775.24874755028</v>
@@ -1686,7 +1686,7 @@
         <v>1.00439540324969</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>0.992603472231845</v>
+        <v>0.992603383581314</v>
       </c>
     </row>
     <row r="3">
@@ -1715,10 +1715,10 @@
         <v>1771.99220927855</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>1812.37040519022</v>
+        <v>1812.37053493999</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>1757.34941922595</v>
+        <v>1757.34941929469</v>
       </c>
       <c r="K3" s="11" t="n">
         <v>1754.65547896032</v>
@@ -1743,7 +1743,7 @@
         <v>1.00173783722545</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>0.979419901262802</v>
+        <v>0.979419831144964</v>
       </c>
     </row>
     <row r="4">
@@ -1772,10 +1772,10 @@
         <v>1815.72686774121</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>1843.17516955168</v>
+        <v>1843.17526983848</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>1785.26597341086</v>
+        <v>1785.26597351667</v>
       </c>
       <c r="K4" s="11" t="n">
         <v>1732.50233872429</v>
@@ -1800,7 +1800,7 @@
         <v>1.00011996967783</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.9852263256944</v>
+        <v>0.985226272088432</v>
       </c>
     </row>
     <row r="5">
@@ -1829,10 +1829,10 @@
         <v>1860.95703972976</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>1873.93597089964</v>
+        <v>1873.93604144349</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>1813.62493732239</v>
+        <v>1813.62493746461</v>
       </c>
       <c r="K5" s="11" t="n">
         <v>1877.66958519149</v>
@@ -1857,7 +1857,7 @@
         <v>0.996082087039312</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>0.989183195589445</v>
+        <v>0.989183158351896</v>
       </c>
     </row>
     <row r="6">
@@ -1886,10 +1886,10 @@
         <v>1856.60744927745</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>1904.59563662427</v>
+        <v>1904.59567690196</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>1842.79308544485</v>
+        <v>1842.79308562179</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>1843.59784997389</v>
@@ -1916,7 +1916,7 @@
         <v>0.996528854768895</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.971420316001094</v>
+        <v>0.971420295457856</v>
       </c>
     </row>
     <row r="7">
@@ -1945,10 +1945,10 @@
         <v>1824.37010523696</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1935.09932762468</v>
+        <v>1935.09933682569</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>1873.45741550187</v>
+        <v>1873.45741571011</v>
       </c>
       <c r="K7" s="11" t="n">
         <v>1835.78629559616</v>
@@ -1975,7 +1975,7 @@
         <v>1.00414065645182</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>0.946682254978813</v>
+        <v>0.946682250477526</v>
       </c>
     </row>
     <row r="8">
@@ -2004,10 +2004,10 @@
         <v>1812.52633916864</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>1965.3540811833</v>
+        <v>1965.35405818465</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>1906.30894903976</v>
+        <v>1906.30894927324</v>
       </c>
       <c r="K8" s="11" t="n">
         <v>1730.66717915826</v>
@@ -2034,7 +2034,7 @@
         <v>1.00744660195661</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>0.929106627062789</v>
+        <v>0.929106637935233</v>
       </c>
     </row>
     <row r="9">
@@ -2063,10 +2063,10 @@
         <v>1843.44643514561</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>1995.20486393757</v>
+        <v>1995.20480729802</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>1941.85035200527</v>
+        <v>1941.85035225426</v>
       </c>
       <c r="K9" s="11" t="n">
         <v>1843.25503147577</v>
@@ -2093,7 +2093,7 @@
         <v>1.005182977798</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>0.928727175130195</v>
+        <v>0.928727201494749</v>
       </c>
     </row>
     <row r="10">
@@ -2122,10 +2122,10 @@
         <v>1907.0072419922</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>2024.40112518616</v>
+        <v>2024.40103316064</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>1980.11537729581</v>
+        <v>1980.11537754576</v>
       </c>
       <c r="K10" s="11" t="n">
         <v>1912.96750624288</v>
@@ -2152,7 +2152,7 @@
         <v>1.00011552539216</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>0.942119388308625</v>
+        <v>0.942119431135629</v>
       </c>
     </row>
     <row r="11">
@@ -2181,10 +2181,10 @@
         <v>1961.23239831564</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>2052.59734558245</v>
+        <v>2052.5972161574</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>2020.64480120613</v>
+        <v>2020.6448014364</v>
       </c>
       <c r="K11" s="11" t="n">
         <v>1959.72015504519</v>
@@ -2211,7 +2211,7 @@
         <v>1.000166185914</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>0.955646918152716</v>
+        <v>0.955646978410348</v>
       </c>
     </row>
     <row r="12">
@@ -2240,10 +2240,10 @@
         <v>2014.57756141362</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>2079.37835976798</v>
+        <v>2079.37819071892</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>2062.64366067573</v>
+        <v>2062.64366085836</v>
       </c>
       <c r="K12" s="11" t="n">
         <v>2013.82549372401</v>
@@ -2270,7 +2270,7 @@
         <v>1.00174498392577</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>0.970527060356961</v>
+        <v>0.970527139258765</v>
       </c>
     </row>
     <row r="13">
@@ -2299,10 +2299,10 @@
         <v>2090.01563239174</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>2104.27095414022</v>
+        <v>2104.2707431126</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>2105.01236941331</v>
+        <v>2105.01236951184</v>
       </c>
       <c r="K13" s="11" t="n">
         <v>2085.00072500881</v>
@@ -2329,7 +2329,7 @@
         <v>0.999579551006778</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>0.99280792870939</v>
+        <v>0.992808028273524</v>
       </c>
     </row>
     <row r="14">
@@ -2358,10 +2358,10 @@
         <v>2158.61881531001</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>2126.76094455533</v>
+        <v>2126.76068917022</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>2146.40725029279</v>
+        <v>2146.40725026138</v>
       </c>
       <c r="K14" s="11" t="n">
         <v>2172.72060595151</v>
@@ -2388,7 +2388,7 @@
         <v>1.0004781190168</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>1.01546480696127</v>
+        <v>1.01546492890004</v>
       </c>
     </row>
     <row r="15">
@@ -2417,10 +2417,10 @@
         <v>2231.26859147113</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>2146.32210297629</v>
+        <v>2146.32180096224</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>2185.38456796608</v>
+        <v>2185.38456774901</v>
       </c>
       <c r="K15" s="11" t="n">
         <v>2208.16163115073</v>
@@ -2435,19 +2435,19 @@
         <v>2226.22662290828</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>0.0303614703411082</v>
+        <v>0.0303614703411086</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>0.134927568393722</v>
+        <v>0.134927568393723</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>0.0308270800335244</v>
+        <v>0.0308270800335249</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>0.997740313029939</v>
+        <v>0.99774031302994</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>1.03722857805042</v>
+        <v>1.03722872400132</v>
       </c>
     </row>
     <row r="16">
@@ -2467,7 +2467,7 @@
         <v>2209.94973449106</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.952198672314391</v>
+        <v>0.952198672314389</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>0.831713051711106</v>
@@ -2476,10 +2476,10 @@
         <v>2291.00911646623</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>2162.45692615443</v>
+        <v>2162.45657550713</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>2220.63215386338</v>
+        <v>2220.63215339519</v>
       </c>
       <c r="K16" s="11" t="n">
         <v>2320.89142607142</v>
@@ -2494,19 +2494,19 @@
         <v>2285.07925268273</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.0260926527243342</v>
+        <v>0.0260926527243346</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>0.132296326378159</v>
+        <v>0.13229632637816</v>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>0.026436046163876</v>
+        <v>0.0264360461638764</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>0.997411680407171</v>
+        <v>0.997411680407172</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>1.05670509550743</v>
+        <v>1.05670526685459</v>
       </c>
     </row>
     <row r="17">
@@ -2535,10 +2535,10 @@
         <v>2303.53627422467</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>2174.70656054622</v>
+        <v>2174.7061597172</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>2250.95172473082</v>
+        <v>2250.95172393741</v>
       </c>
       <c r="K17" s="11" t="n">
         <v>2300.43013281991</v>
@@ -2553,19 +2553,19 @@
         <v>2302.9246352751</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.00777918808353193</v>
+        <v>0.00777918808353149</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>0.102333049183533</v>
+        <v>0.102333049183534</v>
       </c>
       <c r="Q17" s="17" t="n">
-        <v>0.00780952458056827</v>
+        <v>0.00780952458056783</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>0.999734478264392</v>
+        <v>0.999734478264393</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>1.05895879336322</v>
+        <v>1.05895898854426</v>
       </c>
     </row>
     <row r="18">
@@ -2591,13 +2591,13 @@
         <v>1</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>2319.03403184881</v>
+        <v>2319.0340318488</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>2182.70803116887</v>
+        <v>2182.70757928469</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>2275.6211496621</v>
+        <v>2275.62114846306</v>
       </c>
       <c r="K18" s="11" t="n">
         <v>2294.97565208045</v>
@@ -2612,19 +2612,19 @@
         <v>2318.86298584789</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.00689707752115064</v>
+        <v>0.00689707752114998</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>0.0737212178231539</v>
+        <v>0.0737212178231534</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>0.00692091713669352</v>
+        <v>0.00692091713669285</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>0.999926242565409</v>
+        <v>0.999926242565413</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>1.06237891313668</v>
+        <v>1.06237913308012</v>
       </c>
     </row>
     <row r="19">
@@ -2644,7 +2644,7 @@
         <v>2074.47075910088</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.869773347800401</v>
+        <v>0.869773347800402</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>1</v>
@@ -2653,16 +2653,16 @@
         <v>2354.81514801591</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>2186.17694027228</v>
+        <v>2186.17643738505</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>2294.16568979139</v>
+        <v>2294.16568810398</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>2385.07050641076</v>
+        <v>2385.07050641075</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>2385.07050641076</v>
+        <v>2385.07050641075</v>
       </c>
       <c r="M19" s="13" t="n">
         <v>2348.76495904353</v>
@@ -2671,19 +2671,19 @@
         <v>2348.76495904353</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.012812667426638</v>
+        <v>0.0128126674266387</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.0550430647420648</v>
+        <v>0.0550430647420646</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>0.012895101339806</v>
+        <v>0.0128951013398066</v>
       </c>
       <c r="R19" s="18" t="n">
         <v>0.997430715961938</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>1.0743709330092</v>
+        <v>1.07437118014727</v>
       </c>
     </row>
     <row r="20">
@@ -2703,46 +2703,46 @@
         <v>2220.49703180433</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.953026262263706</v>
+        <v>0.953026262263703</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>2346.92948857002</v>
+        <v>2346.92948857003</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>2184.89905736939</v>
+        <v>2184.8985047392</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>2306.20737876493</v>
+        <v>2306.20737651007</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>2329.94317127214</v>
+        <v>2329.94317127215</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>2329.94317127214</v>
+        <v>2329.94317127215</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>2336.45703444792</v>
+        <v>2336.45703444793</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>2336.45703444792</v>
+        <v>2336.45703444793</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>-0.00525394652589266</v>
+        <v>-0.00525394652589054</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>0.0224840261907222</v>
+        <v>0.0224840261907238</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>-0.00524016868874488</v>
+        <v>-0.00524016868874277</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>0.995537806238705</v>
+        <v>0.995537806238703</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>1.06936612314759</v>
+        <v>1.06936639362423</v>
       </c>
     </row>
     <row r="21">
@@ -2762,7 +2762,7 @@
         <v>2157.68471807993</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.937768543833182</v>
+        <v>0.937768543833178</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>1</v>
@@ -2771,16 +2771,16 @@
         <v>2294.61439283767</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>2178.78446045202</v>
+        <v>2178.78386086122</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>2311.82277431205</v>
+        <v>2311.82277142275</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>2300.87128883666</v>
+        <v>2300.87128883667</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>2300.87128883666</v>
+        <v>2300.87128883667</v>
       </c>
       <c r="M21" s="13" t="n">
         <v>2292.37019651742</v>
@@ -2789,19 +2789,19 @@
         <v>2292.37019651742</v>
       </c>
       <c r="O21" s="15" t="n">
-        <v>-0.0190493915223183</v>
+        <v>-0.0190493915223199</v>
       </c>
       <c r="P21" s="16" t="n">
-        <v>-0.00458305868807685</v>
+        <v>-0.00458305868807651</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>-0.0188690985027776</v>
+        <v>-0.0188690985027792</v>
       </c>
       <c r="R21" s="18" t="n">
         <v>0.999021972350886</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.05213261712076</v>
+        <v>1.05213290666257</v>
       </c>
     </row>
     <row r="22">
@@ -2821,46 +2821,46 @@
         <v>2761.19404120798</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1.23389050176659</v>
+        <v>1.2338905017666</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>2231.15104945891</v>
+        <v>2231.1510494589</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>2167.83388008314</v>
+        <v>2167.83323818175</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>2311.20711312465</v>
+        <v>2311.2071095573</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>2237.79503712421</v>
+        <v>2237.79503712419</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>2237.79503712421</v>
+        <v>2237.79503712419</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>2235.58223044938</v>
+        <v>2235.58223044937</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>2235.58223044938</v>
+        <v>2235.58223044937</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>-0.0250846026815211</v>
+        <v>-0.0250846026815238</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>-0.0359144787366832</v>
+        <v>-0.0359144787366847</v>
       </c>
       <c r="Q22" s="17" t="n">
-        <v>-0.0247725983151916</v>
+        <v>-0.0247725983151943</v>
       </c>
       <c r="R22" s="18" t="n">
         <v>1.0019860515457</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>1.03125163371081</v>
+        <v>1.03125193906725</v>
       </c>
     </row>
     <row r="23">
@@ -2880,25 +2880,25 @@
         <v>1899.39115314154</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.876965512272921</v>
+        <v>0.876965512272918</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>2182.97523299183</v>
+        <v>2182.97523299182</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>2152.12435109348</v>
+        <v>2152.12367377394</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>2304.50087446722</v>
+        <v>2304.50087021601</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>2165.86755871242</v>
+        <v>2165.86755871243</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>2165.86755871242</v>
+        <v>2165.86755871243</v>
       </c>
       <c r="M23" s="13" t="n">
         <v>2192.56423378053</v>
@@ -2907,19 +2907,19 @@
         <v>2192.56423378053</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>-0.0194299580493704</v>
+        <v>-0.0194299580493674</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>-0.066503344517965</v>
+        <v>-0.0665033445179642</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>-0.0192424130425294</v>
+        <v>-0.0192424130425264</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>1.00439262921712</v>
+        <v>1.00439262921713</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>1.01879068124781</v>
+        <v>1.01879100188312</v>
       </c>
     </row>
     <row r="24">
@@ -2939,46 +2939,46 @@
         <v>2098.32520367766</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.953469200357193</v>
+        <v>0.953469200357188</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>2183.98489379687</v>
+        <v>2183.98489379689</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>2131.77663403692</v>
+        <v>2131.77593083526</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>2291.47747722426</v>
+        <v>2291.47747233905</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>2200.72678057307</v>
+        <v>2200.72678057308</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>2200.72678057307</v>
+        <v>2200.72678057308</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>2197.21465100988</v>
+        <v>2197.21465100989</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>2197.21465100988</v>
+        <v>2197.21465100989</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>0.0021187486163123</v>
+        <v>0.00211874861631585</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>-0.0595955249273149</v>
+        <v>-0.0595955249273128</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>0.00212099475021277</v>
+        <v>0.00212099475021632</v>
       </c>
       <c r="R24" s="18" t="n">
         <v>1.00605762304061</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>1.03069646975586</v>
+        <v>1.0306968097482</v>
       </c>
     </row>
     <row r="25">
@@ -2998,7 +2998,7 @@
         <v>2070.99836436598</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.940611665725703</v>
+        <v>0.940611665725696</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0.612021987566334</v>
@@ -3007,16 +3007,16 @@
         <v>2252.74044292679</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>2106.9200789721</v>
+        <v>2106.91936249128</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>2271.2171737015</v>
+        <v>2271.21716830906</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>2201.75704791856</v>
+        <v>2201.75704791858</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>2221.53748418097</v>
+        <v>2221.53748418098</v>
       </c>
       <c r="M25" s="13" t="n">
         <v>2249.24029580153</v>
@@ -3025,19 +3025,19 @@
         <v>2249.24029580153</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>0.0234020223899132</v>
+        <v>0.0234020223899084</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>-0.0188145443442815</v>
+        <v>-0.0188145443442825</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>0.0236779983092401</v>
+        <v>0.0236779983092352</v>
       </c>
       <c r="R25" s="18" t="n">
         <v>0.998446271457394</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>1.06754893944476</v>
+        <v>1.06754930247637</v>
       </c>
     </row>
     <row r="26">
@@ -3057,46 +3057,46 @@
         <v>2878.0472386878</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1.21923217155114</v>
+        <v>1.21923217155116</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>0.834599830389808</v>
+        <v>0.834599830389825</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>2315.91367766713</v>
+        <v>2315.91367766712</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>2077.72712979923</v>
+        <v>2077.72641614864</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>2242.3464627214</v>
+        <v>2242.34645704983</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>2360.54076150752</v>
+        <v>2360.54076150748</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>2353.15943427111</v>
+        <v>2353.15943427108</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>2308.71789463234</v>
+        <v>2308.71789463233</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>2308.71789463234</v>
+        <v>2308.71789463233</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>0.0260998335916517</v>
+        <v>0.0260998335916476</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>0.0327143699689658</v>
+        <v>0.0327143699689634</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>0.0264434168913974</v>
+        <v>0.0264434168913932</v>
       </c>
       <c r="R26" s="18" t="n">
         <v>0.996892896698103</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>1.11117473585448</v>
+        <v>1.11117511751709</v>
       </c>
     </row>
     <row r="27">
@@ -3116,7 +3116,7 @@
         <v>2048.28319054732</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.887849879634654</v>
+        <v>0.887849879634648</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>1</v>
@@ -3125,37 +3125,37 @@
         <v>2316.98853854445</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>2044.44186629679</v>
+        <v>2044.44117554006</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>2203.24344465884</v>
+        <v>2203.24343906454</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>2307.01522580617</v>
+        <v>2307.01522580619</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>2307.01522580617</v>
+        <v>2307.01522580619</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>2313.57323878201</v>
+        <v>2313.57323878202</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>2313.57323878201</v>
+        <v>2313.57323878202</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>0.00210083951672115</v>
+        <v>0.00210083951672846</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>0.0551906316527067</v>
+        <v>0.0551906316527087</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.0021030478262225</v>
+        <v>0.00210304782622983</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>0.998525974684111</v>
+        <v>0.998525974684114</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>1.13164051124266</v>
+        <v>1.13164089359082</v>
       </c>
     </row>
     <row r="28">
@@ -3175,46 +3175,46 @@
         <v>2180.06020796427</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.953197185242869</v>
+        <v>0.953197185242857</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>2292.52747883232</v>
+        <v>2292.52747883233</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>2007.48051343357</v>
+        <v>2007.47987003456</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>2152.84028474644</v>
+        <v>2152.84027974246</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>2287.10306924459</v>
+        <v>2287.10306924461</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>2287.10306924459</v>
+        <v>2287.10306924461</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>2311.23685247283</v>
+        <v>2311.23685247287</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>2311.23685247283</v>
+        <v>2311.23685247287</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>-0.0010103707879185</v>
+        <v>-0.00101037078790605</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>0.0518939746785965</v>
+        <v>0.0518939746786078</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>-0.00100986053521657</v>
+        <v>-0.00100986053520413</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>1.00816102481356</v>
+        <v>1.00816102481357</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>1.15131222296137</v>
+        <v>1.15131259195794</v>
       </c>
     </row>
     <row r="29">
@@ -3234,46 +3234,46 @@
         <v>2112.86602822575</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.952874437844272</v>
+        <v>0.952874437844264</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>2363.72604559598</v>
+        <v>2363.72604559605</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>1967.42340452803</v>
+        <v>1967.42283778259</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>2090.58800712254</v>
+        <v>2090.58800340656</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>2217.36038276541</v>
+        <v>2217.36038276543</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>2363.72604559598</v>
+        <v>2363.72604559605</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>2368.44945259938</v>
+        <v>2368.44945259945</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>2368.44945259938</v>
+        <v>2368.44945259945</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>0.0244526864185003</v>
+        <v>0.0244526864185115</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>0.0529997426332647</v>
+        <v>0.0529997426332931</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>0.0247541051733138</v>
+        <v>0.0247541051733253</v>
       </c>
       <c r="R29" s="18" t="n">
-        <v>1.00199828868164</v>
+        <v>1.00199828868163</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>1.20383311855922</v>
+        <v>1.20383346534131</v>
       </c>
     </row>
     <row r="30">
@@ -3293,46 +3293,46 @@
         <v>2935.63493973013</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1.19162939212283</v>
+        <v>1.19162939212286</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>0.872461918315517</v>
+        <v>0.872461918319202</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>2429.79789895371</v>
+        <v>2429.79789895382</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>1925.02563699601</v>
+        <v>1925.02518143412</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>2016.60894984798</v>
+        <v>2016.60894832734</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>2463.54693760989</v>
+        <v>2463.54693760982</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>2459.24264996098</v>
+        <v>2459.24264996107</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>2400.54154181527</v>
+        <v>2400.54154181533</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>2400.54154181527</v>
+        <v>2400.54154181533</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>0.0134588526940012</v>
+        <v>0.0134588526940031</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>0.0397725713463775</v>
+        <v>0.0397725713464117</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>0.0135498307471424</v>
+        <v>0.0135498307471444</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>0.987959345445544</v>
+        <v>0.987959345445528</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>1.24701795949133</v>
+        <v>1.2470182546012</v>
       </c>
     </row>
     <row r="31">
@@ -3352,46 +3352,46 @@
         <v>2085.81764439801</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.899076837552731</v>
+        <v>0.899076837552717</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>2307.53924736255</v>
+        <v>2307.53924736264</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>1881.28999740405</v>
+        <v>1881.28969314399</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>1932.39114117599</v>
+        <v>1932.39114298624</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>2319.95482174312</v>
+        <v>2319.95482174316</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>2319.95482174312</v>
+        <v>2319.95482174316</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>2268.47340378071</v>
+        <v>2268.47340378077</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>2268.47340378071</v>
+        <v>2268.47340378077</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>-0.0565872584137456</v>
+        <v>-0.0565872584137494</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>-0.0194935843159401</v>
+        <v>-0.0194935843159186</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>-0.0550159769093964</v>
+        <v>-0.0550159769094</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>0.983070344902479</v>
+        <v>0.983070344902466</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>1.20580740178863</v>
+        <v>1.2058075968033</v>
       </c>
     </row>
     <row r="32">
@@ -3411,46 +3411,46 @@
         <v>1894.04001281739</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.959133225211618</v>
+        <v>0.959133225211585</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>1984.39953936684</v>
+        <v>1984.39953936687</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>1837.55315795174</v>
+        <v>1837.55305098486</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>1841.63577786032</v>
+        <v>1841.63578437285</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>1974.74132167562</v>
+        <v>1974.74132167569</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>1974.74132167562</v>
+        <v>1974.74132167569</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>1973.19864809582</v>
+        <v>1973.19864809586</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>1973.19864809582</v>
+        <v>1973.19864809586</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>-0.139451190665418</v>
+        <v>-0.139451190665424</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>-0.146258573203061</v>
+        <v>-0.146258573203058</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>-0.130164521740822</v>
+        <v>-0.130164521740827</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>0.994355526168589</v>
+        <v>0.994355526168593</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>1.07381853937509</v>
+        <v>1.07381860188379</v>
       </c>
     </row>
     <row r="33">
@@ -3470,25 +3470,25 @@
         <v>1574.64834843281</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.969995031877271</v>
+        <v>0.969995031877284</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>1620.24163556229</v>
+        <v>1620.24163556227</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>1795.42595635394</v>
+        <v>1795.42609873477</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>1749.98187505761</v>
+        <v>1749.98188787058</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>1623.35712728892</v>
+        <v>1623.3571272889</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>1623.35712728892</v>
+        <v>1623.3571272889</v>
       </c>
       <c r="M33" s="13" t="n">
         <v>1644.4417714242</v>
@@ -3497,19 +3497,19 @@
         <v>1644.4417714242</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>-0.182254927297096</v>
+        <v>-0.182254927297115</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>-0.305688466511532</v>
+        <v>-0.30568846651155</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>-0.166611140236123</v>
+        <v>-0.166611140236138</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>1.01493612763106</v>
+        <v>1.01493612763107</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.915906203541611</v>
+        <v>0.91590613090844</v>
       </c>
     </row>
     <row r="34">
@@ -3529,46 +3529,46 @@
         <v>1475.19763584073</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1.15539727863135</v>
+        <v>1.1553972786314</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>1356.31150944334</v>
+        <v>1356.31150944332</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>1756.60497292778</v>
+        <v>1756.60542284096</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1663.73397564352</v>
+        <v>1663.73399654932</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>1276.78822092104</v>
+        <v>1276.78822092098</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>1356.31150944334</v>
+        <v>1356.31150944332</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>1393.05245164079</v>
+        <v>1393.05245164078</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>1393.05245164079</v>
+        <v>1393.05245164078</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>-0.165903630132121</v>
+        <v>-0.165903630132128</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>-0.419692420491346</v>
+        <v>-0.419692420491366</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>-0.152872132143475</v>
+        <v>-0.152872132143481</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>1.02708886707931</v>
+        <v>1.02708886707932</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.793036837029415</v>
+        <v>0.793036633911672</v>
       </c>
     </row>
     <row r="35">
@@ -3588,46 +3588,46 @@
         <v>1124.55064572027</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.909661595862145</v>
+        <v>0.909661595862126</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>1226.10512660259</v>
+        <v>1226.10512660257</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1722.67924497228</v>
+        <v>1722.68006664348</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>1588.56349875492</v>
+        <v>1588.56352967608</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>1236.22966038756</v>
+        <v>1236.22966038759</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>1236.22966038756</v>
+        <v>1236.22966038759</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>1255.14399169794</v>
+        <v>1255.1439916979</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>1255.14399169794</v>
+        <v>1255.1439916979</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>-0.1042470473922</v>
+        <v>-0.104247047392222</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.446701032683005</v>
+        <v>-0.446701032683034</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>-0.098997320438595</v>
+        <v>-0.0989973204386141</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>1.02368382976736</v>
+        <v>1.02368382976735</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.728599938358305</v>
+        <v>0.728599590836075</v>
       </c>
     </row>
     <row r="36">
@@ -3647,46 +3647,46 @@
         <v>1152.15904543455</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.966734418302038</v>
+        <v>0.966734418302176</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>1196.45173875604</v>
+        <v>1196.4517387552</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>1694.98762637174</v>
+        <v>1694.98888978654</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1528.60475119763</v>
+        <v>1528.60479408233</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>1191.80513657328</v>
+        <v>1191.80513657311</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>1191.80513657328</v>
+        <v>1191.80513657311</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>1209.78595673279</v>
+        <v>1209.78595673259</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>1209.78595673279</v>
+        <v>1209.78595673259</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>-0.0368068517242453</v>
+        <v>-0.0368068517243785</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>-0.386890945875999</v>
+        <v>-0.386890945876109</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>-0.036137714290286</v>
+        <v>-0.0361377142904145</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>1.0111448022054</v>
+        <v>1.01114480220595</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>0.713743237950611</v>
+        <v>0.713742705938883</v>
       </c>
     </row>
     <row r="37">
@@ -3706,46 +3706,46 @@
         <v>1203.71436422561</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.987214402204545</v>
+        <v>0.987214402204921</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>1210.93719858923</v>
+        <v>1210.93719858977</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>1674.56494002012</v>
+        <v>1674.56672041044</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1486.23037058567</v>
+        <v>1486.23042725308</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>1219.30389339702</v>
+        <v>1219.30389339656</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>1219.30389339702</v>
+        <v>1219.30389339656</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>1224.92526010681</v>
+        <v>1224.92526010863</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>1224.92526010681</v>
+        <v>1224.92526010863</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>0.0124363812789892</v>
+        <v>0.0124363812806392</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>-0.255111806697819</v>
+        <v>-0.25511180669671</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>0.0125140346437063</v>
+        <v>0.0125140346453769</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>1.01155143432201</v>
+        <v>1.01155143432306</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>0.73148865764029</v>
+        <v>0.731487879926578</v>
       </c>
     </row>
     <row r="38">
@@ -3765,46 +3765,46 @@
         <v>1425.89524509937</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1.12338185943331</v>
+        <v>1.12338185942588</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>1282.7762580583</v>
+        <v>1282.77625807608</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>1662.13151975524</v>
+        <v>1662.13389680969</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>1462.12899645993</v>
+        <v>1462.12906838582</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>1269.28811705992</v>
+        <v>1269.28811706831</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>1269.28811705992</v>
+        <v>1269.28811706831</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>1291.03663407031</v>
+        <v>1291.0366340799</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>1291.03663407031</v>
+        <v>1291.0366340799</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>0.0525656579910541</v>
+        <v>0.0525656579969944</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>-0.0732318567404446</v>
+        <v>-0.0732318567335534</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>0.053971761475252</v>
+        <v>0.0539717614815129</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>1.00643945189983</v>
+        <v>1.00643945189335</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>0.776735546330547</v>
+        <v>0.77673443550963</v>
       </c>
     </row>
     <row r="39">
@@ -3824,46 +3824,46 @@
         <v>1290.38528816145</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.917596609091487</v>
+        <v>0.917596609077105</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>1403.098264404</v>
+        <v>1403.09826440097</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>1658.12316126079</v>
+        <v>1658.12621801194</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1455.65463597534</v>
+        <v>1455.65472400874</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>1406.26640876437</v>
+        <v>1406.26640878641</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>1406.26640876437</v>
+        <v>1406.26640878641</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>1398.218167438</v>
+        <v>1398.2181674282</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>1398.218167438</v>
+        <v>1398.2181674282</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>0.0797532004899035</v>
+        <v>0.079753200475461</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.113990248677778</v>
+        <v>0.113990248669996</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>0.0830197459461552</v>
+        <v>0.0830197459305138</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>0.996521913618024</v>
+        <v>0.996521913613187</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>0.843253504989845</v>
+        <v>0.843251950448397</v>
       </c>
     </row>
     <row r="40">
@@ -3883,46 +3883,46 @@
         <v>1470.49652561565</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.973160939096958</v>
+        <v>0.973160939156016</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>1495.26012887845</v>
+        <v>1495.26012876762</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>1662.73013309377</v>
+        <v>1662.73395443251</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>1465.19709188985</v>
+        <v>1465.19719589346</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>1511.05173516335</v>
+        <v>1511.05173507165</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>1511.05173516335</v>
+        <v>1511.05173507165</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>1483.99351272718</v>
+        <v>1483.99351265599</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>1483.99351272718</v>
+        <v>1483.99351265599</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>0.059538084799368</v>
+        <v>0.0595380847584065</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>0.226657909581736</v>
+        <v>0.226657909523085</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>0.0613461813662077</v>
+        <v>0.0613461813227334</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>0.992465112970196</v>
+        <v>0.992465112996145</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>0.892504131121976</v>
+        <v>0.892502079902778</v>
       </c>
     </row>
     <row r="41">
@@ -3942,46 +3942,46 @@
         <v>1506.23806134637</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.999093853349032</v>
+        <v>0.999093853430819</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>1520.18026156748</v>
+        <v>1520.18026157934</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>1675.98529334087</v>
+        <v>1675.98996410593</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>1488.89922582534</v>
+        <v>1488.89934423545</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>1507.60417181765</v>
+        <v>1507.60417169423</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>1507.60417181765</v>
+        <v>1507.60417169423</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>1515.30262776551</v>
+        <v>1515.30262778008</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>1515.30262776551</v>
+        <v>1515.30262778008</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>0.0208784000557699</v>
+        <v>0.0208784001133644</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.237057212481173</v>
+        <v>0.237057212491231</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>0.0210978786428706</v>
+        <v>0.0210978787016802</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>0.996791410910082</v>
+        <v>0.996791410911894</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>0.904126446566211</v>
+        <v>0.904123926892625</v>
       </c>
     </row>
     <row r="42">
@@ -4001,46 +4001,46 @@
         <v>1689.82206595359</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1.1008968305653</v>
+        <v>1.10089683028068</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>1524.68175900308</v>
+        <v>1524.68175928561</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>1697.82670109008</v>
+        <v>1697.83230367964</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>1525.13317262007</v>
+        <v>1525.13330192613</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>1534.95043226337</v>
+        <v>1534.95043266021</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>1534.95043226337</v>
+        <v>1534.95043266021</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>1534.58697530417</v>
+        <v>1534.58697549591</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>1534.58697530417</v>
+        <v>1534.58697549591</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>0.0126461000560943</v>
+        <v>0.0126461001714211</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0.188647118762239</v>
+        <v>0.188647118901925</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>0.0127264001165888</v>
+        <v>0.0127264002333833</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>1.00649657952723</v>
+        <v>1.00649657946649</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>0.903853717413499</v>
+        <v>0.903850734946002</v>
       </c>
     </row>
     <row r="43">
@@ -4060,46 +4060,46 @@
         <v>1445.19764128156</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.925908477917038</v>
+        <v>0.925908477859672</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>1576.54392874338</v>
+        <v>1576.54392873646</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>1728.08717722843</v>
+        <v>1728.09378868083</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>1572.36459184225</v>
+        <v>1572.36472599416</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>1560.84286487227</v>
+        <v>1560.84286496898</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>1560.84286487227</v>
+        <v>1560.84286496898</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>1587.3798825351</v>
+        <v>1587.37988247282</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>1587.3798825351</v>
+        <v>1587.37988247282</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>0.0338235110073294</v>
+        <v>0.0338235108431487</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.135287696514277</v>
+        <v>0.135287696477697</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>0.0344020300449053</v>
+        <v>0.0344020298750765</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>1.00687323302203</v>
+        <v>1.00687323298695</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>0.918576275232251</v>
+        <v>0.918572760847996</v>
       </c>
     </row>
     <row r="44">
@@ -4119,46 +4119,46 @@
         <v>1649.16622342598</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.974175926393124</v>
+        <v>0.974175926876139</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>1690.86540361995</v>
+        <v>1690.86540275746</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>1766.49774497492</v>
+        <v>1766.50543346729</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>1629.10822935831</v>
+        <v>1629.1083591219</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>1692.88336813249</v>
+        <v>1692.88336729312</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>1692.88336813249</v>
+        <v>1692.88336729312</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>1692.8624762848</v>
+        <v>1692.86247568537</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>1692.8624762848</v>
+        <v>1692.86247568537</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>0.0643360846916594</v>
+        <v>0.0643360843768011</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.140747895301626</v>
+        <v>0.140747894952423</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>0.0664507563124939</v>
+        <v>0.0664507559767129</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>1.00118109499465</v>
+        <v>1.00118109515083</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>0.958315673541281</v>
+        <v>0.958311502253706</v>
       </c>
     </row>
     <row r="45">
@@ -4178,46 +4178,46 @@
         <v>1834.94060897935</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>1.0055348980156</v>
+        <v>1.00553489846507</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>1815.7659983286</v>
+        <v>1815.76599813348</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>1812.68489985338</v>
+        <v>1812.69372056949</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>1693.82122239984</v>
+        <v>1693.82133468657</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>1824.84030400194</v>
+        <v>1824.84030318625</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>1824.84030400194</v>
+        <v>1824.84030318625</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>1806.0708946579</v>
+        <v>1806.07089441468</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>1806.0708946579</v>
+        <v>1806.07089441468</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>0.0647328402263062</v>
+        <v>0.0647328404457326</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.191887918336923</v>
+        <v>0.19188791816495</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>0.0668739605012396</v>
+        <v>0.0668739607353399</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>0.99466059851345</v>
+        <v>0.994660598486388</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>0.996351265906162</v>
+        <v>0.996346417445121</v>
       </c>
     </row>
     <row r="46">
@@ -4237,46 +4237,46 @@
         <v>1933.00273454338</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1.08672517922505</v>
+        <v>1.08672517802431</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>1881.71960249522</v>
+        <v>1881.71960399311</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>1866.22912840205</v>
+        <v>1866.23911872655</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>1765.27958389229</v>
+        <v>1765.27966110626</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>1778.74109434164</v>
+        <v>1778.741096307</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>1881.71960249522</v>
+        <v>1881.71960399311</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>1868.43026699487</v>
+        <v>1868.43026789247</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>1868.43026699487</v>
+        <v>1868.43026789247</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0.0339449396386735</v>
+        <v>0.0339449402537448</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0.217546021869845</v>
+        <v>0.217546022302632</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>0.0345276436940656</v>
+        <v>0.0345276443303739</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>0.992937664313679</v>
+        <v>0.992937664000291</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>1.00117945784862</v>
+        <v>1.00117409883007</v>
       </c>
     </row>
     <row r="47">
@@ -4296,46 +4296,46 @@
         <v>1888.09456688716</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.935898063190541</v>
+        <v>0.935898062546897</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>1885.44155898709</v>
+        <v>1885.44156039742</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>1926.71851428681</v>
+        <v>1926.72968829174</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>1842.91442216912</v>
+        <v>1842.91444164155</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>2017.4147603752</v>
+        <v>2017.41476176264</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>1885.44155898709</v>
+        <v>1885.44156039742</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>1882.13005470812</v>
+        <v>1882.13005534214</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>1882.13005470812</v>
+        <v>1882.13005534214</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>0.00730549436254097</v>
+        <v>0.00730549421899846</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>0.185683449447709</v>
+        <v>0.185683449893641</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>0.00733224458801196</v>
+        <v>0.00733224444341696</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>0.998243645228256</v>
+        <v>0.998243644817831</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>0.976857823678934</v>
+        <v>0.976852158753445</v>
       </c>
     </row>
     <row r="48">
@@ -4355,46 +4355,46 @@
         <v>1827.0050126273</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.973926099746679</v>
+        <v>0.97392610067209</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>1899.247254131</v>
+        <v>1899.24725088796</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>1993.75082271982</v>
+        <v>1993.7631649216</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>1926.73904565682</v>
+        <v>1926.73897926745</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>1875.91749836307</v>
+        <v>1875.9174965806</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>1875.91749836307</v>
+        <v>1875.9174965806</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>1901.01907422491</v>
+        <v>1901.01907186328</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>1901.01907422491</v>
+        <v>1901.01907186328</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>0.00998595394439167</v>
+        <v>0.00998595236523152</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>0.122961316029014</v>
+        <v>0.122961315031594</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>0.0100359799629908</v>
+        <v>0.0100359783679822</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>1.00093290649233</v>
+        <v>1.000932906958</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>0.953488797377195</v>
+        <v>0.953482893710716</v>
       </c>
     </row>
     <row r="49">
@@ -4414,46 +4414,46 @@
         <v>1977.85475412658</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1.00562081268808</v>
+        <v>1.00562081641642</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>1942.45703588737</v>
+        <v>1942.45703125003</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>2066.89802081618</v>
+        <v>2066.91147919273</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>2016.97939846595</v>
+        <v>2016.97921255276</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>1966.79974118641</v>
+        <v>1966.7997338945</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>1966.79974118641</v>
+        <v>1966.7997338945</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>1953.47061946748</v>
+        <v>1953.47061651255</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>1953.47061946748</v>
+        <v>1953.47061651255</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>0.0272174982141491</v>
+        <v>0.0272174979437882</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.0816134766611714</v>
+        <v>0.0816134751707167</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>0.0275912777276865</v>
+        <v>0.0275912774498661</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>1.00566992390392</v>
+        <v>1.00566992478358</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>0.945121916898489</v>
+        <v>0.945115761452692</v>
       </c>
     </row>
     <row r="50">
@@ -4473,46 +4473,46 @@
         <v>2160.36159801246</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1.07782817111025</v>
+        <v>1.07782816866538</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>2031.37412350354</v>
+        <v>2031.37413006628</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>2145.65842986328</v>
+        <v>2145.67290813903</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>2113.6073169706</v>
+        <v>2113.60697265283</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>2004.36549713403</v>
+        <v>2004.36550168059</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>2004.36549713403</v>
+        <v>2004.36550168059</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>2032.57434783342</v>
+        <v>2032.5743526221</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>2032.57434783342</v>
+        <v>2032.5743526221</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>0.0396955458157453</v>
+        <v>0.039695549684374</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>0.0878513283252236</v>
+        <v>0.0878513303655597</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>0.0404939432298714</v>
+        <v>0.0404939472551562</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>1.00059084356544</v>
+        <v>1.00059084269021</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>0.947296326173842</v>
+        <v>0.947289936370116</v>
       </c>
     </row>
     <row r="51">
@@ -4532,46 +4532,46 @@
         <v>2033.21078101257</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0.943587453177364</v>
+        <v>0.943587445578132</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>2130.76087781863</v>
+        <v>2130.76088732823</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>2229.46780972373</v>
+        <v>2229.48315895359</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>2216.34373925849</v>
+        <v>2216.34319332974</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>2154.76665587921</v>
+        <v>2154.76667323273</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>2154.76665587921</v>
+        <v>2154.76667323273</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>2132.55553683407</v>
+        <v>2132.55554347028</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>2132.55553683407</v>
+        <v>2132.55554347028</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>0.0480179018379705</v>
+        <v>0.0480179025938594</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>0.133054292130085</v>
+        <v>0.133054295274307</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>0.0491894375756634</v>
+        <v>0.0491894383687341</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>1.00084226204551</v>
+        <v>1.00084226069322</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>0.956531207821441</v>
+        <v>0.956524625407439</v>
       </c>
     </row>
     <row r="52">
@@ -4591,46 +4591,46 @@
         <v>2167.47837936594</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.977961266647953</v>
+        <v>0.977961272255745</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>2221.35219829693</v>
+        <v>2221.35218889344</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>2317.67361217719</v>
+        <v>2317.68962170046</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>2324.36339431813</v>
+        <v>2324.36260099069</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>2216.32333844382</v>
+        <v>2216.32332573505</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>2216.32333844382</v>
+        <v>2216.32332573505</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>2225.42620828899</v>
+        <v>2225.42620061018</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>2225.42620828899</v>
+        <v>2225.42620061018</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>0.0426274084525857</v>
+        <v>0.0426274018902406</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>0.170649068419443</v>
+        <v>0.17064906583443</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>0.0435490048680249</v>
+        <v>0.0435489980198962</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>1.00183402253599</v>
+        <v>1.00183402332017</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.960198276666941</v>
+        <v>0.960191640750163</v>
       </c>
     </row>
     <row r="53">
@@ -4650,46 +4650,46 @@
         <v>2312.92176137013</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>0.999408138940692</v>
+        <v>0.999408148722431</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>2327.80015685316</v>
+        <v>2327.80013633988</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>2409.57660078218</v>
+        <v>2409.59298864011</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>2436.53312572115</v>
+        <v>2436.53203944241</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>2314.2915003891</v>
+        <v>2314.2914777379</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>2314.2915003891</v>
+        <v>2314.2914777379</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>2337.58628867231</v>
+        <v>2337.5862755447</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>2337.58628867231</v>
+        <v>2337.5862755447</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>0.049170444878184</v>
+        <v>0.0491704427127876</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>0.196632427115562</v>
+        <v>0.196632422205512</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>0.0503993706758585</v>
+        <v>0.0503993684013275</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>1.00420402575811</v>
+        <v>1.00420402896797</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>0.970123252323044</v>
+        <v>0.970116648979775</v>
       </c>
     </row>
     <row r="54">
@@ -4709,46 +4709,46 @@
         <v>2696.86049566001</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>1.07640245653218</v>
+        <v>1.07640245416892</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>2491.07621711659</v>
+        <v>2491.07623389076</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>2504.41419517611</v>
+        <v>2504.43059809804</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>2551.17957675978</v>
+        <v>2551.17815611533</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>2505.43881546724</v>
+        <v>2505.43882096797</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>2505.43881546724</v>
+        <v>2505.43882096797</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>2496.93176327513</v>
+        <v>2496.93177551397</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>2496.93176327513</v>
+        <v>2496.93177551397</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>0.0659437870019144</v>
+        <v>0.0659437975193464</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>0.228457776187466</v>
+        <v>0.228457779314603</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>0.0681666706273001</v>
+        <v>0.0681666818616704</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>1.00235060899314</v>
+        <v>1.00235060715668</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>0.997012302551474</v>
+        <v>0.997005777445073</v>
       </c>
     </row>
     <row r="55">
@@ -4768,46 +4768,46 @@
         <v>2516.13485121782</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.945006615870572</v>
+        <v>0.945006594360355</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>2671.90890647181</v>
+        <v>2671.90894111614</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>2601.36426180866</v>
+        <v>2601.38022495544</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>2666.01818259964</v>
+        <v>2666.01639563139</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>2662.55792177695</v>
+        <v>2662.55798238203</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>2662.55792177695</v>
+        <v>2662.55798238203</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>2671.15025682719</v>
+        <v>2671.1502830015</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>2671.15025682719</v>
+        <v>2671.1502830015</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>0.0674465040002593</v>
+        <v>0.0674465088976016</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>0.252558355780364</v>
+        <v>0.252558364156262</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>0.0697730294894165</v>
+        <v>0.0697730347284613</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>0.999716064554901</v>
+        <v>0.999716061388559</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>1.02682669091871</v>
+        <v>1.02682039994644</v>
       </c>
     </row>
     <row r="56">
@@ -4827,46 +4827,46 @@
         <v>2803.88411969971</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.982424164812011</v>
+        <v>0.982424172389578</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>2842.79402991501</v>
+        <v>2842.79402571247</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>2699.60530751719</v>
+        <v>2699.62027423276</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>2778.53567459983</v>
+        <v>2778.53350593676</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>2854.04636828761</v>
+        <v>2854.04634627397</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>2854.04636828761</v>
+        <v>2854.04634627397</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>2847.90021411913</v>
+        <v>2847.90020489601</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>2847.90021411913</v>
+        <v>2847.90020489601</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>0.064072768317074</v>
+        <v>0.0640727552796136</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>0.279710018472699</v>
+        <v>0.279710018743892</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>0.0661699793338781</v>
+        <v>0.0661699654337293</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>1.00179618507369</v>
+        <v>1.00179618331028</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>1.05493206958403</v>
+        <v>1.05492621761606</v>
       </c>
     </row>
     <row r="57">
@@ -4886,46 +4886,46 @@
         <v>3010.33905330945</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>0.996487481051003</v>
+        <v>0.996487498688655</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>3034.64102794569</v>
+        <v>3034.64093815868</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>2798.35408517653</v>
+        <v>2798.3673870489</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>2886.20148281538</v>
+        <v>2886.19894291138</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>3020.95019812433</v>
+        <v>3020.95014465405</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>3020.95019812433</v>
+        <v>3020.95014465405</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>3038.37708776767</v>
+        <v>3038.37703366664</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>3038.37708776767</v>
+        <v>3038.37703366664</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>0.0647415644013945</v>
+        <v>0.0647415498340633</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>0.299792483593574</v>
+        <v>0.299792467749081</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>0.0668832681370688</v>
+        <v>0.066883252595427</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>1.00123113731989</v>
+        <v>1.00123114911586</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>1.08577292054018</v>
+        <v>1.08576774005033</v>
       </c>
     </row>
     <row r="58">
@@ -4945,46 +4945,46 @@
         <v>3500.76983696121</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>1.07465960165792</v>
+        <v>1.07465963050739</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>3256.79646152791</v>
+        <v>3256.79647442638</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>2896.92387332451</v>
+        <v>2896.93472081772</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>2986.86259076975</v>
+        <v>2986.85972663688</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>3257.56158653441</v>
+        <v>3257.56149908446</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>3257.56158653441</v>
+        <v>3257.56149908446</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>3251.94750416924</v>
+        <v>3251.94752631711</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>3251.94750416924</v>
+        <v>3251.94752631711</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0.0679305287658506</v>
+        <v>0.0679305533823994</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>0.302377402538138</v>
+        <v>0.302377405024506</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>0.0702909514626704</v>
+        <v>0.0702909778095402</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>0.998511126680481</v>
+        <v>0.99851112952641</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>1.12255193659518</v>
+        <v>1.12254774087529</v>
       </c>
     </row>
     <row r="59">
@@ -5004,46 +5004,46 @@
         <v>3286.26557559881</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0.946582313932149</v>
+        <v>0.946582227510843</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>3484.64680418221</v>
+        <v>3484.64703377109</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>2994.76707306954</v>
+        <v>2994.77454717665</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>3079.03972556292</v>
+        <v>3079.0366332036</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>3471.7166454838</v>
+        <v>3471.71696244547</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>3471.7166454838</v>
+        <v>3471.71696244547</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>3446.62962566986</v>
+        <v>3446.62982254225</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>3446.62962566986</v>
+        <v>3446.62982254225</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>0.0581427845242451</v>
+        <v>0.0581428348338555</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>0.290316640503704</v>
+        <v>0.290316701563254</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>0.0598663174147271</v>
+        <v>0.0598663707361899</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>0.98909009129226</v>
+        <v>0.989090082622314</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.1508840392509</v>
+        <v>1.15088123270969</v>
       </c>
     </row>
     <row r="60">
@@ -5063,46 +5063,46 @@
         <v>3537.71845126756</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>0.981479075790983</v>
+        <v>0.98147910341908</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.742571657283123</v>
+        <v>0.742575131382382</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>3530.85206393775</v>
+        <v>3530.85229927458</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>3091.5614840908</v>
+        <v>3091.56452949947</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>3162.60710927373</v>
+        <v>3162.60394756411</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>3604.47669087237</v>
+        <v>3604.47658940834</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>3585.52362517744</v>
+        <v>3585.52386619359</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>3493.08769181478</v>
+        <v>3493.08787355111</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>3493.08769181478</v>
+        <v>3493.08787355111</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>0.0133892370736912</v>
+        <v>0.0133892319808456</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0.226548484563114</v>
+        <v>0.226548552349523</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>0.0134792743029037</v>
+        <v>0.0134792691414103</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>0.989304459252577</v>
+        <v>0.989304444784838</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.12987812462739</v>
+        <v>1.12987707040249</v>
       </c>
     </row>
     <row r="61">
@@ -5122,46 +5122,46 @@
         <v>3321.73023465199</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>0.997640356875538</v>
+        <v>0.997640378463397</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>3366.34131392214</v>
+        <v>3366.34119010791</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>3187.2829995502</v>
+        <v>3187.28042016956</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>3239.40234858059</v>
+        <v>3239.39935631719</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>3329.58687142044</v>
+        <v>3329.58679937178</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>3329.58687142044</v>
+        <v>3329.58679937178</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>3348.60878903262</v>
+        <v>3348.60872454175</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>3348.60878903262</v>
+        <v>3348.60872454175</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>-0.0422410977982484</v>
+        <v>-0.0422411690846658</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.102104410447907</v>
+        <v>0.102104408846436</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>-0.0413613729539956</v>
+        <v>-0.0413614412919064</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>0.994732404341715</v>
+        <v>0.994732421770478</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>1.05061545821478</v>
+        <v>1.0506162882159</v>
       </c>
     </row>
     <row r="62">
@@ -5181,46 +5181,46 @@
         <v>3386.00448971788</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>1.07501154619837</v>
+        <v>1.07501166732039</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>3121.46632456763</v>
+        <v>3121.46614936826</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>3282.21623894786</v>
+        <v>3282.2066961557</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>3313.37763274145</v>
+        <v>3313.37514565478</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>3149.73778811216</v>
+        <v>3149.73743322986</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>3149.73778811216</v>
+        <v>3149.73743322986</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>3160.84325349282</v>
+        <v>3160.84312145752</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>3160.84325349282</v>
+        <v>3160.84312145752</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>-0.0577061283543691</v>
+        <v>-0.0577061508675421</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>-0.0280152894718074</v>
+        <v>-0.0280153366935699</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>-0.0560726998491955</v>
+        <v>-0.0560727210999938</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>1.01261488186346</v>
+        <v>1.01261489639964</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>0.963021027068602</v>
+        <v>0.963023786758971</v>
       </c>
     </row>
     <row r="63">
@@ -5240,46 +5240,46 @@
         <v>2696.05052423399</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0.949598792902685</v>
+        <v>0.94959865465256</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>3014.31056632651</v>
+        <v>3014.31081999856</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>3376.73476170381</v>
+        <v>3376.71677591369</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>3388.93607362846</v>
+        <v>3388.93453898408</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>2839.14695804619</v>
+        <v>2839.14737139179</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>3014.31056632651</v>
+        <v>3014.31081999856</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>3076.24940044804</v>
+        <v>3076.24956546887</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>3076.24940044804</v>
+        <v>3076.24956546887</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>-0.0271277165451152</v>
+        <v>-0.0271276211294257</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>-0.10746156838649</v>
+        <v>-0.10746157148962</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>-0.026763064872419</v>
+        <v>-0.0267629720103414</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>1.02054825896623</v>
+        <v>1.02054822782686</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>0.911013039974703</v>
+        <v>0.911017941277141</v>
       </c>
     </row>
     <row r="64">
@@ -5299,46 +5299,46 @@
         <v>3036.48849479411</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>0.971167059762958</v>
+        <v>0.97116690209037</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>3133.76486513737</v>
+        <v>3133.76534396598</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>3471.12932820629</v>
+        <v>3471.10128460997</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>3469.66258389061</v>
+        <v>3469.66257115017</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>3126.63868102698</v>
+        <v>3126.6391886485</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>3126.63868102698</v>
+        <v>3126.6391886485</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>3166.13327021105</v>
+        <v>3166.13353624204</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>3166.13327021105</v>
+        <v>3166.13353624204</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>0.0287999269385351</v>
+        <v>0.02879995731896</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>-0.0936004046992225</v>
+        <v>-0.0936003756975855</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>0.0292186549471298</v>
+        <v>0.0292186862152304</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>1.01032891951587</v>
+        <v>1.01032885003288</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>0.912133479004411</v>
+        <v>0.912140924921989</v>
       </c>
     </row>
     <row r="65">
@@ -5358,46 +5358,46 @@
         <v>3418.10930449306</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.00623034846883</v>
+        <v>1.00623040913128</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>3353.10057061988</v>
+        <v>3353.10023119716</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>3565.46418372145</v>
+        <v>3565.42434368858</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>3557.26894864039</v>
+        <v>3557.27115840321</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>3396.94515246371</v>
+        <v>3396.94494767262</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>3396.94515246371</v>
+        <v>3396.94494767262</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>3351.26178934381</v>
+        <v>3351.26137129933</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>3351.26178934381</v>
+        <v>3351.26137129933</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>0.0568258736916811</v>
+        <v>0.0568256649253215</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>0.000792269410472946</v>
+        <v>0.000792163843489124</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>0.058471486615731</v>
+        <v>0.058471265642515</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>0.999451617618577</v>
+        <v>0.999451594115582</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>0.939922999267359</v>
+        <v>0.939933384712437</v>
       </c>
     </row>
     <row r="66">
@@ -5417,46 +5417,46 @@
         <v>3735.59369195447</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>1.07205458780295</v>
+        <v>1.0720551324322</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>3532.23550348917</v>
+        <v>3532.2334807144</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>3659.58826686095</v>
+        <v>3659.53478578355</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>3651.75183347598</v>
+        <v>3651.75710008084</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>3484.51817142085</v>
+        <v>3484.51640120357</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>3484.51817142085</v>
+        <v>3484.51640120357</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>3513.09879494691</v>
+        <v>3513.09723640087</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>3513.09879494691</v>
+        <v>3513.09723640087</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>0.0471615671040008</v>
+        <v>0.0471612482077777</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>0.111443533640856</v>
+        <v>0.111443086989058</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>0.0482913647980903</v>
+        <v>0.0482910305019866</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>0.994582267087415</v>
+        <v>0.994582395411286</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.959971051049498</v>
+        <v>0.959984654346899</v>
       </c>
     </row>
     <row r="67">
@@ -5476,46 +5476,46 @@
         <v>3551.93509050901</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>0.956071348379942</v>
+        <v>0.956071136652159</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>0.680802551080681</v>
+        <v>0.680771274598217</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>3625.15307694015</v>
+        <v>3625.1523417104</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>3753.2451918419</v>
+        <v>3753.1761439064</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>3752.30628501464</v>
+        <v>3752.31556446706</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>3715.13600583026</v>
+        <v>3715.13682856978</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>3686.41368448225</v>
+        <v>3686.41119552373</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>3624.61657958098</v>
+        <v>3624.61575107763</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>3624.61657958098</v>
+        <v>3624.61575107763</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>0.0312500160020956</v>
+        <v>0.0312502310638873</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>0.178258361969311</v>
+        <v>0.178258029440851</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>0.0317434240091594</v>
+        <v>0.0317436458977727</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>0.999852006977972</v>
+        <v>0.999851981218389</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>0.965728694586618</v>
+        <v>0.965746240544157</v>
       </c>
     </row>
     <row r="68">
@@ -5535,46 +5535,46 @@
         <v>3501.98814428698</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>0.961788514543489</v>
+        <v>0.961787607434078</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>3682.58914122278</v>
+        <v>3682.59068640353</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>3846.06915407179</v>
+        <v>3845.98256457832</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>3857.29118156341</v>
+        <v>3857.30551635146</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>3641.12077793858</v>
+        <v>3641.12421205948</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>3641.12077793858</v>
+        <v>3641.12421205948</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>3693.37980238386</v>
+        <v>3693.38068702193</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>3693.37980238386</v>
+        <v>3693.38068702193</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.0187934628823631</v>
+        <v>0.018793930979115</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>0.16652695486115</v>
+        <v>0.166527136251393</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.0189711715137695</v>
+        <v>0.0189716484909768</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>1.00293018328879</v>
+        <v>1.00293000269029</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>0.960299894367143</v>
+        <v>0.960321744835283</v>
       </c>
     </row>
     <row r="69">
@@ -5594,46 +5594,46 @@
         <v>3831.21508377001</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1.00692563907867</v>
+        <v>1.0069258615712</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>3803.1174225621</v>
+        <v>3803.1164493572</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>3937.65257926597</v>
+        <v>3937.54646622772</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>3964.73593842662</v>
+        <v>3964.75639867893</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>3804.86396917606</v>
+        <v>3804.86312844503</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>3804.86396917606</v>
+        <v>3804.86312844503</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>3827.81365875481</v>
+        <v>3827.81265395562</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>3827.81365875481</v>
+        <v>3827.81265395562</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>0.0357518194749032</v>
+        <v>0.0357513174554632</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>0.142200728969106</v>
+        <v>0.142200571622834</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>0.0363986006216248</v>
+        <v>0.0363980803295103</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>1.00649368227397</v>
+        <v>1.0064936756282</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>0.972105482060677</v>
+        <v>0.972131424171552</v>
       </c>
     </row>
     <row r="70">
@@ -5653,46 +5653,46 @@
         <v>4375.22212253129</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>1.07753318513074</v>
+        <v>1.07753471684332</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>4057.14418180297</v>
+        <v>4057.13949596517</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>4027.45980040473</v>
+        <v>4027.33223081271</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>4071.5891188905</v>
+        <v>4071.61674787291</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>4060.40591872855</v>
+        <v>4060.40014687292</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>4060.40591872855</v>
+        <v>4060.40014687292</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>4060.53673897943</v>
+        <v>4060.53359852201</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>4060.53673897943</v>
+        <v>4060.53359852201</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>0.0590213726751685</v>
+        <v>0.0590208617649748</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0.155827654155337</v>
+        <v>0.155827272996854</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>0.0607979125870843</v>
+        <v>0.0607973706147558</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>1.00083619339724</v>
+        <v>1.00083657526694</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>1.00821285381207</v>
+        <v>1.0082440101304</v>
       </c>
     </row>
     <row r="71">
@@ -5712,46 +5712,46 @@
         <v>4129.41074094782</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>0.956663579607671</v>
+        <v>0.956663618922213</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>4305.67903705404</v>
+        <v>4305.68043739183</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>4114.87215758706</v>
+        <v>4114.72131320528</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>4173.99992639501</v>
+        <v>4174.03563400565</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>4316.47114928457</v>
+        <v>4316.47097189716</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>4316.47114928457</v>
+        <v>4316.47097189716</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>4304.88853783519</v>
+        <v>4304.89008968019</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>4304.88853783519</v>
+        <v>4304.89008968019</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>0.0584360796221901</v>
+        <v>0.0584372135162203</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>0.187681081107026</v>
+        <v>0.187681780724014</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>0.0601772166004768</v>
+        <v>0.0601784187297751</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>0.999816405446842</v>
+        <v>0.999816440694302</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>1.04617795473859</v>
+        <v>1.0462166844361</v>
       </c>
     </row>
     <row r="72">
@@ -5771,46 +5771,46 @@
         <v>4333.19154339499</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>0.957356250806805</v>
+        <v>0.957353641997135</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>4565.4390345781</v>
+        <v>4565.45027665089</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>4199.29158223589</v>
+        <v>4199.11583572495</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>4268.06164837933</v>
+        <v>4268.10604414442</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>4526.20593404307</v>
+        <v>4526.21826805351</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>4526.20593404307</v>
+        <v>4526.21826805351</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>4539.6544634879</v>
+        <v>4539.66225278623</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>4539.6544634879</v>
+        <v>4539.66225278623</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>0.0530996535758678</v>
+        <v>0.0531010089251677</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>0.229132855645612</v>
+        <v>0.229134670232621</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>0.0545347280398505</v>
+        <v>0.0545361573037244</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>0.994352225296427</v>
+        <v>0.994351482920195</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>1.08105245244027</v>
+        <v>1.08109955294969</v>
       </c>
     </row>
     <row r="73">
@@ -5830,46 +5830,46 @@
         <v>4811.64490558585</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>1.00457438036812</v>
+        <v>1.00457298216005</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>4727.16877888504</v>
+        <v>4727.16775207854</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>4280.24600514395</v>
+        <v>4280.04401422794</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>4350.57992839706</v>
+        <v>4350.63314204592</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>4789.7348365809</v>
+        <v>4789.74150314074</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>4789.7348365809</v>
+        <v>4789.74150314074</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>4694.63514081257</v>
+        <v>4694.63470650351</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>4694.63514081257</v>
+        <v>4694.63470650351</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>0.0335694975605833</v>
+        <v>0.0335676892152024</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>0.226453416841544</v>
+        <v>0.226453625323626</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>0.0341393113883808</v>
+        <v>0.0341374413090247</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>0.993117732919165</v>
+        <v>0.993117856763022</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>1.09681432683323</v>
+        <v>1.09686598803596</v>
       </c>
     </row>
     <row r="74">
@@ -5889,46 +5889,46 @@
         <v>5066.12763917827</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>1.08415879483615</v>
+        <v>1.08416515300385</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>4698.7421427025</v>
+        <v>4698.72800139924</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>4357.46767857388</v>
+        <v>4357.23850359065</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>4419.65113143013</v>
+        <v>4419.71265258642</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>4672.86495604541</v>
+        <v>4672.83755167907</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>4672.86495604541</v>
+        <v>4672.83755167907</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>4682.23956483794</v>
+        <v>4682.22869752653</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>4682.23956483794</v>
+        <v>4682.22869752653</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>-0.00264386239214552</v>
+        <v>-0.00264609084746818</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0.153108533630645</v>
+        <v>0.153106749130413</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>-0.00264037046603982</v>
+        <v>-0.00264259303493841</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>0.996487873272596</v>
+        <v>0.996488559485078</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>1.07453225364378</v>
+        <v>1.07458627607097</v>
       </c>
     </row>
     <row r="75">
@@ -5948,46 +5948,46 @@
         <v>4383.03555041862</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>0.95418346411678</v>
+        <v>0.954182493433938</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>4617.37326794684</v>
+        <v>4617.37007192823</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>4431.00728530794</v>
+        <v>4430.75051962008</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>4475.56739700138</v>
+        <v>4475.63584244766</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>4593.49351068003</v>
+        <v>4593.49818360724</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>4593.49351068003</v>
+        <v>4593.49818360724</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>4619.23676470095</v>
+        <v>4619.23645503496</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>4619.23676470095</v>
+        <v>4619.23645503496</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>-0.0135470459607946</v>
+        <v>-0.0135447920320336</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>0.0730212232216889</v>
+        <v>0.0730207644809178</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>-0.013455697698623</v>
+        <v>-0.0134534740955401</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>1.00040358373603</v>
+        <v>1.00040420912287</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.04248006542827</v>
+        <v>1.0425404081273</v>
       </c>
     </row>
     <row r="76">
@@ -6007,46 +6007,46 @@
         <v>4429.87614408065</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>0.959450924441226</v>
+        <v>0.959447429221911</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>4562.05973896335</v>
+        <v>4562.08375906755</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>4501.11263142683</v>
+        <v>4500.82852752827</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>4519.88693375675</v>
+        <v>4519.95960280684</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>4617.09508139832</v>
+        <v>4617.1119012463</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>4617.09508139832</v>
+        <v>4617.1119012463</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>4577.90209281063</v>
+        <v>4577.9192023042</v>
       </c>
       <c r="N76" s="14" t="n">
-        <v>4577.90209281063</v>
+        <v>4577.9192023042</v>
       </c>
       <c r="O76" s="15" t="n">
-        <v>-0.00898865415350189</v>
+        <v>-0.00898484971290129</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>0.00842522919538258</v>
+        <v>0.00842726779828062</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>-0.00894837697131767</v>
+        <v>-0.0089446065671136</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>1.00347263182724</v>
+        <v>1.00347109875069</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.01706010661623</v>
+        <v>1.01712810748164</v>
       </c>
     </row>
     <row r="77">
@@ -6066,46 +6066,46 @@
         <v>4465.28611985202</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>0.99584324466396</v>
+        <v>0.995836554113189</v>
       </c>
       <c r="G77" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>4554.37007898967</v>
+        <v>4554.38623603062</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>4568.1330769021</v>
+        <v>4567.82270981725</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>4554.75758091054</v>
+        <v>4554.83013654696</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>4483.92469776586</v>
+        <v>4483.95482311697</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>4483.92469776586</v>
+        <v>4483.95482311697</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>4567.17770390767</v>
+        <v>4567.18887598509</v>
       </c>
       <c r="N77" s="14" t="n">
-        <v>4567.17770390767</v>
+        <v>4567.18887598509</v>
       </c>
       <c r="O77" s="15" t="n">
-        <v>-0.00234539097688833</v>
+        <v>-0.00234668221556364</v>
       </c>
       <c r="P77" s="16" t="n">
-        <v>-0.027149593755829</v>
+        <v>-0.0271471240013353</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>-0.00234264269648832</v>
+        <v>-0.00234393090942109</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>1.00281216165921</v>
+        <v>1.00281105714162</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>0.999790861391656</v>
+        <v>0.999861239397318</v>
       </c>
     </row>
     <row r="78">
@@ -6125,46 +6125,46 @@
         <v>5131.88191643965</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>1.09567419579332</v>
+        <v>1.09568177102831</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>4645.72429938467</v>
+        <v>4645.69566136202</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>4632.49047073654</v>
+        <v>4632.15592609762</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>4582.81321841529</v>
+        <v>4582.8794080432</v>
       </c>
       <c r="K78" s="11" t="n">
-        <v>4683.76633870065</v>
+        <v>4683.73395646012</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>4683.76633870065</v>
+        <v>4683.73395646012</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>4649.61558921466</v>
+        <v>4649.59256955151</v>
       </c>
       <c r="N78" s="14" t="n">
-        <v>4649.61558921466</v>
+        <v>4649.59256955151</v>
       </c>
       <c r="O78" s="15" t="n">
-        <v>0.0178891033257536</v>
+        <v>0.0178817062754435</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>-0.00696760069012148</v>
+        <v>-0.00697021228208139</v>
       </c>
       <c r="Q78" s="17" t="n">
-        <v>0.0180500717623608</v>
+        <v>0.0180425412226137</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>1.00083760670656</v>
+        <v>1.00083882123874</v>
       </c>
       <c r="S78" s="19" t="n">
-        <v>1.0036967412208</v>
+        <v>1.00376426090401</v>
       </c>
     </row>
     <row r="79">
@@ -6184,46 +6184,46 @@
         <v>4499.44907972728</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>0.947850085913331</v>
+        <v>0.947861555190371</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>4743.16547040477</v>
+        <v>4743.10978284322</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>4694.55403169595</v>
+        <v>4694.19861855082</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>4606.33356180779</v>
+        <v>4606.38500510362</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>4747.00498169148</v>
+        <v>4746.94754216885</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>4747.00498169148</v>
+        <v>4746.94754216885</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>4724.97456282014</v>
+        <v>4724.94205355565</v>
       </c>
       <c r="N79" s="14" t="n">
-        <v>4724.97456282014</v>
+        <v>4724.94205355565</v>
       </c>
       <c r="O79" s="15" t="n">
-        <v>0.0160776302051853</v>
+        <v>0.0160757007635902</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>0.0228907508979013</v>
+        <v>0.0228837816703391</v>
       </c>
       <c r="Q79" s="17" t="n">
-        <v>0.0162075707463405</v>
+        <v>0.0162056100350758</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>0.996164816998662</v>
+        <v>0.996169658700862</v>
       </c>
       <c r="S79" s="19" t="n">
-        <v>1.00647996187046</v>
+        <v>1.00654924035028</v>
       </c>
     </row>
     <row r="80">
@@ -6243,46 +6243,46 @@
         <v>4539.76782551238</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>0.961383012627281</v>
+        <v>0.961379505936897</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>4739.18562222663</v>
+        <v>4739.22273086162</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>4754.72502596365</v>
+        <v>4754.35346562722</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>4628.10309222627</v>
+        <v>4628.12878827834</v>
       </c>
       <c r="K80" s="11" t="n">
-        <v>4722.12194919696</v>
+        <v>4722.13917342478</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>4722.12194919696</v>
+        <v>4722.13917342478</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>4718.75855707079</v>
+        <v>4718.82629073957</v>
       </c>
       <c r="N80" s="14" t="n">
-        <v>4718.75855707079</v>
+        <v>4718.82629073957</v>
       </c>
       <c r="O80" s="15" t="n">
-        <v>-0.00131642996855628</v>
+        <v>-0.00129519561430605</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>0.030768780416115</v>
+        <v>0.0307797237584375</v>
       </c>
       <c r="Q80" s="17" t="n">
-        <v>-0.00131556385472631</v>
+        <v>-0.00129435721047111</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>0.995689752040934</v>
+        <v>0.995696247827892</v>
       </c>
       <c r="S80" s="19" t="n">
-        <v>0.992435636404533</v>
+        <v>0.992527443501098</v>
       </c>
     </row>
     <row r="81">
@@ -6302,46 +6302,46 @@
         <v>4837.70906203481</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>0.989654550393854</v>
+        <v>0.989625084763068</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>0.00678800275307756</v>
+        <v>0.00696110715682074</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>4682.38774747861</v>
+        <v>4682.64682256079</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>4813.43750156667</v>
+        <v>4813.05611385449</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>4651.60964790838</v>
+        <v>4651.59543080282</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>4888.28052183415</v>
+        <v>4888.42606813371</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>4683.78534819777</v>
+        <v>4684.07927393987</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>4661.61106427856</v>
+        <v>4661.88039821074</v>
       </c>
       <c r="N81" s="14" t="n">
-        <v>4661.61106427856</v>
+        <v>4661.88039821074</v>
       </c>
       <c r="O81" s="15" t="n">
-        <v>-0.0121846370948498</v>
+        <v>-0.0121412157834242</v>
       </c>
       <c r="P81" s="16" t="n">
-        <v>0.0206765242110218</v>
+        <v>0.0207329989621294</v>
       </c>
       <c r="Q81" s="17" t="n">
-        <v>-0.0121107049875664</v>
+        <v>-0.0120678086075319</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>0.995562801647249</v>
+        <v>0.995565237965417</v>
       </c>
       <c r="S81" s="19" t="n">
-        <v>0.968457793990532</v>
+        <v>0.968590493842656</v>
       </c>
     </row>
     <row r="82">
@@ -6361,46 +6361,46 @@
         <v>4964.35954377805</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>1.10780605640002</v>
+        <v>1.1078069976233</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>0.423000472797716</v>
+        <v>0.42021881289975</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>4612.09970248699</v>
+        <v>4612.28923909565</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>4871.10512960908</v>
+        <v>4870.72207582766</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>4680.81116137662</v>
+        <v>4680.73965783825</v>
       </c>
       <c r="K82" s="11" t="n">
-        <v>4481.25329799196</v>
+        <v>4481.24949059596</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>4556.75161152171</v>
+        <v>4557.22387153843</v>
       </c>
       <c r="M82" s="13" t="n">
-        <v>4592.18178034687</v>
+        <v>4592.42757054202</v>
       </c>
       <c r="N82" s="14" t="n">
-        <v>4592.18178034687</v>
+        <v>4592.42757054202</v>
       </c>
       <c r="O82" s="15" t="n">
-        <v>-0.0150058657914611</v>
+        <v>-0.0150101189405884</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>-0.0123523779043186</v>
+        <v>-0.0122946254224182</v>
       </c>
       <c r="Q82" s="17" t="n">
-        <v>-0.0148938388411933</v>
+        <v>-0.014898028635693</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>0.995681376504202</v>
+        <v>0.99569375042977</v>
       </c>
       <c r="S82" s="19" t="n">
-        <v>0.942739205613369</v>
+        <v>0.942863809317564</v>
       </c>
     </row>
     <row r="83">
@@ -6420,46 +6420,46 @@
         <v>4294.14828388207</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>0.939342886659752</v>
+        <v>0.939395345756259</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>4536.30165422507</v>
+        <v>4536.19369422288</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>4928.06054859909</v>
+        <v>4927.68625361681</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>4719.82644365494</v>
+        <v>4719.6786137615</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>4571.43855014627</v>
+        <v>4571.18326515134</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>4571.43855014627</v>
+        <v>4571.18326515134</v>
       </c>
       <c r="M83" s="13" t="n">
-        <v>4543.91172396844</v>
+        <v>4543.89115450122</v>
       </c>
       <c r="N83" s="14" t="n">
-        <v>4543.91172396844</v>
+        <v>4543.89115450122</v>
       </c>
       <c r="O83" s="15" t="n">
-        <v>-0.0105669902596387</v>
+        <v>-0.0106250392773921</v>
       </c>
       <c r="P83" s="16" t="n">
-        <v>-0.038320383833692</v>
+        <v>-0.0383181205192107</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>-0.0105113557535995</v>
+        <v>-0.0105687929303742</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>1.00167759340614</v>
+        <v>1.00169689850064</v>
       </c>
       <c r="S83" s="19" t="n">
-        <v>0.922048680035019</v>
+        <v>0.92211454233031</v>
       </c>
     </row>
     <row r="84">
@@ -6479,46 +6479,46 @@
         <v>4320.30298531754</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>0.965211222935482</v>
+        <v>0.965220704291804</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>4523.03739870535</v>
+        <v>4523.06761794701</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>4984.43992609611</v>
+        <v>4984.08761291434</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>4772.15400801801</v>
+        <v>4771.91186401794</v>
       </c>
       <c r="K84" s="11" t="n">
-        <v>4476.01818405952</v>
+        <v>4475.97421616376</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>4476.01818405952</v>
+        <v>4475.97421616376</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>4520.57671063874</v>
+        <v>4520.61930445801</v>
       </c>
       <c r="N84" s="14" t="n">
-        <v>4520.57671063874</v>
+        <v>4520.61930445801</v>
       </c>
       <c r="O84" s="15" t="n">
-        <v>-0.00514867773218188</v>
+        <v>-0.00513472873788401</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>-0.0419987257315996</v>
+        <v>-0.0420034504492219</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>-0.00513544600935245</v>
+        <v>-0.00512156855257362</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>0.999455965571429</v>
+        <v>0.999458705087829</v>
       </c>
       <c r="S84" s="19" t="n">
-        <v>0.906937745797917</v>
+        <v>0.90701040100992</v>
       </c>
     </row>
     <row r="85">
@@ -6538,46 +6538,46 @@
         <v>4458.85316814996</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>0.978069216457181</v>
+        <v>0.977959040008133</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>4495.47706046516</v>
+        <v>4495.80515311878</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>5040.15654091052</v>
+        <v>5039.84230504487</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>4840.55042827295</v>
+        <v>4840.1964973099</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>4558.83192428965</v>
+        <v>4559.34552035316</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>4558.83192428965</v>
+        <v>4559.34552035316</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>4509.90269563113</v>
+        <v>4510.13303734554</v>
       </c>
       <c r="N85" s="14" t="n">
-        <v>4509.90269563113</v>
+        <v>4510.13303734554</v>
       </c>
       <c r="O85" s="15" t="n">
-        <v>-0.00236399852064599</v>
+        <v>-0.00232234733686418</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>-0.0325441926740623</v>
+        <v>-0.032550676530321</v>
       </c>
       <c r="Q85" s="17" t="n">
-        <v>-0.00236120647670579</v>
+        <v>-0.00231965277459445</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>1.00320892198357</v>
+        <v>1.00318694510522</v>
       </c>
       <c r="S85" s="19" t="n">
-        <v>0.894794171376353</v>
+        <v>0.89489566624553</v>
       </c>
     </row>
     <row r="86">
@@ -6597,46 +6597,46 @@
         <v>5009.75394783902</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>1.12681831618822</v>
+        <v>1.12683399412535</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>4494.78373542816</v>
+        <v>4494.70913503942</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>5094.80590826391</v>
+        <v>5094.54891046004</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>4926.29159910711</v>
+        <v>4925.80991410043</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>4445.92874988571</v>
+        <v>4445.86689251206</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>4445.92874988571</v>
+        <v>4445.86689251206</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>4519.21999282044</v>
+        <v>4519.13665997677</v>
       </c>
       <c r="N86" s="14" t="n">
-        <v>4519.21999282044</v>
+        <v>4519.13665997677</v>
       </c>
       <c r="O86" s="15" t="n">
-        <v>0.00206383295874412</v>
+        <v>0.00199431978825235</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>-0.0158882620541462</v>
+        <v>-0.015959078164971</v>
       </c>
       <c r="Q86" s="17" t="n">
-        <v>0.00206596412785842</v>
+        <v>0.00199630976662579</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>1.00543658134198</v>
+        <v>1.00543472874516</v>
       </c>
       <c r="S86" s="19" t="n">
-        <v>0.887024957219694</v>
+        <v>0.887053346508884</v>
       </c>
     </row>
     <row r="87">
@@ -6656,46 +6656,46 @@
         <v>4294.11901736909</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>0.928219227794002</v>
+        <v>0.928364359058997</v>
       </c>
       <c r="G87" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>4627.80203075273</v>
+        <v>4627.08106135998</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>5147.6827154925</v>
+        <v>5147.50569912106</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>5029.2448226879</v>
+        <v>5028.6252599678</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>4626.19054722068</v>
+        <v>4625.46733452981</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>4626.19054722068</v>
+        <v>4625.46733452981</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>4655.36266811604</v>
+        <v>4654.92314576653</v>
       </c>
       <c r="N87" s="14" t="n">
-        <v>4655.36266811604</v>
+        <v>4654.92314576653</v>
       </c>
       <c r="O87" s="15" t="n">
-        <v>0.0296804060714761</v>
+        <v>0.0296044293827724</v>
       </c>
       <c r="P87" s="16" t="n">
-        <v>0.0245275328655075</v>
+        <v>0.0244354425513305</v>
       </c>
       <c r="Q87" s="17" t="n">
-        <v>0.0301252595606964</v>
+        <v>0.0300469970276267</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>1.00595544865147</v>
+        <v>1.00601720264619</v>
       </c>
       <c r="S87" s="19" t="n">
-        <v>0.904360840675986</v>
+        <v>0.904306555029432</v>
       </c>
     </row>
     <row r="88">
@@ -6715,46 +6715,46 @@
         <v>4771.89666477564</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>0.969278928098691</v>
+        <v>0.969328113082425</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>4904.81253137447</v>
+        <v>4905.31899872709</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>5197.67610170852</v>
+        <v>5197.60551472792</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>5146.87558693663</v>
+        <v>5146.11596538232</v>
       </c>
       <c r="K88" s="11" t="n">
-        <v>4923.14082813711</v>
+        <v>4922.89102149446</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>4923.14082813711</v>
+        <v>4922.89102149446</v>
       </c>
       <c r="M88" s="13" t="n">
-        <v>4902.70710925305</v>
+        <v>4903.03852086714</v>
       </c>
       <c r="N88" s="14" t="n">
-        <v>4902.70710925305</v>
+        <v>4903.03852086714</v>
       </c>
       <c r="O88" s="15" t="n">
-        <v>0.0517677067726714</v>
+        <v>0.0519297186762073</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>0.0845313381620101</v>
+        <v>0.0845944306860806</v>
       </c>
       <c r="Q88" s="17" t="n">
-        <v>0.0531310788804993</v>
+        <v>0.0533017124732249</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>0.999570743609883</v>
+        <v>0.999535101007591</v>
       </c>
       <c r="S88" s="19" t="n">
-        <v>0.94324983190882</v>
+        <v>0.943326404240164</v>
       </c>
     </row>
     <row r="89">
@@ -6774,46 +6774,46 @@
         <v>4952.78741323696</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>0.96388556732017</v>
+        <v>0.96340774562595</v>
       </c>
       <c r="G89" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>5155.05795547829</v>
+        <v>5156.20666685382</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>5243.34927341901</v>
+        <v>5243.41492700275</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>5274.6341083973</v>
+        <v>5273.73967118715</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>5138.35623351731</v>
+        <v>5140.90470594983</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>5138.35623351731</v>
+        <v>5140.90470594983</v>
       </c>
       <c r="M89" s="13" t="n">
-        <v>5130.72016145044</v>
+        <v>5131.5724471664</v>
       </c>
       <c r="N89" s="14" t="n">
-        <v>5130.72016145044</v>
+        <v>5131.5724471664</v>
       </c>
       <c r="O89" s="15" t="n">
-        <v>0.0454585078423674</v>
+        <v>0.0455570129009924</v>
       </c>
       <c r="P89" s="16" t="n">
-        <v>0.137656510066327</v>
+        <v>0.137787378925438</v>
       </c>
       <c r="Q89" s="17" t="n">
-        <v>0.0465075818555529</v>
+        <v>0.0466106732236824</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>0.995278851520575</v>
+        <v>0.995222414212802</v>
       </c>
       <c r="S89" s="19" t="n">
-        <v>0.978519624366902</v>
+        <v>0.978669916191378</v>
       </c>
     </row>
     <row r="90">
@@ -6833,46 +6833,46 @@
         <v>6108.57642446564</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>1.14757562230873</v>
+        <v>1.14788571921931</v>
       </c>
       <c r="G90" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>5269.44966345155</v>
+        <v>5268.6798431953</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>5283.09385258506</v>
+        <v>5283.3288091094</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>5406.85192981986</v>
+        <v>5405.83789350598</v>
       </c>
       <c r="K90" s="11" t="n">
-        <v>5323.02735063003</v>
+        <v>5321.58935527149</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>5323.02735063003</v>
+        <v>5321.58935527149</v>
       </c>
       <c r="M90" s="13" t="n">
-        <v>5271.32353870366</v>
+        <v>5270.6778047779</v>
       </c>
       <c r="N90" s="14" t="n">
-        <v>5271.32353870366</v>
+        <v>5270.6778047779</v>
       </c>
       <c r="O90" s="15" t="n">
-        <v>0.0270354452064886</v>
+        <v>0.0267468378598365</v>
       </c>
       <c r="P90" s="16" t="n">
-        <v>0.166423309128139</v>
+        <v>0.166301929184189</v>
       </c>
       <c r="Q90" s="17" t="n">
-        <v>0.027404218672779</v>
+        <v>0.0271077450515791</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>1.00035561118747</v>
+        <v>1.00037921483978</v>
       </c>
       <c r="S90" s="19" t="n">
-        <v>0.997772079351641</v>
+        <v>0.997605486088678</v>
       </c>
     </row>
     <row r="91">
@@ -6892,46 +6892,46 @@
         <v>4881.31680020904</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>0.920849714582981</v>
+        <v>0.921241684082154</v>
       </c>
       <c r="G91" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>5385.41134843044</v>
+        <v>5383.55961332773</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>5315.23584051779</v>
+        <v>5315.67796532356</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v>5537.17920457991</v>
+        <v>5536.08797363631</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>5300.88322003728</v>
+        <v>5298.62780261877</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>5300.88322003728</v>
+        <v>5298.62780261877</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>5387.53093650195</v>
+        <v>5386.28125153158</v>
       </c>
       <c r="N91" s="14" t="n">
-        <v>5387.53093650195</v>
+        <v>5386.28125153158</v>
       </c>
       <c r="O91" s="15" t="n">
-        <v>0.0218057208020231</v>
+        <v>0.0216962420352326</v>
       </c>
       <c r="P91" s="16" t="n">
-        <v>0.157274163278498</v>
+        <v>0.157114969004416</v>
       </c>
       <c r="Q91" s="17" t="n">
-        <v>0.0220452030585978</v>
+        <v>0.0219333169348519</v>
       </c>
       <c r="R91" s="18" t="n">
-        <v>1.00039357960504</v>
+        <v>1.00050554621836</v>
       </c>
       <c r="S91" s="19" t="n">
-        <v>1.01360148413981</v>
+        <v>1.01328208493227</v>
       </c>
     </row>
     <row r="92">
@@ -6951,46 +6951,46 @@
         <v>5446.86304040468</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>0.968274409445036</v>
+        <v>0.968110900318167</v>
       </c>
       <c r="G92" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>5537.48288302973</v>
+        <v>5538.81333099249</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>5338.12619696462</v>
+        <v>5338.81711276227</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v>5658.84696315708</v>
+        <v>5657.7460101845</v>
       </c>
       <c r="K92" s="11" t="n">
-        <v>5625.32995530321</v>
+        <v>5626.28004561728</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>5625.32995530321</v>
+        <v>5626.28004561728</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>5562.21907063249</v>
+        <v>5563.32590033218</v>
       </c>
       <c r="N92" s="14" t="n">
-        <v>5562.21907063249</v>
+        <v>5563.32590033218</v>
       </c>
       <c r="O92" s="15" t="n">
-        <v>0.0319099443735</v>
+        <v>0.0323409009094382</v>
       </c>
       <c r="P92" s="16" t="n">
-        <v>0.134519959418892</v>
+        <v>0.134669017315464</v>
       </c>
       <c r="Q92" s="17" t="n">
-        <v>0.0324245254810469</v>
+        <v>0.0328695514647064</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>1.00446704542935</v>
+        <v>1.00442559946957</v>
       </c>
       <c r="S92" s="19" t="n">
-        <v>1.04197968826501</v>
+        <v>1.04205215927574</v>
       </c>
     </row>
     <row r="93">
@@ -7010,46 +7010,46 @@
         <v>5439.60580468164</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>0.955033180946305</v>
+        <v>0.953962719057138</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>0.983590334413217</v>
+        <v>1</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>5793.76042201327</v>
+        <v>5795.45395931855</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>5350.10691128517</v>
+        <v>5351.0903121909</v>
       </c>
       <c r="J93" s="10" t="n">
-        <v>5763.90475610829</v>
+        <v>5762.88080090179</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>5695.72441377561</v>
+        <v>5702.1157074754</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>5697.33315188625</v>
+        <v>5702.1157074754</v>
       </c>
       <c r="M93" s="13" t="n">
-        <v>5784.80994357202</v>
+        <v>5786.35730588156</v>
       </c>
       <c r="N93" s="14" t="n">
-        <v>5784.80994357202</v>
+        <v>5786.35730588156</v>
       </c>
       <c r="O93" s="15" t="n">
-        <v>0.0392383647298131</v>
+        <v>0.0393068452348065</v>
       </c>
       <c r="P93" s="16" t="n">
-        <v>0.127484984863543</v>
+        <v>0.127599262303453</v>
       </c>
       <c r="Q93" s="17" t="n">
-        <v>0.0400183578016147</v>
+        <v>0.0400895812226394</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>0.998455152131034</v>
+        <v>0.998430381208989</v>
       </c>
       <c r="S93" s="19" t="n">
-        <v>1.08125127955292</v>
+        <v>1.08134173940197</v>
       </c>
     </row>
     <row r="94">
@@ -7069,46 +7069,46 @@
         <v>7098.31965039088</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>1.15999953797304</v>
+        <v>1.16082013291982</v>
       </c>
       <c r="G94" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>6027.61068200696</v>
+        <v>6023.70576122433</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>5349.69947518801</v>
+        <v>5351.02128870782</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v>5844.23454895117</v>
+        <v>5843.40381371658</v>
       </c>
       <c r="K94" s="11" t="n">
-        <v>6119.24351521238</v>
+        <v>6114.91776295818</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>6119.24351521238</v>
+        <v>6114.91776295818</v>
       </c>
       <c r="M94" s="13" t="n">
-        <v>6031.37306328933</v>
+        <v>6028.56058092293</v>
       </c>
       <c r="N94" s="14" t="n">
-        <v>6031.37306328933</v>
+        <v>6028.56058092293</v>
       </c>
       <c r="O94" s="15" t="n">
-        <v>0.041739183382109</v>
+        <v>0.0410053144422218</v>
       </c>
       <c r="P94" s="16" t="n">
-        <v>0.144185709529144</v>
+        <v>0.14379227951631</v>
       </c>
       <c r="Q94" s="17" t="n">
-        <v>0.0426225100085238</v>
+        <v>0.0418576424230108</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>1.00062419115647</v>
+        <v>1.00080595233085</v>
       </c>
       <c r="S94" s="19" t="n">
-        <v>1.12742278164651</v>
+        <v>1.12661868747278</v>
       </c>
     </row>
     <row r="95">
@@ -7128,46 +7128,46 @@
         <v>5694.02546550393</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>0.919923608283402</v>
+        <v>0.921021896629531</v>
       </c>
       <c r="G95" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H95" s="8" t="n">
-        <v>6259.15603029203</v>
+        <v>6254.91541155322</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>5335.64239678209</v>
+        <v>5337.35315828349</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v>5891.38544918226</v>
+        <v>5890.92269109017</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>6189.6720708463</v>
+        <v>6182.29109029996</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>6189.6720708463</v>
+        <v>6182.29109029996</v>
       </c>
       <c r="M95" s="13" t="n">
-        <v>6239.6902674079</v>
+        <v>6235.89027658375</v>
       </c>
       <c r="N95" s="14" t="n">
-        <v>6239.6902674079</v>
+        <v>6235.89027658375</v>
       </c>
       <c r="O95" s="15" t="n">
-        <v>0.0339558543431039</v>
+        <v>0.0338130832689147</v>
       </c>
       <c r="P95" s="16" t="n">
-        <v>0.158172517420244</v>
+        <v>0.157735733686499</v>
       </c>
       <c r="Q95" s="17" t="n">
-        <v>0.0345389353191439</v>
+        <v>0.0343912436273595</v>
       </c>
       <c r="R95" s="18" t="n">
-        <v>0.996890033929508</v>
+        <v>0.996958370542576</v>
       </c>
       <c r="S95" s="19" t="n">
-        <v>1.16943561869346</v>
+        <v>1.16834882228202</v>
       </c>
     </row>
     <row r="96">
@@ -7187,46 +7187,46 @@
         <v>6209.22803193611</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>0.961155008579776</v>
+        <v>0.960576930752417</v>
       </c>
       <c r="G96" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>6403.11370547992</v>
+        <v>6403.85863792402</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>5307.15514920135</v>
+        <v>5309.30647218475</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>5898.28160912942</v>
+        <v>5898.40264523003</v>
       </c>
       <c r="K96" s="11" t="n">
-        <v>6460.17341272664</v>
+        <v>6464.06116277688</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>6460.17341272664</v>
+        <v>6464.06116277688</v>
       </c>
       <c r="M96" s="13" t="n">
-        <v>6405.88314691533</v>
+        <v>6405.49045688812</v>
       </c>
       <c r="N96" s="14" t="n">
-        <v>6405.88314691533</v>
+        <v>6405.49045688812</v>
       </c>
       <c r="O96" s="15" t="n">
-        <v>0.026286265311183</v>
+        <v>0.0268341506013583</v>
       </c>
       <c r="P96" s="16" t="n">
-        <v>0.15167760664754</v>
+        <v>0.15137789366351</v>
       </c>
       <c r="Q96" s="17" t="n">
-        <v>0.0266347963416558</v>
+        <v>0.0271974285598373</v>
       </c>
       <c r="R96" s="18" t="n">
-        <v>1.0004325147987</v>
+        <v>1.00025481808022</v>
       </c>
       <c r="S96" s="19" t="n">
-        <v>1.20702767618906</v>
+        <v>1.20646462780897</v>
       </c>
     </row>
     <row r="97">
@@ -7246,46 +7246,46 @@
         <v>6200.06740637572</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>0.960592996360505</v>
+        <v>0.957356014586085</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>0.625562239791223</v>
+        <v>0.728032346993902</v>
       </c>
       <c r="H97" s="8" t="n">
-        <v>6612.24543425963</v>
+        <v>6606.06552339389</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>5263.99097412609</v>
+        <v>5266.62986788596</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>5859.3386142288</v>
+        <v>5860.26573033972</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>6454.41662584106</v>
+        <v>6476.24009450271</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>6513.51369136173</v>
+        <v>6511.54841169875</v>
       </c>
       <c r="M97" s="13" t="n">
-        <v>6570.42485931662</v>
+        <v>6565.21402934404</v>
       </c>
       <c r="N97" s="14" t="n">
-        <v>6570.42485931662</v>
+        <v>6565.21402934404</v>
       </c>
       <c r="O97" s="15" t="n">
-        <v>0.0253616871411468</v>
+        <v>0.0246296023166415</v>
       </c>
       <c r="P97" s="16" t="n">
-        <v>0.13580652146015</v>
+        <v>0.134602251864193</v>
       </c>
       <c r="Q97" s="17" t="n">
-        <v>0.0256860308918576</v>
+        <v>0.02493541650416</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>0.993675283932093</v>
+        <v>0.99381606284328</v>
       </c>
       <c r="S97" s="19" t="n">
-        <v>1.24818315449476</v>
+        <v>1.24656833573523</v>
       </c>
     </row>
     <row r="98">
@@ -7305,46 +7305,46 @@
         <v>7870.36784763967</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>1.15834416379185</v>
+        <v>1.16190117941428</v>
       </c>
       <c r="G98" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>6763.72748465009</v>
+        <v>6749.42291573928</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>5206.62374965123</v>
+        <v>5209.79370454309</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>5771.78150893455</v>
+        <v>5773.76229321051</v>
       </c>
       <c r="K98" s="11" t="n">
-        <v>6794.4986418164</v>
+        <v>6773.6981312018</v>
       </c>
       <c r="L98" s="12" t="n">
-        <v>6794.4986418164</v>
+        <v>6773.6981312018</v>
       </c>
       <c r="M98" s="13" t="n">
-        <v>6666.9011257825</v>
+        <v>6654.80314926119</v>
       </c>
       <c r="N98" s="14" t="n">
-        <v>6666.9011257825</v>
+        <v>6654.80314926119</v>
       </c>
       <c r="O98" s="15" t="n">
-        <v>0.0145766561664667</v>
+        <v>0.0135537632358947</v>
       </c>
       <c r="P98" s="16" t="n">
-        <v>0.105370378489997</v>
+        <v>0.103879285931035</v>
       </c>
       <c r="Q98" s="17" t="n">
-        <v>0.0146834137109222</v>
+        <v>0.0136460318759932</v>
       </c>
       <c r="R98" s="18" t="n">
-        <v>0.98568446776022</v>
+        <v>0.985981058283155</v>
       </c>
       <c r="S98" s="19" t="n">
-        <v>1.28046531617136</v>
+        <v>1.277364042929</v>
       </c>
     </row>
     <row r="99">
@@ -7364,46 +7364,46 @@
         <v>6054.57948367958</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>0.922238115532091</v>
+        <v>0.922916495911036</v>
       </c>
       <c r="G99" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H99" s="8" t="n">
-        <v>6454.63253568105</v>
+        <v>6442.61308790661</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>5136.30830557002</v>
+        <v>5140.046415402</v>
       </c>
       <c r="J99" s="10" t="n">
-        <v>5636.1062130865</v>
+        <v>5639.39909404048</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>6565.09352813547</v>
+        <v>6560.26792294241</v>
       </c>
       <c r="L99" s="12" t="n">
-        <v>6565.09352813547</v>
+        <v>6560.26792294241</v>
       </c>
       <c r="M99" s="13" t="n">
-        <v>6378.99097040669</v>
+        <v>6370.89462276965</v>
       </c>
       <c r="N99" s="14" t="n">
-        <v>6378.99097040669</v>
+        <v>6370.89462276965</v>
       </c>
       <c r="O99" s="15" t="n">
-        <v>-0.0441452233946548</v>
+        <v>-0.0435989691770592</v>
       </c>
       <c r="P99" s="16" t="n">
-        <v>0.0223249387435782</v>
+        <v>0.0216495705020421</v>
       </c>
       <c r="Q99" s="17" t="n">
-        <v>-0.0431850045386741</v>
+        <v>-0.0426621975321787</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>0.988281042358923</v>
+        <v>0.988868109234809</v>
       </c>
       <c r="S99" s="19" t="n">
-        <v>1.24194082420813</v>
+        <v>1.23946246938149</v>
       </c>
     </row>
     <row r="100">
@@ -7423,46 +7423,46 @@
         <v>5310.71118746629</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>0.949820597927123</v>
+        <v>0.950149194448802</v>
       </c>
       <c r="G100" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>5697.05493295268</v>
+        <v>5710.1091081212</v>
       </c>
       <c r="I100" s="9" t="n">
-        <v>5055.2918934833</v>
+        <v>5059.61387397524</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>5457.92223218886</v>
+        <v>5462.68257221763</v>
       </c>
       <c r="K100" s="11" t="n">
-        <v>5591.27818353942</v>
+        <v>5589.34451399195</v>
       </c>
       <c r="L100" s="12" t="n">
-        <v>5591.27818353942</v>
+        <v>5589.34451399195</v>
       </c>
       <c r="M100" s="13" t="n">
-        <v>5717.45516853459</v>
+        <v>5725.22185769866</v>
       </c>
       <c r="N100" s="14" t="n">
-        <v>5717.45516853459</v>
+        <v>5725.22185769866</v>
       </c>
       <c r="O100" s="15" t="n">
-        <v>-0.109486123951964</v>
+        <v>-0.106858601731916</v>
       </c>
       <c r="P100" s="16" t="n">
-        <v>-0.107468082478563</v>
+        <v>-0.106200860616057</v>
       </c>
       <c r="Q100" s="17" t="n">
-        <v>-0.103705398697236</v>
+        <v>-0.101347268052958</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>1.00358083884077</v>
+        <v>1.00264666564006</v>
       </c>
       <c r="S100" s="19" t="n">
-        <v>1.1309841823189</v>
+        <v>1.13155311853876</v>
       </c>
     </row>
     <row r="101">
@@ -7482,46 +7482,46 @@
         <v>5041.77244509139</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>0.984303855278804</v>
+        <v>0.976722267910126</v>
       </c>
       <c r="G101" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H101" s="8" t="n">
-        <v>5113.8924063044</v>
+        <v>5126.68487591752</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>4966.71475575602</v>
+        <v>4971.60959221753</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v>5247.48400832109</v>
+        <v>5253.7235112745</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>5122.17077892406</v>
+        <v>5161.93047986832</v>
       </c>
       <c r="L101" s="12" t="n">
-        <v>5122.17077892406</v>
+        <v>5161.93047986832</v>
       </c>
       <c r="M101" s="13" t="n">
-        <v>5200.48265983139</v>
+        <v>5211.88377791921</v>
       </c>
       <c r="N101" s="14" t="n">
-        <v>5200.48265983139</v>
+        <v>5211.88377791921</v>
       </c>
       <c r="O101" s="15" t="n">
-        <v>-0.0947723653099372</v>
+        <v>-0.0939399410529781</v>
       </c>
       <c r="P101" s="16" t="n">
-        <v>-0.208501311379082</v>
+        <v>-0.206136501472146</v>
       </c>
       <c r="Q101" s="17" t="n">
-        <v>-0.0904200371431518</v>
+        <v>-0.0896625654932778</v>
       </c>
       <c r="R101" s="18" t="n">
-        <v>1.01693235732145</v>
+        <v>1.01661871249429</v>
       </c>
       <c r="S101" s="19" t="n">
-        <v>1.04706690751758</v>
+        <v>1.04832925458946</v>
       </c>
     </row>
     <row r="102">
@@ -7541,46 +7541,46 @@
         <v>5651.60509658883</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>1.13798858201474</v>
+        <v>1.14536431719605</v>
       </c>
       <c r="G102" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>4985.06220429754</v>
+        <v>4978.83814186341</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>4874.05212618438</v>
+        <v>4879.47816373363</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v>5015.71276331943</v>
+        <v>5023.2660044525</v>
       </c>
       <c r="K102" s="11" t="n">
-        <v>4966.31089793801</v>
+        <v>4934.32963794825</v>
       </c>
       <c r="L102" s="12" t="n">
-        <v>4966.31089793801</v>
+        <v>4934.32963794825</v>
       </c>
       <c r="M102" s="13" t="n">
-        <v>5024.94356248638</v>
+        <v>5018.36177998537</v>
       </c>
       <c r="N102" s="14" t="n">
-        <v>5024.94356248638</v>
+        <v>5018.36177998537</v>
       </c>
       <c r="O102" s="15" t="n">
-        <v>-0.0343372179422177</v>
+        <v>-0.0378378182776554</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>-0.246284972930869</v>
+        <v>-0.245903797989501</v>
       </c>
       <c r="Q102" s="17" t="n">
-        <v>-0.0337543856651766</v>
+        <v>-0.0371309120041624</v>
       </c>
       <c r="R102" s="18" t="n">
-        <v>1.00800017262662</v>
+        <v>1.0079383255683</v>
       </c>
       <c r="S102" s="19" t="n">
-        <v>1.030958108858</v>
+        <v>1.02846280106016</v>
       </c>
     </row>
     <row r="103">
@@ -7600,46 +7600,46 @@
         <v>4665.68219017201</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>0.924816479147573</v>
+        <v>0.925206059428922</v>
       </c>
       <c r="G103" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H103" s="8" t="n">
-        <v>5048.00274328818</v>
+        <v>5028.71327006441</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>4780.87639857909</v>
+        <v>4786.78313268305</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>4772.90315287311</v>
+        <v>4781.59517983601</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>5044.98167514542</v>
+        <v>5042.85736417667</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>5044.98167514542</v>
+        <v>5042.85736417667</v>
       </c>
       <c r="M103" s="13" t="n">
-        <v>5020.09138977743</v>
+        <v>5009.42749163177</v>
       </c>
       <c r="N103" s="14" t="n">
-        <v>5020.09138977743</v>
+        <v>5009.42749163177</v>
       </c>
       <c r="O103" s="15" t="n">
-        <v>-0.00096608386320076</v>
+        <v>-0.00178190635554926</v>
       </c>
       <c r="P103" s="16" t="n">
-        <v>-0.213027356040077</v>
+        <v>-0.213701090938151</v>
       </c>
       <c r="Q103" s="17" t="n">
-        <v>-0.000965617354426351</v>
+        <v>-0.00178031970298131</v>
       </c>
       <c r="R103" s="18" t="n">
-        <v>0.994470812531181</v>
+        <v>0.996164868148788</v>
       </c>
       <c r="S103" s="19" t="n">
-        <v>1.05003580332456</v>
+        <v>1.04651231375588</v>
       </c>
     </row>
     <row r="104">
@@ -7659,46 +7659,46 @@
         <v>4755.00405694119</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>0.946440612383599</v>
+        <v>0.947652640847067</v>
       </c>
       <c r="G104" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>4974.33525124538</v>
+        <v>4978.70927609164</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>4690.81762848321</v>
+        <v>4697.12232539672</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v>4529.10282334445</v>
+        <v>4538.55148367689</v>
       </c>
       <c r="K104" s="11" t="n">
-        <v>5024.09131088085</v>
+        <v>5017.66560022551</v>
       </c>
       <c r="L104" s="12" t="n">
-        <v>5024.09131088085</v>
+        <v>5017.66560022551</v>
       </c>
       <c r="M104" s="13" t="n">
-        <v>4905.39205787234</v>
+        <v>4914.93098590942</v>
       </c>
       <c r="N104" s="14" t="n">
-        <v>4905.39205787234</v>
+        <v>4914.93098590942</v>
       </c>
       <c r="O104" s="15" t="n">
-        <v>-0.0231131186005944</v>
+        <v>-0.0190439234631884</v>
       </c>
       <c r="P104" s="16" t="n">
-        <v>-0.142032265531587</v>
+        <v>-0.1415300388228</v>
       </c>
       <c r="Q104" s="17" t="n">
-        <v>-0.0228480565391002</v>
+        <v>-0.0188637336063263</v>
       </c>
       <c r="R104" s="18" t="n">
-        <v>0.986140219769912</v>
+        <v>0.987189794252802</v>
       </c>
       <c r="S104" s="19" t="n">
-        <v>1.04574350281414</v>
+        <v>1.04637065961324</v>
       </c>
     </row>
     <row r="105">
@@ -7718,46 +7718,46 @@
         <v>4573.30287832837</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>1.00991495997149</v>
+        <v>0.998203113148627</v>
       </c>
       <c r="G105" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H105" s="8" t="n">
-        <v>4557.18972639108</v>
+        <v>4620.9802064394</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>4607.67093723763</v>
+        <v>4614.25361460023</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>4295.71981370716</v>
+        <v>4305.28167314868</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>4528.40393458224</v>
+        <v>4581.53537901001</v>
       </c>
       <c r="L105" s="12" t="n">
-        <v>4528.40393458224</v>
+        <v>4581.53537901001</v>
       </c>
       <c r="M105" s="13" t="n">
-        <v>4485.7131869586</v>
+        <v>4552.35712366993</v>
       </c>
       <c r="N105" s="14" t="n">
-        <v>4485.7131869586</v>
+        <v>4552.35712366993</v>
       </c>
       <c r="O105" s="15" t="n">
-        <v>-0.0894375211589477</v>
+        <v>-0.0766325639965777</v>
       </c>
       <c r="P105" s="16" t="n">
-        <v>-0.137442910519379</v>
+        <v>-0.126542855203995</v>
       </c>
       <c r="Q105" s="17" t="n">
-        <v>-0.0855546031718759</v>
+        <v>-0.0737698786165984</v>
       </c>
       <c r="R105" s="18" t="n">
-        <v>0.984315654224674</v>
+        <v>0.985149669614718</v>
       </c>
       <c r="S105" s="19" t="n">
-        <v>0.973531584190744</v>
+        <v>0.986585806481367</v>
       </c>
     </row>
     <row r="106">
@@ -7777,46 +7777,46 @@
         <v>4670.88465711875</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>1.10940329517855</v>
+        <v>1.12039712922521</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>0.158793815968157</v>
+        <v>0.496050501651822</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>3796.20262322254</v>
+        <v>3890.62826780361</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>4535.43974223477</v>
+        <v>4542.13521256594</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>4086.63710537261</v>
+        <v>4095.3280760077</v>
       </c>
       <c r="K106" s="11" t="n">
-        <v>4210.26751715841</v>
+        <v>4168.95450307769</v>
       </c>
       <c r="L106" s="12" t="n">
-        <v>3861.95356778907</v>
+        <v>4028.69213643418</v>
       </c>
       <c r="M106" s="13" t="n">
-        <v>3810.95618825631</v>
+        <v>3920.56059610933</v>
       </c>
       <c r="N106" s="14" t="n">
-        <v>3810.95618825631</v>
+        <v>3920.56059610933</v>
       </c>
       <c r="O106" s="15" t="n">
-        <v>-0.163017373215655</v>
+        <v>-0.149410495190852</v>
       </c>
       <c r="P106" s="16" t="n">
-        <v>-0.241592240616006</v>
+        <v>-0.218756883621737</v>
       </c>
       <c r="Q106" s="17" t="n">
-        <v>-0.15042357158813</v>
+        <v>-0.138784482499313</v>
       </c>
       <c r="R106" s="18" t="n">
-        <v>1.00388640083212</v>
+        <v>1.00769344338379</v>
       </c>
       <c r="S106" s="19" t="n">
-        <v>0.840261673585486</v>
+        <v>0.863153651891075</v>
       </c>
     </row>
     <row r="107">
@@ -7836,46 +7836,46 @@
         <v>2175.26624692192</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>0.929205561572338</v>
+        <v>0.928461838199844</v>
       </c>
       <c r="G107" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="8" t="n">
-        <v>2991.51368286488</v>
+        <v>3043.32273255897</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>4478.07791899037</v>
+        <v>4484.70488266898</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>3916.90110035653</v>
+        <v>3923.61428853955</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>2340.99572460703</v>
+        <v>2342.87092632633</v>
       </c>
       <c r="L107" s="12" t="n">
-        <v>2991.51368286488</v>
+        <v>3043.32273255897</v>
       </c>
       <c r="M107" s="13" t="n">
-        <v>3091.61914926731</v>
+        <v>3157.6667754024</v>
       </c>
       <c r="N107" s="14" t="n">
-        <v>3091.61914926731</v>
+        <v>3157.6667754024</v>
       </c>
       <c r="O107" s="15" t="n">
-        <v>-0.209185175499624</v>
+        <v>-0.216401260128338</v>
       </c>
       <c r="P107" s="16" t="n">
-        <v>-0.384150823317107</v>
+        <v>-0.369655159062135</v>
       </c>
       <c r="Q107" s="17" t="n">
-        <v>-0.188755000964243</v>
+        <v>-0.194587942720235</v>
       </c>
       <c r="R107" s="18" t="n">
-        <v>1.03346314843078</v>
+        <v>1.03757210552142</v>
       </c>
       <c r="S107" s="19" t="n">
-        <v>0.690389762124628</v>
+        <v>0.704096893332962</v>
       </c>
     </row>
     <row r="108">
@@ -7895,46 +7895,46 @@
         <v>2405.16348217783</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>0.953863818584259</v>
+        <v>0.956202152490509</v>
       </c>
       <c r="G108" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>2556.69765786709</v>
+        <v>2523.66070974813</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>4439.11841416111</v>
+        <v>4445.5794863619</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>3800.43478298677</v>
+        <v>3804.73072733198</v>
       </c>
       <c r="K108" s="11" t="n">
-        <v>2521.4956635504</v>
+        <v>2515.32950005748</v>
       </c>
       <c r="L108" s="12" t="n">
-        <v>2521.4956635504</v>
+        <v>2515.32950005748</v>
       </c>
       <c r="M108" s="13" t="n">
-        <v>2657.27376985177</v>
+        <v>2628.10691579873</v>
       </c>
       <c r="N108" s="14" t="n">
-        <v>2657.27376985177</v>
+        <v>2628.10691579873</v>
       </c>
       <c r="O108" s="15" t="n">
-        <v>-0.151394251524063</v>
+        <v>-0.183569609533085</v>
       </c>
       <c r="P108" s="16" t="n">
-        <v>-0.458295333277738</v>
+        <v>-0.465281013439816</v>
       </c>
       <c r="Q108" s="17" t="n">
-        <v>-0.140491230790337</v>
+        <v>-0.16770606187101</v>
       </c>
       <c r="R108" s="18" t="n">
-        <v>1.03933828924793</v>
+        <v>1.04138678612666</v>
       </c>
       <c r="S108" s="19" t="n">
-        <v>0.598603939326077</v>
+        <v>0.591173079653893</v>
       </c>
     </row>
     <row r="109">
@@ -7954,46 +7954,46 @@
         <v>2776.70598703957</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>1.01949645209296</v>
+        <v>1.00701032459566</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>0.41691341074077</v>
+        <v>0.0323632386211981</v>
       </c>
       <c r="H109" s="8" t="n">
-        <v>2502.34270869943</v>
+        <v>2427.77911142296</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>4421.16507175617</v>
+        <v>4427.47502125339</v>
       </c>
       <c r="J109" s="10" t="n">
-        <v>3746.53420050369</v>
+        <v>3748.86635119281</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>2723.60534589323</v>
+        <v>2757.37588703918</v>
       </c>
       <c r="L109" s="12" t="n">
-        <v>2594.59006944139</v>
+        <v>2438.44593052101</v>
       </c>
       <c r="M109" s="13" t="n">
-        <v>2568.81962096975</v>
+        <v>2475.32470479515</v>
       </c>
       <c r="N109" s="14" t="n">
-        <v>2568.81962096975</v>
+        <v>2475.32470479515</v>
       </c>
       <c r="O109" s="15" t="n">
-        <v>-0.0338541967249447</v>
+        <v>-0.0598922018555522</v>
       </c>
       <c r="P109" s="16" t="n">
-        <v>-0.42733306524409</v>
+        <v>-0.456254279365578</v>
       </c>
       <c r="Q109" s="17" t="n">
-        <v>-0.0332875557970667</v>
+        <v>-0.0581339404744684</v>
       </c>
       <c r="R109" s="18" t="n">
-        <v>1.02656587046978</v>
+        <v>1.01958398651199</v>
       </c>
       <c r="S109" s="19" t="n">
-        <v>0.581027756095378</v>
+        <v>0.559082703552871</v>
       </c>
     </row>
     <row r="110">
@@ -8013,46 +8013,46 @@
         <v>2640.35379506736</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>1.08515231270291</v>
+        <v>1.09526481034905</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>0.424067990537546</v>
+        <v>0.496024245864342</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>2661.38292220947</v>
+        <v>2605.9037332208</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>4425.62322156551</v>
+        <v>4431.90107871074</v>
       </c>
       <c r="J110" s="10" t="n">
-        <v>3758.10070455048</v>
+        <v>3759.76311279351</v>
       </c>
       <c r="K110" s="11" t="n">
-        <v>2433.16423340677</v>
+        <v>2410.69901097791</v>
       </c>
       <c r="L110" s="12" t="n">
-        <v>2564.6026814458</v>
+        <v>2509.07745808111</v>
       </c>
       <c r="M110" s="13" t="n">
-        <v>2700.78009197382</v>
+        <v>2633.93666191386</v>
       </c>
       <c r="N110" s="14" t="n">
-        <v>2700.78009197382</v>
+        <v>2633.93666191386</v>
       </c>
       <c r="O110" s="15" t="n">
-        <v>0.050094152284308</v>
+        <v>0.0621079754097625</v>
       </c>
       <c r="P110" s="16" t="n">
-        <v>-0.291311692247623</v>
+        <v>-0.328173459548689</v>
       </c>
       <c r="Q110" s="17" t="n">
-        <v>0.0513700806108977</v>
+        <v>0.0640772327006038</v>
       </c>
       <c r="R110" s="18" t="n">
-        <v>1.01480326992241</v>
+        <v>1.01075746902531</v>
       </c>
       <c r="S110" s="19" t="n">
-        <v>0.610259833872268</v>
+        <v>0.594313053277824</v>
       </c>
     </row>
     <row r="111">
@@ -8072,46 +8072,46 @@
         <v>2885.42830497867</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>0.93703274755309</v>
+        <v>0.937087261040908</v>
       </c>
       <c r="G111" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H111" s="8" t="n">
-        <v>3019.76460175172</v>
+        <v>3010.2754621773</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>4452.75658400268</v>
+        <v>4459.1241069195</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>3832.27592611502</v>
+        <v>3834.61086270218</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>3079.32493556228</v>
+        <v>3079.14580097222</v>
       </c>
       <c r="L111" s="12" t="n">
-        <v>3079.32493556228</v>
+        <v>3079.14580097222</v>
       </c>
       <c r="M111" s="13" t="n">
-        <v>3068.57371415761</v>
+        <v>3053.8732642964</v>
       </c>
       <c r="N111" s="14" t="n">
-        <v>3068.57371415761</v>
+        <v>3053.8732642964</v>
       </c>
       <c r="O111" s="15" t="n">
-        <v>0.127672211188933</v>
+        <v>0.147931150987733</v>
       </c>
       <c r="P111" s="16" t="n">
-        <v>-0.00745416365892237</v>
+        <v>-0.0328703180191554</v>
       </c>
       <c r="Q111" s="17" t="n">
-        <v>0.136180514391676</v>
+        <v>0.15943306779344</v>
       </c>
       <c r="R111" s="18" t="n">
-        <v>1.01616321761556</v>
+        <v>1.01448299421993</v>
       </c>
       <c r="S111" s="19" t="n">
-        <v>0.689140233980453</v>
+        <v>0.684859445727809</v>
       </c>
     </row>
     <row r="112">
@@ -8131,46 +8131,46 @@
         <v>3444.49013745048</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>0.969994115111563</v>
+        <v>0.970791928412725</v>
       </c>
       <c r="G112" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>3616.31028079975</v>
+        <v>3630.00058270531</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>4501.6657416437</v>
+        <v>4508.20878930236</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>3960.23400606968</v>
+        <v>3964.34602321338</v>
       </c>
       <c r="K112" s="11" t="n">
-        <v>3551.04230406007</v>
+        <v>3548.12399716006</v>
       </c>
       <c r="L112" s="12" t="n">
-        <v>3551.04230406007</v>
+        <v>3548.12399716006</v>
       </c>
       <c r="M112" s="13" t="n">
-        <v>3616.39505779704</v>
+        <v>3623.36745397481</v>
       </c>
       <c r="N112" s="14" t="n">
-        <v>3616.39505779704</v>
+        <v>3623.36745397481</v>
       </c>
       <c r="O112" s="15" t="n">
-        <v>0.164264823849362</v>
+        <v>0.170993121671425</v>
       </c>
       <c r="P112" s="16" t="n">
-        <v>0.36094184153211</v>
+        <v>0.378698648899372</v>
       </c>
       <c r="Q112" s="17" t="n">
-        <v>0.178526375661735</v>
+        <v>0.186482587976556</v>
       </c>
       <c r="R112" s="18" t="n">
-        <v>1.00002344295448</v>
+        <v>0.998172692103107</v>
       </c>
       <c r="S112" s="19" t="n">
-        <v>0.803345975766868</v>
+        <v>0.803726629204216</v>
       </c>
     </row>
     <row r="113">
@@ -8190,46 +8190,46 @@
         <v>4318.55493831423</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>1.00802588256084</v>
+        <v>1.00011090997589</v>
       </c>
       <c r="G113" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H113" s="8" t="n">
-        <v>4184.96816539866</v>
+        <v>4195.16526455592</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>4570.59288228426</v>
+        <v>4577.35732284081</v>
       </c>
       <c r="J113" s="10" t="n">
-        <v>4129.38433033404</v>
+        <v>4136.12769131298</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>4284.17068750572</v>
+        <v>4318.0760206069</v>
       </c>
       <c r="L113" s="12" t="n">
-        <v>4284.17068750572</v>
+        <v>4318.0760206069</v>
       </c>
       <c r="M113" s="13" t="n">
-        <v>4199.10334955308</v>
+        <v>4208.45185312498</v>
       </c>
       <c r="N113" s="14" t="n">
-        <v>4199.10334955308</v>
+        <v>4208.45185312498</v>
       </c>
       <c r="O113" s="15" t="n">
-        <v>0.149393325024179</v>
+        <v>0.149691019874508</v>
       </c>
       <c r="P113" s="16" t="n">
-        <v>0.634643131528203</v>
+        <v>0.700161536372359</v>
       </c>
       <c r="Q113" s="17" t="n">
-        <v>0.161129600733113</v>
+        <v>0.161475314491865</v>
       </c>
       <c r="R113" s="18" t="n">
-        <v>1.00337760852551</v>
+        <v>1.00316711922682</v>
       </c>
       <c r="S113" s="19" t="n">
-        <v>0.918721806492308</v>
+        <v>0.919406451431046</v>
       </c>
     </row>
     <row r="114">
@@ -8249,46 +8249,46 @@
         <v>5038.84746379941</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>1.07736058276001</v>
+        <v>1.08373232877615</v>
       </c>
       <c r="G114" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>4798.38994261553</v>
+        <v>4791.75322792124</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>4657.18605407159</v>
+        <v>4664.1718515212</v>
       </c>
       <c r="J114" s="10" t="n">
-        <v>4325.09032631765</v>
+        <v>4335.03385385663</v>
       </c>
       <c r="K114" s="11" t="n">
-        <v>4677.02971914079</v>
+        <v>4649.53137412606</v>
       </c>
       <c r="L114" s="12" t="n">
-        <v>4677.02971914079</v>
+        <v>4649.53137412606</v>
       </c>
       <c r="M114" s="13" t="n">
-        <v>4779.30325762497</v>
+        <v>4773.52144223532</v>
       </c>
       <c r="N114" s="14" t="n">
-        <v>4779.30325762497</v>
+        <v>4773.52144223532</v>
       </c>
       <c r="O114" s="15" t="n">
-        <v>0.129423759580083</v>
+        <v>0.125989431161879</v>
       </c>
       <c r="P114" s="16" t="n">
-        <v>0.769601039280507</v>
+        <v>0.812314438406731</v>
       </c>
       <c r="Q114" s="17" t="n">
-        <v>0.138172333418192</v>
+        <v>0.134270180301754</v>
       </c>
       <c r="R114" s="18" t="n">
-        <v>0.996022273050165</v>
+        <v>0.996195174329996</v>
       </c>
       <c r="S114" s="19" t="n">
-        <v>1.02622124221269</v>
+        <v>1.02344458870624</v>
       </c>
     </row>
     <row r="115">
@@ -8308,46 +8308,46 @@
         <v>5155.69426033944</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>0.940994770380636</v>
+        <v>0.941344559343373</v>
       </c>
       <c r="G115" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>5429.13578171984</v>
+        <v>5420.90270298966</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>4758.91429128117</v>
+        <v>4766.09246851601</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>4533.48935321589</v>
+        <v>4547.05223934642</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>5478.98290471258</v>
+        <v>5476.94700008226</v>
       </c>
       <c r="L115" s="12" t="n">
-        <v>5478.98290471258</v>
+        <v>5476.94700008226</v>
       </c>
       <c r="M115" s="13" t="n">
-        <v>5355.39465399343</v>
+        <v>5350.31975395624</v>
       </c>
       <c r="N115" s="14" t="n">
-        <v>5355.39465399343</v>
+        <v>5350.31975395624</v>
       </c>
       <c r="O115" s="15" t="n">
-        <v>0.113809625532954</v>
+        <v>0.114072045839132</v>
       </c>
       <c r="P115" s="16" t="n">
-        <v>0.745239043561189</v>
+        <v>0.751978320943496</v>
       </c>
       <c r="Q115" s="17" t="n">
-        <v>0.120538782603794</v>
+        <v>0.120832873320209</v>
       </c>
       <c r="R115" s="18" t="n">
-        <v>0.986417520082165</v>
+        <v>0.986979484248169</v>
       </c>
       <c r="S115" s="19" t="n">
-        <v>1.12533958928512</v>
+        <v>1.12257993089717</v>
       </c>
     </row>
     <row r="116">
@@ -8367,46 +8367,46 @@
         <v>5721.03663102072</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>0.988672683793361</v>
+        <v>0.986750784813992</v>
       </c>
       <c r="G116" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>5646.92409250806</v>
+        <v>5653.8198995903</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>4873.25903047914</v>
+        <v>4880.55011669934</v>
       </c>
       <c r="J116" s="10" t="n">
-        <v>4742.47846718831</v>
+        <v>4759.74306388578</v>
       </c>
       <c r="K116" s="11" t="n">
-        <v>5786.58308740777</v>
+        <v>5797.85364153439</v>
       </c>
       <c r="L116" s="12" t="n">
-        <v>5786.58308740777</v>
+        <v>5797.85364153439</v>
       </c>
       <c r="M116" s="13" t="n">
-        <v>5606.85063291297</v>
+        <v>5611.42656889312</v>
       </c>
       <c r="N116" s="14" t="n">
-        <v>5606.85063291297</v>
+        <v>5611.42656889312</v>
       </c>
       <c r="O116" s="15" t="n">
-        <v>0.0458847779829702</v>
+        <v>0.0476486513470144</v>
       </c>
       <c r="P116" s="16" t="n">
-        <v>0.550397714659094</v>
+        <v>0.548677201573201</v>
       </c>
       <c r="Q116" s="17" t="n">
-        <v>0.0469537718815987</v>
+        <v>0.048802095378282</v>
       </c>
       <c r="R116" s="18" t="n">
-        <v>0.992903488883753</v>
+        <v>0.99250182505809</v>
       </c>
       <c r="S116" s="19" t="n">
-        <v>1.15053408773178</v>
+        <v>1.14975288332621</v>
       </c>
     </row>
     <row r="117">
@@ -8426,46 +8426,46 @@
         <v>5275.14336147936</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>0.981375745062804</v>
+        <v>0.981777836678263</v>
       </c>
       <c r="G117" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H117" s="8" t="n">
-        <v>5622.74363674877</v>
+        <v>5626.23257134936</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>4998.15175111505</v>
+        <v>5005.42002302753</v>
       </c>
       <c r="J117" s="10" t="n">
-        <v>4944.68219215188</v>
+        <v>4965.31601738185</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>5375.25345212376</v>
+        <v>5373.05199242145</v>
       </c>
       <c r="L117" s="12" t="n">
-        <v>5375.25345212376</v>
+        <v>5373.05199242145</v>
       </c>
       <c r="M117" s="13" t="n">
-        <v>5614.88241934517</v>
+        <v>5617.22569083646</v>
       </c>
       <c r="N117" s="14" t="n">
-        <v>5614.88241934517</v>
+        <v>5617.22569083646</v>
       </c>
       <c r="O117" s="15" t="n">
-        <v>0.00143147012431958</v>
+        <v>0.00103291513973272</v>
       </c>
       <c r="P117" s="16" t="n">
-        <v>0.33716223487159</v>
+        <v>0.334748712086464</v>
       </c>
       <c r="Q117" s="17" t="n">
-        <v>0.0014324951667255</v>
+        <v>0.00103344878029499</v>
       </c>
       <c r="R117" s="18" t="n">
-        <v>0.99860188941352</v>
+        <v>0.998399127586945</v>
       </c>
       <c r="S117" s="19" t="n">
-        <v>1.12339174537719</v>
+        <v>1.12222863715618</v>
       </c>
     </row>
     <row r="118">
@@ -8485,46 +8485,46 @@
         <v>6464.88884607211</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>1.09159217976574</v>
+        <v>1.09113058376433</v>
       </c>
       <c r="G118" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>5744.06278909782</v>
+        <v>5740.85003355712</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>5132.09476017401</v>
+        <v>5139.15072915994</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>5137.94557512473</v>
+        <v>5161.17134262999</v>
       </c>
       <c r="K118" s="11" t="n">
-        <v>5922.4396857254</v>
+        <v>5924.94513696854</v>
       </c>
       <c r="L118" s="12" t="n">
-        <v>5922.4396857254</v>
+        <v>5924.94513696854</v>
       </c>
       <c r="M118" s="13" t="n">
-        <v>5738.78492224928</v>
+        <v>5737.7000162805</v>
       </c>
       <c r="N118" s="14" t="n">
-        <v>5738.78492224928</v>
+        <v>5737.7000162805</v>
       </c>
       <c r="O118" s="15" t="n">
-        <v>0.0218268543873866</v>
+        <v>0.0212205433010803</v>
       </c>
       <c r="P118" s="16" t="n">
-        <v>0.200757644556984</v>
+        <v>0.201984758152397</v>
       </c>
       <c r="Q118" s="17" t="n">
-        <v>0.0220668027663808</v>
+        <v>0.0214473001575459</v>
       </c>
       <c r="R118" s="18" t="n">
-        <v>0.999081161358724</v>
+        <v>0.999451297759356</v>
       </c>
       <c r="S118" s="19" t="n">
-        <v>1.11821491816232</v>
+        <v>1.11646852148631</v>
       </c>
     </row>
     <row r="119">
@@ -8544,46 +8544,46 @@
         <v>5373.68391411676</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>0.936996945289762</v>
+        <v>0.938166432008283</v>
       </c>
       <c r="G119" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H119" s="8" t="n">
-        <v>5788.08139283135</v>
+        <v>5791.18602541094</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>5273.82605320429</v>
+        <v>5280.42054673678</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>5322.26651942479</v>
+        <v>5346.74796230076</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>5735.00686542257</v>
+        <v>5727.85779876349</v>
       </c>
       <c r="L119" s="12" t="n">
-        <v>5735.00686542257</v>
+        <v>5727.85779876349</v>
       </c>
       <c r="M119" s="13" t="n">
-        <v>5735.39923357612</v>
+        <v>5735.99385392081</v>
       </c>
       <c r="N119" s="14" t="n">
-        <v>5735.39923357612</v>
+        <v>5735.99385392081</v>
       </c>
       <c r="O119" s="15" t="n">
-        <v>-0.000590140218326868</v>
+        <v>-0.000297404199827523</v>
       </c>
       <c r="P119" s="16" t="n">
-        <v>0.0709573437877868</v>
+        <v>0.072084308546118</v>
       </c>
       <c r="Q119" s="17" t="n">
-        <v>-0.000589966119837415</v>
+        <v>-0.000297359979582357</v>
       </c>
       <c r="R119" s="18" t="n">
-        <v>0.990898165440369</v>
+        <v>0.990469625522656</v>
       </c>
       <c r="S119" s="19" t="n">
-        <v>1.08752150255153</v>
+        <v>1.08627595153677</v>
       </c>
     </row>
     <row r="120">
@@ -8603,46 +8603,46 @@
         <v>5519.15105764071</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>0.994595119049022</v>
+        <v>0.992061634820627</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>5566.27789050784</v>
+        <v>5562.18299070868</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>5422.57759133261</v>
+        <v>5428.39890890316</v>
       </c>
       <c r="J120" s="10" t="n">
-        <v>5501.56539892304</v>
+        <v>5525.30366803642</v>
       </c>
       <c r="K120" s="11" t="n">
-        <v>5549.14351773395</v>
+        <v>5563.31468118774</v>
       </c>
       <c r="L120" s="12" t="n">
-        <v>5549.14351773395</v>
+        <v>5563.31468118774</v>
       </c>
       <c r="M120" s="13" t="n">
-        <v>5552.87688848253</v>
+        <v>5551.21437860507</v>
       </c>
       <c r="N120" s="14" t="n">
-        <v>5552.87688848253</v>
+        <v>5551.21437860507</v>
       </c>
       <c r="O120" s="15" t="n">
-        <v>-0.0323412099429752</v>
+        <v>-0.0327443210250967</v>
       </c>
       <c r="P120" s="16" t="n">
-        <v>-0.00962639241958974</v>
+        <v>-0.0107302821392753</v>
       </c>
       <c r="Q120" s="17" t="n">
-        <v>-0.0318238256240424</v>
+        <v>-0.0322140295163387</v>
       </c>
       <c r="R120" s="18" t="n">
-        <v>0.997592466224482</v>
+        <v>0.998028002292997</v>
       </c>
       <c r="S120" s="19" t="n">
-        <v>1.02402903323286</v>
+        <v>1.02262462132259</v>
       </c>
     </row>
     <row r="121">
@@ -8662,46 +8662,46 @@
         <v>5214.52990895346</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>0.969565406909101</v>
+        <v>0.974611020292353</v>
       </c>
       <c r="G121" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>5291.18806148257</v>
+        <v>5287.15221622173</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>5577.86957369332</v>
+        <v>5582.53489708671</v>
       </c>
       <c r="J121" s="10" t="n">
-        <v>5681.82628922042</v>
+        <v>5702.00180066154</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>5378.21365303964</v>
+        <v>5350.37035328131</v>
       </c>
       <c r="L121" s="12" t="n">
-        <v>5378.21365303964</v>
+        <v>5350.37035328131</v>
       </c>
       <c r="M121" s="13" t="n">
-        <v>5326.94956670071</v>
+        <v>5321.88682958975</v>
       </c>
       <c r="N121" s="14" t="n">
-        <v>5326.94956670071</v>
+        <v>5321.88682958975</v>
       </c>
       <c r="O121" s="15" t="n">
-        <v>-0.041537391338447</v>
+        <v>-0.0421888030893391</v>
       </c>
       <c r="P121" s="16" t="n">
-        <v>-0.0512802995931727</v>
+        <v>-0.0525773535730455</v>
       </c>
       <c r="Q121" s="17" t="n">
-        <v>-0.0406865353435837</v>
+        <v>-0.04131123991521</v>
       </c>
       <c r="R121" s="18" t="n">
-        <v>1.00675869101657</v>
+        <v>1.00656962613285</v>
       </c>
       <c r="S121" s="19" t="n">
-        <v>0.955015081712199</v>
+        <v>0.953310087209133</v>
       </c>
     </row>
     <row r="122">
@@ -8721,46 +8721,46 @@
         <v>5530.3441739009</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>1.10557631313854</v>
+        <v>1.10089639842038</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>5106.56541584403</v>
+        <v>5105.7120640064</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>5739.30130312478</v>
+        <v>5742.36191507272</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>5869.27115651194</v>
+        <v>5882.19575606645</v>
       </c>
       <c r="K122" s="11" t="n">
-        <v>5002.22744298962</v>
+        <v>5023.49193060864</v>
       </c>
       <c r="L122" s="12" t="n">
-        <v>5002.22744298962</v>
+        <v>5023.49193060864</v>
       </c>
       <c r="M122" s="13" t="n">
-        <v>5192.26731843607</v>
+        <v>5193.86789055865</v>
       </c>
       <c r="N122" s="14" t="n">
-        <v>5192.26731843607</v>
+        <v>5193.86789055865</v>
       </c>
       <c r="O122" s="15" t="n">
-        <v>-0.0256082957256804</v>
+        <v>-0.0243492297829269</v>
       </c>
       <c r="P122" s="16" t="n">
-        <v>-0.095232285443275</v>
+        <v>-0.0947822514559405</v>
       </c>
       <c r="Q122" s="17" t="n">
-        <v>-0.0252831844150638</v>
+        <v>-0.0240551787609078</v>
       </c>
       <c r="R122" s="18" t="n">
-        <v>1.01678268965793</v>
+        <v>1.01726611791795</v>
       </c>
       <c r="S122" s="19" t="n">
-        <v>0.904686310093029</v>
+        <v>0.904482853462376</v>
       </c>
     </row>
     <row r="123">
@@ -8780,46 +8780,46 @@
         <v>5009.70362811794</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>0.930065153864444</v>
+        <v>0.931497642056257</v>
       </c>
       <c r="G123" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>5389.18120570663</v>
+        <v>5370.23089987216</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>5906.34729751496</v>
+        <v>5907.26826380662</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>6068.6039038117</v>
+        <v>6069.48077290456</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>5386.40073472541</v>
+        <v>5378.11734773601</v>
       </c>
       <c r="L123" s="12" t="n">
-        <v>5386.40073472541</v>
+        <v>5378.11734773601</v>
       </c>
       <c r="M123" s="13" t="n">
-        <v>5462.4986167625</v>
+        <v>5467.41281333041</v>
       </c>
       <c r="N123" s="14" t="n">
-        <v>5462.4986167625</v>
+        <v>5467.41281333041</v>
       </c>
       <c r="O123" s="15" t="n">
-        <v>0.0507358425193121</v>
+        <v>0.0513268491842704</v>
       </c>
       <c r="P123" s="16" t="n">
-        <v>-0.0475817995748238</v>
+        <v>-0.0468238020176421</v>
       </c>
       <c r="Q123" s="17" t="n">
-        <v>0.0520449510307228</v>
+        <v>0.0526669003786193</v>
       </c>
       <c r="R123" s="18" t="n">
-        <v>1.01360455480291</v>
+        <v>1.01809641247652</v>
       </c>
       <c r="S123" s="19" t="n">
-        <v>0.924852254973357</v>
+        <v>0.925539956739197</v>
       </c>
     </row>
     <row r="124">
@@ -8839,46 +8839,46 @@
         <v>6033.85596798828</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>0.993232951487256</v>
+        <v>0.990793209656172</v>
       </c>
       <c r="G124" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>6002.79876092009</v>
+        <v>6111.75012769553</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>6078.02140358921</v>
+        <v>6076.19295049354</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>6280.19321556619</v>
+        <v>6263.15857070203</v>
       </c>
       <c r="K124" s="11" t="n">
-        <v>6074.96555460957</v>
+        <v>6089.924627241</v>
       </c>
       <c r="L124" s="12" t="n">
-        <v>6074.96555460957</v>
+        <v>6089.924627241</v>
       </c>
       <c r="M124" s="13" t="n">
-        <v>6027.65460156317</v>
+        <v>6117.81787231287</v>
       </c>
       <c r="N124" s="14" t="n">
-        <v>6027.65460156317</v>
+        <v>6117.81787231287</v>
       </c>
       <c r="O124" s="15" t="n">
-        <v>0.0984516729144223</v>
+        <v>0.112399949039653</v>
       </c>
       <c r="P124" s="16" t="n">
-        <v>0.0855012136259317</v>
+        <v>0.102068386314092</v>
       </c>
       <c r="Q124" s="17" t="n">
-        <v>0.103461076047946</v>
+        <v>0.118960298259658</v>
       </c>
       <c r="R124" s="18" t="n">
-        <v>1.0041407086316</v>
+        <v>1.0009927998512</v>
       </c>
       <c r="S124" s="19" t="n">
-        <v>0.991713289789289</v>
+        <v>1.00685049374806</v>
       </c>
     </row>
     <row r="125">
@@ -8898,46 +8898,46 @@
         <v>6342.86762614381</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>0.964799384089659</v>
+        <v>0.972781684428456</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>1</v>
+        <v>0.0372866130238805</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>6703.2719876509</v>
+        <v>6928.52470058822</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>6253.01250147116</v>
+        <v>6247.74426301607</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v>6500.99676037646</v>
+        <v>6459.07405185914</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>6574.28656230813</v>
+        <v>6520.34030623271</v>
       </c>
       <c r="L125" s="12" t="n">
-        <v>6574.28656230813</v>
+        <v>6913.3048870335</v>
       </c>
       <c r="M125" s="13" t="n">
-        <v>6605.2499039907</v>
+        <v>6814.51322450653</v>
       </c>
       <c r="N125" s="14" t="n">
-        <v>6605.2499039907</v>
+        <v>6814.51322450653</v>
       </c>
       <c r="O125" s="15" t="n">
-        <v>0.0915067927243971</v>
+        <v>0.107849159394666</v>
       </c>
       <c r="P125" s="16" t="n">
-        <v>0.23996854509019</v>
+        <v>0.280469397924389</v>
       </c>
       <c r="Q125" s="17" t="n">
-        <v>0.0958242202991761</v>
+        <v>0.113879714423447</v>
       </c>
       <c r="R125" s="18" t="n">
-        <v>0.985376979504818</v>
+        <v>0.983544624431805</v>
       </c>
       <c r="S125" s="19" t="n">
-        <v>1.0563308329284</v>
+        <v>1.09071577478699</v>
       </c>
     </row>
     <row r="126">
@@ -8957,46 +8957,46 @@
         <v>9133.82917570275</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>1.11985936522943</v>
+        <v>1.11139909622694</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>7197.46093673697</v>
+        <v>7341.51849671811</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>6430.00756137883</v>
+        <v>6420.53907155476</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v>6726.9460685388</v>
+        <v>6652.20594905888</v>
       </c>
       <c r="K126" s="11" t="n">
-        <v>8156.22877237935</v>
+        <v>8218.31618066899</v>
       </c>
       <c r="L126" s="12" t="n">
-        <v>7197.46093673697</v>
+        <v>7341.51849671811</v>
       </c>
       <c r="M126" s="13" t="n">
-        <v>7043.64439119317</v>
+        <v>7197.53453661084</v>
       </c>
       <c r="N126" s="14" t="n">
-        <v>7043.64439119317</v>
+        <v>7197.53453661084</v>
       </c>
       <c r="O126" s="15" t="n">
-        <v>0.0642609325928083</v>
+        <v>0.0546839063845197</v>
       </c>
       <c r="P126" s="16" t="n">
-        <v>0.356564282848738</v>
+        <v>0.385775435238627</v>
       </c>
       <c r="Q126" s="17" t="n">
-        <v>0.0663706133113307</v>
+        <v>0.0562067017093584</v>
       </c>
       <c r="R126" s="18" t="n">
-        <v>0.978629054482436</v>
+        <v>0.980387714044222</v>
       </c>
       <c r="S126" s="19" t="n">
-        <v>1.09543329832147</v>
+        <v>1.12101716949258</v>
       </c>
     </row>
     <row r="127">
@@ -9016,46 +9016,46 @@
         <v>6663.08011470637</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>0.924738205000163</v>
+        <v>0.926225857440869</v>
       </c>
       <c r="G127" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>7273.72212643606</v>
+        <v>7257.0129439313</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>6607.89434981824</v>
+        <v>6593.61022168018</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>6954.33911935913</v>
+        <v>6839.80414916011</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>7205.36912899061</v>
+        <v>7193.79626597365</v>
       </c>
       <c r="L127" s="12" t="n">
-        <v>7205.36912899061</v>
+        <v>7193.79626597365</v>
       </c>
       <c r="M127" s="13" t="n">
-        <v>7202.22123054657</v>
+        <v>7183.14038955146</v>
       </c>
       <c r="N127" s="14" t="n">
-        <v>7202.22123054657</v>
+        <v>7183.14038955146</v>
       </c>
       <c r="O127" s="15" t="n">
-        <v>0.0222637772578919</v>
+        <v>-0.00200187431262255</v>
       </c>
       <c r="P127" s="16" t="n">
-        <v>0.318484769670324</v>
+        <v>0.313809773433942</v>
       </c>
       <c r="Q127" s="17" t="n">
-        <v>0.0225134646989948</v>
+        <v>-0.00199987189865736</v>
       </c>
       <c r="R127" s="18" t="n">
-        <v>0.99016997148824</v>
+        <v>0.989820528783593</v>
       </c>
       <c r="S127" s="19" t="n">
-        <v>1.08994194659675</v>
+        <v>1.08940931417706</v>
       </c>
     </row>
     <row r="128">
@@ -9063,92 +9063,118 @@
         <v>177</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>7087.36023836712</v>
+        <v>6896.80805983389</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>7087.36023836712</v>
+        <v>6896.80805983389</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>7087.36023836712</v>
+        <v>6896.80805983389</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>7087.36023836712</v>
+        <v>6896.80805983389</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>0.984261847636445</v>
+        <v>0.984772867423462</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>7273.46373356411</v>
+        <v>6965.07257856779</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>6786.04029165504</v>
+        <v>6766.56617110362</v>
       </c>
       <c r="J128" s="10" t="n">
-        <v>7181.82646648438</v>
+        <v>7022.56510175999</v>
       </c>
       <c r="K128" s="11" t="n">
-        <v>7200.68572746809</v>
+        <v>7003.45052954043</v>
       </c>
       <c r="L128" s="12" t="n">
-        <v>7200.68572746809</v>
+        <v>7003.45052954043</v>
       </c>
       <c r="M128" s="13" t="n">
-        <v>7202.24686130893</v>
+        <v>6982.37126951723</v>
       </c>
       <c r="N128" s="14" t="n">
-        <v>7202.24686130893</v>
+        <v>6982.37126951723</v>
       </c>
       <c r="O128" s="15" t="n">
-        <v>0.00000355872389002077</v>
+        <v>-0.0283480850898006</v>
       </c>
       <c r="P128" s="16" t="n">
-        <v>0.194867214097031</v>
+        <v>0.141317282607746</v>
       </c>
       <c r="Q128" s="17" t="n">
-        <v>0.00000355873022228614</v>
+        <v>-0.0279500481887092</v>
       </c>
       <c r="R128" s="18" t="n">
-        <v>0.990208671567779</v>
+        <v>1.00248363398289</v>
       </c>
       <c r="S128" s="19" t="n">
-        <v>1.0613327583931</v>
+        <v>1.03189285273455</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
         <v>178</v>
       </c>
-      <c r="B129" s="2"/>
+      <c r="B129" s="2" t="n">
+        <v>6578.69950141729</v>
+      </c>
       <c r="C129" s="3" t="n">
-        <v>7338.81267625428</v>
+        <v>6578.69950141729</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>9340.90723726053</v>
+        <v>6578.69950141729</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>5765.83945532745</v>
+        <v>6578.69950141729</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>0.97079063400161</v>
-      </c>
-      <c r="G129" s="7"/>
-      <c r="H129" s="8"/>
-      <c r="I129" s="9"/>
-      <c r="J129" s="10"/>
-      <c r="K129" s="11"/>
-      <c r="L129" s="12"/>
-      <c r="M129" s="13"/>
+        <v>0.977694607542064</v>
+      </c>
+      <c r="G129" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" s="8" t="n">
+        <v>6780.85733523067</v>
+      </c>
+      <c r="I129" s="9" t="n">
+        <v>6939.39049381407</v>
+      </c>
+      <c r="J129" s="10" t="n">
+        <v>7202.95521703975</v>
+      </c>
+      <c r="K129" s="11" t="n">
+        <v>6728.78775301443</v>
+      </c>
+      <c r="L129" s="12" t="n">
+        <v>6728.78775301443</v>
+      </c>
+      <c r="M129" s="13" t="n">
+        <v>6820.34201185643</v>
+      </c>
       <c r="N129" s="14" t="n">
-        <v>7559.62451553906</v>
-      </c>
-      <c r="O129" s="15"/>
-      <c r="P129" s="16"/>
-      <c r="Q129" s="17"/>
-      <c r="R129" s="18"/>
-      <c r="S129" s="19"/>
+        <v>6820.34201185643</v>
+      </c>
+      <c r="O129" s="15" t="n">
+        <v>-0.0234789635438526</v>
+      </c>
+      <c r="P129" s="16" t="n">
+        <v>0.000855349040771225</v>
+      </c>
+      <c r="Q129" s="17" t="n">
+        <v>-0.0232054772521435</v>
+      </c>
+      <c r="R129" s="18" t="n">
+        <v>1.00582296230015</v>
+      </c>
+      <c r="S129" s="19" t="n">
+        <v>0.98284453338319</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
@@ -9156,16 +9182,16 @@
       </c>
       <c r="B130" s="2"/>
       <c r="C130" s="3" t="n">
-        <v>8411.45955157587</v>
+        <v>7540.24692596969</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>11831.2049985505</v>
+        <v>9586.28014491874</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>5980.17292376096</v>
+        <v>5930.90571578297</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>1.12285715374434</v>
+        <v>1.1134238859576</v>
       </c>
       <c r="G130" s="7"/>
       <c r="H130" s="8"/>
@@ -9175,7 +9201,7 @@
       <c r="L130" s="12"/>
       <c r="M130" s="13"/>
       <c r="N130" s="14" t="n">
-        <v>7491.12166541092</v>
+        <v>6772.12607082226</v>
       </c>
       <c r="O130" s="15"/>
       <c r="P130" s="16"/>
@@ -9189,16 +9215,16 @@
       </c>
       <c r="B131" s="2"/>
       <c r="C131" s="3" t="n">
-        <v>7046.00747122949</v>
+        <v>6316.22139473634</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>10700.3598427121</v>
+        <v>8869.71535004944</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>4639.67773181341</v>
+        <v>4497.85039686789</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>0.923215123283081</v>
+        <v>0.925230612440542</v>
       </c>
       <c r="G131" s="7"/>
       <c r="H131" s="8"/>
@@ -9208,7 +9234,7 @@
       <c r="L131" s="12"/>
       <c r="M131" s="13"/>
       <c r="N131" s="14" t="n">
-        <v>7632.03211638574</v>
+        <v>6826.64549768368</v>
       </c>
       <c r="O131" s="15"/>
       <c r="P131" s="16"/>
@@ -9222,16 +9248,16 @@
       </c>
       <c r="B132" s="2"/>
       <c r="C132" s="3" t="n">
-        <v>7456.18464299239</v>
+        <v>6672.53796730296</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>12079.3389468599</v>
+        <v>10113.0591770683</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>4602.46125015373</v>
+        <v>4402.50196756056</v>
       </c>
       <c r="F132" s="6" t="n">
-        <v>0.980198694782586</v>
+        <v>0.982287280215694</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="8"/>
@@ -9241,7 +9267,7 @@
       <c r="L132" s="12"/>
       <c r="M132" s="13"/>
       <c r="N132" s="14" t="n">
-        <v>7606.80939760506</v>
+        <v>6792.85795682683</v>
       </c>
       <c r="O132" s="15"/>
       <c r="P132" s="16"/>
@@ -9254,10 +9280,18 @@
         <v>182</v>
       </c>
       <c r="B133" s="2"/>
-      <c r="C133" s="3"/>
-      <c r="D133" s="4"/>
-      <c r="E133" s="5"/>
-      <c r="F133" s="6"/>
+      <c r="C133" s="3" t="n">
+        <v>6873.91604554784</v>
+      </c>
+      <c r="D133" s="4" t="n">
+        <v>11110.4927414235</v>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>4252.80164443781</v>
+      </c>
+      <c r="F133" s="6" t="n">
+        <v>0.978727261095369</v>
+      </c>
       <c r="G133" s="7"/>
       <c r="H133" s="8"/>
       <c r="I133" s="9"/>
@@ -9265,7 +9299,9 @@
       <c r="K133" s="11"/>
       <c r="L133" s="12"/>
       <c r="M133" s="13"/>
-      <c r="N133" s="14"/>
+      <c r="N133" s="14" t="n">
+        <v>7023.32132636697</v>
+      </c>
       <c r="O133" s="15"/>
       <c r="P133" s="16"/>
       <c r="Q133" s="17"/>
@@ -9786,7 +9822,7 @@
         <v>220</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.0810352050436087</v>
+        <v>-0.0760360616958245</v>
       </c>
     </row>
     <row r="6">
@@ -9794,7 +9830,7 @@
         <v>221</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0402500140844762</v>
+        <v>0.0420889856838775</v>
       </c>
     </row>
     <row r="7">
@@ -9802,7 +9838,7 @@
         <v>222</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.236767051253355</v>
+        <v>0.226691643338528</v>
       </c>
     </row>
     <row r="8">
@@ -9810,7 +9846,7 @@
         <v>223</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.458724293738252</v>
+        <v>0.437105690310537</v>
       </c>
     </row>
     <row r="9">
@@ -9818,7 +9854,7 @@
         <v>224</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.601910742305836</v>
+        <v>0.579327025860819</v>
       </c>
     </row>
     <row r="10">
@@ -9826,7 +9862,7 @@
         <v>225</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.569788141883</v>
+        <v>0.561331652381918</v>
       </c>
     </row>
     <row r="11">
@@ -9834,7 +9870,7 @@
         <v>226</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.402808807113062</v>
+        <v>0.404730761410807</v>
       </c>
     </row>
     <row r="12">
@@ -9842,7 +9878,7 @@
         <v>227</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.22543289538925</v>
+        <v>0.215646368191768</v>
       </c>
     </row>
     <row r="13">
@@ -9850,7 +9886,7 @@
         <v>228</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.10540561531832</v>
+        <v>0.0880231819730406</v>
       </c>
     </row>
     <row r="14">
@@ -9908,237 +9944,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
-    <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5dd4176-d247-4204-85b8-921214f3ccea" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="01529062-7a8b-4d76-943d-e0db5644ee6d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="359b39ce-e1f9-4933-8424-33b611e6fdcd" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c9b73259-0823-4f05-8927-4a40ee49fbe1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="359b39ce-e1f9-4933-8424-33b611e6fdcd">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64EE0691-6624-4D5D-990D-043CFB93874C}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{319E09E3-5999-4BA9-AE4E-1088A538FE25}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A42C381E-09B7-4873-8485-7490A963766E}"/>
 </file>
--- a/indicadores/ARG-ESS_out.xlsx
+++ b/indicadores/ARG-ESS_out.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="231">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -23,7 +23,7 @@
     <t xml:space="preserve">Título</t>
   </si>
   <si>
-    <t xml:space="preserve">Egresos por servicios de Argentina</t>
+    <t xml:space="preserve">Egresos por servicios</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
@@ -71,6 +71,12 @@
     <t xml:space="preserve">Regresores</t>
   </si>
   <si>
+    <t xml:space="preserve">Alcance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argentina</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resumen del correlograma</t>
   </si>
   <si>
@@ -104,13 +110,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">30/03/2026</t>
+    <t xml:space="preserve">17/06/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">arodriguez</t>
+    <t xml:space="preserve">focampo</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1203,9 +1209,13 @@
       <c r="J6" s="1"/>
     </row>
     <row r="7">
-      <c r="A7"/>
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
       <c r="B7"/>
-      <c r="C7"/>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
       <c r="D7"/>
       <c r="E7"/>
       <c r="F7"/>
@@ -1216,7 +1226,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8"/>
       <c r="C8"/>
@@ -1230,12 +1240,12 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.579327025860819</v>
+        <v>0.577296261064304</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1246,7 +1256,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
@@ -1274,7 +1284,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
@@ -1288,12 +1298,12 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.335619802892742</v>
+        <v>0.333270973038825</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1316,7 +1326,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -1330,7 +1340,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B16"/>
       <c r="C16"/>
@@ -1344,7 +1354,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1358,12 +1368,12 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.0050691223722586</v>
+        <v>0.00935338540452576</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1374,7 +1384,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1388,12 +1398,12 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.821075588484585</v>
+        <v>0.800563499721089</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1536,10 +1546,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C32"/>
       <c r="D32"/>
@@ -1552,10 +1562,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C33"/>
       <c r="D33"/>
@@ -1579,66 +1589,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="R1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>2241.8</v>
@@ -1691,7 +1701,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>1494.9</v>
@@ -1748,7 +1758,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>1621.6</v>
@@ -1805,7 +1815,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>1784.8</v>
@@ -1862,7 +1872,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>2322.2</v>
@@ -1921,7 +1931,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>1565.8</v>
@@ -1980,7 +1990,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>1627.6</v>
@@ -2039,7 +2049,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>1747.1</v>
@@ -2098,7 +2108,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>2398.86386883434</v>
@@ -2157,7 +2167,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>1679.23231807648</v>
@@ -2216,7 +2226,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>1905.32218351584</v>
@@ -2275,7 +2285,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>1968.88110515463</v>
@@ -2334,7 +2344,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>2708.71231090393</v>
@@ -2393,7 +2403,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>1903.58013454352</v>
@@ -2452,7 +2462,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>2209.94973449106</v>
@@ -2511,7 +2521,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>2161.65562016748</v>
@@ -2570,7 +2580,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>2845.82603759642</v>
@@ -2629,7 +2639,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>2074.47075910088</v>
@@ -2688,7 +2698,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>2220.49703180433</v>
@@ -2747,7 +2757,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>2157.68471807993</v>
@@ -2806,7 +2816,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>2761.19404120798</v>
@@ -2865,7 +2875,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>1899.39115314154</v>
@@ -2924,7 +2934,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>2098.32520367766</v>
@@ -2983,7 +2993,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>2070.99836436598</v>
@@ -3042,7 +3052,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>2878.0472386878</v>
@@ -3101,7 +3111,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>2048.28319054732</v>
@@ -3160,7 +3170,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>2180.06020796427</v>
@@ -3219,7 +3229,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>2112.86602822575</v>
@@ -3278,7 +3288,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>2935.63493973013</v>
@@ -3337,7 +3347,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>2085.81764439801</v>
@@ -3396,7 +3406,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>1894.04001281739</v>
@@ -3455,7 +3465,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>1574.64834843281</v>
@@ -3514,7 +3524,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>1475.19763584073</v>
@@ -3573,7 +3583,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>1124.55064572027</v>
@@ -3632,7 +3642,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>1152.15904543455</v>
@@ -3691,7 +3701,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>1203.71436422561</v>
@@ -3750,7 +3760,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>1425.89524509937</v>
@@ -3809,7 +3819,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>1290.38528816145</v>
@@ -3868,7 +3878,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>1470.49652561565</v>
@@ -3927,7 +3937,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>1506.23806134637</v>
@@ -3986,7 +3996,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>1689.82206595359</v>
@@ -4045,7 +4055,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>1445.19764128156</v>
@@ -4104,7 +4114,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>1649.16622342598</v>
@@ -4163,7 +4173,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>1834.94060897935</v>
@@ -4222,7 +4232,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>1933.00273454338</v>
@@ -4281,7 +4291,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>1888.09456688716</v>
@@ -4340,7 +4350,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>1827.0050126273</v>
@@ -4399,7 +4409,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>1977.85475412658</v>
@@ -4458,7 +4468,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>2160.36159801246</v>
@@ -4517,7 +4527,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>2033.21078101257</v>
@@ -4576,7 +4586,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>2167.47837936594</v>
@@ -4635,7 +4645,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>2312.92176137013</v>
@@ -4694,7 +4704,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>2696.86049566001</v>
@@ -4753,7 +4763,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>2516.13485121782</v>
@@ -4812,7 +4822,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>2803.88411969971</v>
@@ -4871,7 +4881,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>3010.33905330945</v>
@@ -4930,7 +4940,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>3500.76983696121</v>
@@ -4989,7 +4999,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>3286.26557559881</v>
@@ -5048,7 +5058,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>3537.71845126756</v>
@@ -5107,7 +5117,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>3321.73023465199</v>
@@ -5166,7 +5176,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>3386.00448971788</v>
@@ -5225,7 +5235,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>2696.05052423399</v>
@@ -5284,7 +5294,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>3036.48849479411</v>
@@ -5343,7 +5353,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>3418.10930449306</v>
@@ -5402,7 +5412,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>3735.59369195447</v>
@@ -5461,7 +5471,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>3551.93509050901</v>
@@ -5520,7 +5530,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>3501.98814428698</v>
@@ -5579,7 +5589,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>3831.21508377001</v>
@@ -5638,7 +5648,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>4375.22212253129</v>
@@ -5697,7 +5707,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>4129.41074094782</v>
@@ -5756,7 +5766,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>4333.19154339499</v>
@@ -5815,7 +5825,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>4811.64490558585</v>
@@ -5874,7 +5884,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>5066.12763917827</v>
@@ -5933,7 +5943,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>4383.03555041862</v>
@@ -5992,7 +6002,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>4429.87614408065</v>
@@ -6051,7 +6061,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>4465.28611985202</v>
@@ -6110,7 +6120,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>5131.88191643965</v>
@@ -6169,7 +6179,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>4499.44907972728</v>
@@ -6228,7 +6238,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>4539.76782551238</v>
@@ -6287,7 +6297,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>4837.70906203481</v>
@@ -6346,7 +6356,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>4964.35954377805</v>
@@ -6405,7 +6415,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>4294.14828388207</v>
@@ -6464,7 +6474,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>4320.30298531754</v>
@@ -6523,7 +6533,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>4458.85316814996</v>
@@ -6582,7 +6592,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>5009.75394783902</v>
@@ -6641,7 +6651,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>4294.11901736909</v>
@@ -6700,7 +6710,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>4771.89666477564</v>
@@ -6759,7 +6769,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>4952.78741323696</v>
@@ -6818,7 +6828,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>6108.57642446564</v>
@@ -6877,7 +6887,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>4881.31680020904</v>
@@ -6936,7 +6946,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>5446.86304040468</v>
@@ -6995,7 +7005,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>5439.60580468164</v>
@@ -7054,7 +7064,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>7098.31965039088</v>
@@ -7113,7 +7123,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>5694.02546550393</v>
@@ -7172,7 +7182,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>6209.22803193611</v>
@@ -7231,7 +7241,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>6200.06740637572</v>
@@ -7290,7 +7300,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>7870.36784763967</v>
@@ -7349,7 +7359,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>6054.57948367958</v>
@@ -7408,7 +7418,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>5310.71118746629</v>
@@ -7467,7 +7477,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>5041.77244509139</v>
@@ -7526,7 +7536,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>5651.60509658883</v>
@@ -7585,7 +7595,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>4665.68219017201</v>
@@ -7644,7 +7654,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>4755.00405694119</v>
@@ -7703,7 +7713,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>4573.30287832837</v>
@@ -7762,7 +7772,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>4670.88465711875</v>
@@ -7821,7 +7831,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>2175.26624692192</v>
@@ -7880,7 +7890,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>2405.16348217783</v>
@@ -7939,7 +7949,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>2776.70598703957</v>
@@ -7998,7 +8008,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>2640.35379506736</v>
@@ -8057,7 +8067,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>2885.42830497867</v>
@@ -8116,7 +8126,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>3444.49013745048</v>
@@ -8175,7 +8185,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>4318.55493831423</v>
@@ -8234,7 +8244,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>5038.84746379941</v>
@@ -8293,7 +8303,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B115" s="2" t="n">
         <v>5155.69426033944</v>
@@ -8352,7 +8362,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>5721.03663102072</v>
@@ -8411,7 +8421,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B117" s="2" t="n">
         <v>5275.14336147936</v>
@@ -8470,7 +8480,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B118" s="2" t="n">
         <v>6464.88884607211</v>
@@ -8529,7 +8539,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>5373.68391411676</v>
@@ -8588,7 +8598,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B120" s="2" t="n">
         <v>5519.15105764071</v>
@@ -8647,7 +8657,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B121" s="2" t="n">
         <v>5214.52990895346</v>
@@ -8706,7 +8716,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B122" s="2" t="n">
         <v>5530.3441739009</v>
@@ -8765,7 +8775,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B123" s="2" t="n">
         <v>5009.70362811794</v>
@@ -8824,7 +8834,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B124" s="2" t="n">
         <v>6033.85596798828</v>
@@ -8883,7 +8893,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B125" s="2" t="n">
         <v>6342.86762614381</v>
@@ -8942,7 +8952,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B126" s="2" t="n">
         <v>9133.82917570275</v>
@@ -9001,7 +9011,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B127" s="2" t="n">
         <v>6663.08011470637</v>
@@ -9060,7 +9070,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B128" s="2" t="n">
         <v>6896.80805983389</v>
@@ -9119,7 +9129,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B129" s="2" t="n">
         <v>6578.69950141729</v>
@@ -9178,7 +9188,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B130" s="2"/>
       <c r="C130" s="3" t="n">
@@ -9211,7 +9221,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B131" s="2"/>
       <c r="C131" s="3" t="n">
@@ -9244,7 +9254,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B132" s="2"/>
       <c r="C132" s="3" t="n">
@@ -9277,7 +9287,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B133" s="2"/>
       <c r="C133" s="3" t="n">
@@ -9310,7 +9320,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B134" s="2"/>
       <c r="C134" s="3"/>
@@ -9333,7 +9343,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B135" s="2"/>
       <c r="C135" s="3"/>
@@ -9356,7 +9366,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B136" s="2"/>
       <c r="C136" s="3"/>
@@ -9379,7 +9389,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B137" s="2"/>
       <c r="C137" s="3"/>
@@ -9402,7 +9412,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B138" s="2"/>
       <c r="C138" s="3"/>
@@ -9425,7 +9435,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B139" s="2"/>
       <c r="C139" s="3"/>
@@ -9448,7 +9458,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B140" s="2"/>
       <c r="C140" s="3"/>
@@ -9471,7 +9481,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B141" s="2"/>
       <c r="C141" s="3"/>
@@ -9494,7 +9504,7 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B142" s="2"/>
       <c r="C142" s="3"/>
@@ -9517,7 +9527,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B143" s="2"/>
       <c r="C143" s="3"/>
@@ -9540,7 +9550,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B144" s="2"/>
       <c r="C144" s="3"/>
@@ -9563,7 +9573,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B145" s="2"/>
       <c r="C145" s="3"/>
@@ -9586,7 +9596,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B146" s="2"/>
       <c r="C146" s="3"/>
@@ -9609,7 +9619,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B147" s="2"/>
       <c r="C147" s="3"/>
@@ -9632,7 +9642,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B148" s="2"/>
       <c r="C148" s="3"/>
@@ -9655,7 +9665,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B149" s="2"/>
       <c r="C149" s="3"/>
@@ -9689,97 +9699,97 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -9803,7 +9813,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -9813,80 +9823,80 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.0760360616958245</v>
+        <v>-0.0776990570851476</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0420889856838775</v>
+        <v>0.0439167477028377</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.226691643338528</v>
+        <v>0.22932987864076</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.437105690310537</v>
+        <v>0.436736073625052</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.579327025860819</v>
+        <v>0.577296261064304</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.561331652381918</v>
+        <v>0.560510095456793</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.404730761410807</v>
+        <v>0.406320642893262</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.215646368191768</v>
+        <v>0.218546449441727</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.0880231819730406</v>
+        <v>0.0893269871463753</v>
       </c>
     </row>
     <row r="14">

--- a/indicadores/ARG-ESS_out.xlsx
+++ b/indicadores/ARG-ESS_out.xlsx
@@ -59,7 +59,7 @@
     <t xml:space="preserve">log</t>
   </si>
   <si>
-    <t xml:space="preserve">(0 1 0)(0 1 1)</t>
+    <t xml:space="preserve">(0 1 1)(0 1 1)</t>
   </si>
   <si>
     <t xml:space="preserve">Código</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">17/06/2026</t>
+    <t xml:space="preserve">25/06/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">focampo</t>
+    <t xml:space="preserve">arodriguez</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1225,9 +1225,7 @@
       <c r="J7" s="1"/>
     </row>
     <row r="8">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
+      <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
@@ -1239,14 +1237,10 @@
       <c r="J8" s="1"/>
     </row>
     <row r="9">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
+      <c r="A9"/>
       <c r="B9"/>
       <c r="C9"/>
-      <c r="D9" t="n">
-        <v>0.577296261064304</v>
-      </c>
+      <c r="D9"/>
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9"/>
@@ -1256,13 +1250,11 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
+      <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
@@ -1271,10 +1263,14 @@
       <c r="J10" s="1"/>
     </row>
     <row r="11">
-      <c r="A11"/>
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
       <c r="B11"/>
       <c r="C11"/>
-      <c r="D11"/>
+      <c r="D11" t="n">
+        <v>0.566138820054058</v>
+      </c>
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11"/>
@@ -1284,11 +1280,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
-      <c r="D12"/>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12"/>
@@ -1297,14 +1295,10 @@
       <c r="J12" s="1"/>
     </row>
     <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
+      <c r="A13"/>
       <c r="B13"/>
       <c r="C13"/>
-      <c r="D13" t="n">
-        <v>0.333270973038825</v>
-      </c>
+      <c r="D13"/>
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13"/>
@@ -1313,7 +1307,9 @@
       <c r="J13" s="1"/>
     </row>
     <row r="14">
-      <c r="A14"/>
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -1326,11 +1322,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
-      <c r="D15"/>
+      <c r="D15" t="n">
+        <v>0.320513163572201</v>
+      </c>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
@@ -1339,9 +1337,7 @@
       <c r="J15" s="1"/>
     </row>
     <row r="16">
-      <c r="A16" t="s">
-        <v>26</v>
-      </c>
+      <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -1354,7 +1350,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1368,13 +1364,11 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
-      <c r="D18" t="n">
-        <v>0.00935338540452576</v>
-      </c>
+      <c r="D18"/>
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
@@ -1384,7 +1378,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1403,7 +1397,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.800563499721089</v>
+        <v>0.00918669217091027</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1413,7 +1407,9 @@
       <c r="J20" s="1"/>
     </row>
     <row r="21">
-      <c r="A21"/>
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -1425,10 +1421,14 @@
       <c r="J21" s="1"/>
     </row>
     <row r="22">
-      <c r="A22"/>
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
       <c r="B22"/>
       <c r="C22"/>
-      <c r="D22"/>
+      <c r="D22" t="n">
+        <v>0.601090922048891</v>
+      </c>
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
@@ -1672,10 +1672,10 @@
         <v>1760.64557739452</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>1781.56185434975</v>
+        <v>1781.56149111148</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>1729.66080478652</v>
+        <v>1729.66080480816</v>
       </c>
       <c r="K2" s="11" t="n">
         <v>1775.24874755028</v>
@@ -1696,7 +1696,7 @@
         <v>1.00439540324969</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>0.992603383581314</v>
+        <v>0.99260358596082</v>
       </c>
     </row>
     <row r="3">
@@ -1725,10 +1725,10 @@
         <v>1771.99220927855</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>1812.37053493999</v>
+        <v>1812.37023936634</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>1757.34941929469</v>
+        <v>1757.34941931496</v>
       </c>
       <c r="K3" s="11" t="n">
         <v>1754.65547896032</v>
@@ -1753,7 +1753,7 @@
         <v>1.00173783722545</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>0.979419831144964</v>
+        <v>0.979419990875405</v>
       </c>
     </row>
     <row r="4">
@@ -1782,10 +1782,10 @@
         <v>1815.72686774121</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>1843.17526983848</v>
+        <v>1843.17504215647</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>1785.26597351667</v>
+        <v>1785.26597353546</v>
       </c>
       <c r="K4" s="11" t="n">
         <v>1732.50233872429</v>
@@ -1810,7 +1810,7 @@
         <v>1.00011996967783</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.985226272088432</v>
+        <v>0.985226393790547</v>
       </c>
     </row>
     <row r="5">
@@ -1839,10 +1839,10 @@
         <v>1860.95703972976</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>1873.93604144349</v>
+        <v>1873.9358822919</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>1813.62493746461</v>
+        <v>1813.62493748161</v>
       </c>
       <c r="K5" s="11" t="n">
         <v>1877.66958519149</v>
@@ -1867,7 +1867,7 @@
         <v>0.996082087039312</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>0.989183158351896</v>
+        <v>0.98918324236228</v>
       </c>
     </row>
     <row r="6">
@@ -1896,10 +1896,10 @@
         <v>1856.60744927745</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>1904.59567690196</v>
+        <v>1904.59558747363</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>1842.79308562179</v>
+        <v>1842.79308563638</v>
       </c>
       <c r="K6" s="11" t="n">
         <v>1843.59784997389</v>
@@ -1926,7 +1926,7 @@
         <v>0.996528854768895</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>0.971420295457856</v>
+        <v>0.971420341069899</v>
       </c>
     </row>
     <row r="7">
@@ -1955,10 +1955,10 @@
         <v>1824.37010523696</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1935.09933682569</v>
+        <v>1935.09931896699</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>1873.45741571011</v>
+        <v>1873.45741572127</v>
       </c>
       <c r="K7" s="11" t="n">
         <v>1835.78629559616</v>
@@ -1985,7 +1985,7 @@
         <v>1.00414065645182</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>0.946682250477526</v>
+        <v>0.946682259214294</v>
       </c>
     </row>
     <row r="8">
@@ -2014,10 +2014,10 @@
         <v>1812.52633916864</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>1965.35405818465</v>
+        <v>1965.35411445137</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>1906.30894927324</v>
+        <v>1906.3089492795</v>
       </c>
       <c r="K8" s="11" t="n">
         <v>1730.66717915826</v>
@@ -2044,7 +2044,7 @@
         <v>1.00744660195661</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>0.929106637935233</v>
+        <v>0.929106611335556</v>
       </c>
     </row>
     <row r="9">
@@ -2073,10 +2073,10 @@
         <v>1843.44643514561</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>1995.20480729802</v>
+        <v>1995.20494096654</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>1941.85035225426</v>
+        <v>1941.85035225364</v>
       </c>
       <c r="K9" s="11" t="n">
         <v>1843.25503147577</v>
@@ -2103,7 +2103,7 @@
         <v>1.005182977798</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>0.928727201494749</v>
+        <v>0.928727139274783</v>
       </c>
     </row>
     <row r="10">
@@ -2132,10 +2132,10 @@
         <v>1907.0072419922</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>2024.40103316064</v>
+        <v>2024.40124819273</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>1980.11537754576</v>
+        <v>1980.11537753571</v>
       </c>
       <c r="K10" s="11" t="n">
         <v>1912.96750624288</v>
@@ -2162,7 +2162,7 @@
         <v>1.00011552539216</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>0.942119431135629</v>
+        <v>0.942119331063614</v>
       </c>
     </row>
     <row r="11">
@@ -2191,10 +2191,10 @@
         <v>1961.23239831564</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>2052.5972161574</v>
+        <v>2052.59751711674</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>2020.6448014364</v>
+        <v>2020.64480141385</v>
       </c>
       <c r="K11" s="11" t="n">
         <v>1959.72015504519</v>
@@ -2221,7 +2221,7 @@
         <v>1.000166185914</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>0.955646978410348</v>
+        <v>0.955646838289901</v>
       </c>
     </row>
     <row r="12">
@@ -2250,10 +2250,10 @@
         <v>2014.57756141362</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>2079.37819071892</v>
+        <v>2079.37858263665</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>2062.64366085836</v>
+        <v>2062.64366081972</v>
       </c>
       <c r="K12" s="11" t="n">
         <v>2013.82549372401</v>
@@ -2280,7 +2280,7 @@
         <v>1.00174498392577</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>0.970527139258765</v>
+        <v>0.970526956335467</v>
       </c>
     </row>
     <row r="13">
@@ -2309,10 +2309,10 @@
         <v>2090.01563239174</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>2104.2707431126</v>
+        <v>2104.27123129923</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>2105.01236951184</v>
+        <v>2105.01236945317</v>
       </c>
       <c r="K13" s="11" t="n">
         <v>2085.00072500881</v>
@@ -2339,7 +2339,7 @@
         <v>0.999579551006778</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>0.992808028273524</v>
+        <v>0.992807797944088</v>
       </c>
     </row>
     <row r="14">
@@ -2368,10 +2368,10 @@
         <v>2158.61881531001</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>2126.76068917022</v>
+        <v>2126.7612789707</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>2146.40725026138</v>
+        <v>2146.40725017852</v>
       </c>
       <c r="K14" s="11" t="n">
         <v>2172.72060595151</v>
@@ -2398,7 +2398,7 @@
         <v>1.0004781190168</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>1.01546492890004</v>
+        <v>1.01546464728794</v>
       </c>
     </row>
     <row r="15">
@@ -2427,10 +2427,10 @@
         <v>2231.26859147113</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>2146.32180096224</v>
+        <v>2146.32249745084</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>2185.38456774901</v>
+        <v>2185.38456763791</v>
       </c>
       <c r="K15" s="11" t="n">
         <v>2208.16163115073</v>
@@ -2445,19 +2445,19 @@
         <v>2226.22662290828</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>0.0303614703411086</v>
+        <v>0.0303614703411084</v>
       </c>
       <c r="P15" s="16" t="n">
         <v>0.134927568393723</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>0.0308270800335249</v>
+        <v>0.0308270800335246</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>0.99774031302994</v>
+        <v>0.997740313029939</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>1.03722872400132</v>
+        <v>1.03722838741724</v>
       </c>
     </row>
     <row r="16">
@@ -2477,7 +2477,7 @@
         <v>2209.94973449106</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.952198672314389</v>
+        <v>0.95219867231439</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>0.831713051711106</v>
@@ -2486,10 +2486,10 @@
         <v>2291.00911646623</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>2162.45657550713</v>
+        <v>2162.45738311879</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>2220.63215339519</v>
+        <v>2220.63215325233</v>
       </c>
       <c r="K16" s="11" t="n">
         <v>2320.89142607142</v>
@@ -2504,19 +2504,19 @@
         <v>2285.07925268273</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.0260926527243346</v>
+        <v>0.0260926527243344</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>0.13229632637816</v>
+        <v>0.132296326378159</v>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>0.0264360461638764</v>
+        <v>0.0264360461638762</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>0.997411680407172</v>
+        <v>0.997411680407171</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>1.05670526685459</v>
+        <v>1.05670487220751</v>
       </c>
     </row>
     <row r="17">
@@ -2545,10 +2545,10 @@
         <v>2303.53627422467</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>2174.7061597172</v>
+        <v>2174.70708181226</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>2250.95172393741</v>
+        <v>2250.95172376033</v>
       </c>
       <c r="K17" s="11" t="n">
         <v>2300.43013281991</v>
@@ -2563,19 +2563,19 @@
         <v>2302.9246352751</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>0.00777918808353149</v>
+        <v>0.00777918808353193</v>
       </c>
       <c r="P17" s="16" t="n">
         <v>0.102333049183534</v>
       </c>
       <c r="Q17" s="17" t="n">
-        <v>0.00780952458056783</v>
+        <v>0.00780952458056827</v>
       </c>
       <c r="R17" s="18" t="n">
         <v>0.999734478264393</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>1.05895898854426</v>
+        <v>1.05895853953627</v>
       </c>
     </row>
     <row r="18">
@@ -2604,10 +2604,10 @@
         <v>2319.0340318488</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>2182.70757928469</v>
+        <v>2182.70861764412</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>2275.62114846306</v>
+        <v>2275.62114825111</v>
       </c>
       <c r="K18" s="11" t="n">
         <v>2294.97565208045</v>
@@ -2622,19 +2622,19 @@
         <v>2318.86298584789</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>0.00689707752114998</v>
+        <v>0.0068970775211502</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>0.0737212178231534</v>
+        <v>0.0737212178231539</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>0.00692091713669285</v>
+        <v>0.00692091713669307</v>
       </c>
       <c r="R18" s="18" t="n">
         <v>0.999926242565413</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>1.06237913308012</v>
+        <v>1.0623786276845</v>
       </c>
     </row>
     <row r="19">
@@ -2654,7 +2654,7 @@
         <v>2074.47075910088</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.869773347800402</v>
+        <v>0.869773347800401</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>1</v>
@@ -2663,16 +2663,16 @@
         <v>2354.81514801591</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>2186.17643738505</v>
+        <v>2186.17759163411</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>2294.16568810398</v>
+        <v>2294.16568785917</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>2385.07050641075</v>
+        <v>2385.07050641076</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>2385.07050641075</v>
+        <v>2385.07050641076</v>
       </c>
       <c r="M19" s="13" t="n">
         <v>2348.76495904353</v>
@@ -2681,19 +2681,19 @@
         <v>2348.76495904353</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>0.0128126674266387</v>
+        <v>0.0128126674266385</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>0.0550430647420646</v>
+        <v>0.0550430647420648</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>0.0128951013398066</v>
+        <v>0.0128951013398064</v>
       </c>
       <c r="R19" s="18" t="n">
         <v>0.997430715961938</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>1.07437118014727</v>
+        <v>1.07437061290519</v>
       </c>
     </row>
     <row r="20">
@@ -2713,7 +2713,7 @@
         <v>2220.49703180433</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.953026262263703</v>
+        <v>0.953026262263705</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>1</v>
@@ -2722,16 +2722,16 @@
         <v>2346.92948857003</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>2184.8985047392</v>
+        <v>2184.89977169851</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>2306.20737651007</v>
+        <v>2306.20737623813</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>2329.94317127215</v>
+        <v>2329.94317127214</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>2329.94317127215</v>
+        <v>2329.94317127214</v>
       </c>
       <c r="M20" s="13" t="n">
         <v>2336.45703444793</v>
@@ -2740,19 +2740,19 @@
         <v>2336.45703444793</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>-0.00525394652589054</v>
+        <v>-0.00525394652589188</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>0.0224840261907238</v>
+        <v>0.0224840261907231</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>-0.00524016868874277</v>
+        <v>-0.00524016868874411</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>0.995537806238703</v>
+        <v>0.995537806238702</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>1.06936639362423</v>
+        <v>1.06936577353001</v>
       </c>
     </row>
     <row r="21">
@@ -2772,7 +2772,7 @@
         <v>2157.68471807993</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.937768543833178</v>
+        <v>0.93776854383318</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>1</v>
@@ -2781,10 +2781,10 @@
         <v>2294.61439283767</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>2178.78386086122</v>
+        <v>2178.78523382533</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>2311.82277142275</v>
+        <v>2311.8227711344</v>
       </c>
       <c r="K21" s="11" t="n">
         <v>2300.87128883667</v>
@@ -2799,19 +2799,19 @@
         <v>2292.37019651742</v>
       </c>
       <c r="O21" s="15" t="n">
-        <v>-0.0190493915223199</v>
+        <v>-0.019049391522318</v>
       </c>
       <c r="P21" s="16" t="n">
-        <v>-0.00458305868807651</v>
+        <v>-0.00458305868807563</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>-0.0188690985027792</v>
+        <v>-0.0188690985027773</v>
       </c>
       <c r="R21" s="18" t="n">
-        <v>0.999021972350886</v>
+        <v>0.999021972350887</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.05213290666257</v>
+        <v>1.05213224365977</v>
       </c>
     </row>
     <row r="22">
@@ -2831,46 +2831,46 @@
         <v>2761.19404120798</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1.2338905017666</v>
+        <v>1.23389050176659</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>2231.1510494589</v>
+        <v>2231.15104945891</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>2167.83323818175</v>
+        <v>2167.8347061273</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>2311.2071095573</v>
+        <v>2311.20710926954</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>2237.79503712419</v>
+        <v>2237.79503712421</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>2237.79503712419</v>
+        <v>2237.79503712421</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>2235.58223044937</v>
+        <v>2235.58223044938</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>2235.58223044937</v>
+        <v>2235.58223044938</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>-0.0250846026815238</v>
+        <v>-0.0250846026815214</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>-0.0359144787366847</v>
+        <v>-0.035914478736682</v>
       </c>
       <c r="Q22" s="17" t="n">
-        <v>-0.0247725983151943</v>
+        <v>-0.024772598315192</v>
       </c>
       <c r="R22" s="18" t="n">
         <v>1.0019860515457</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>1.03125193906725</v>
+        <v>1.03125124075677</v>
       </c>
     </row>
     <row r="23">
@@ -2890,25 +2890,25 @@
         <v>1899.39115314154</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.876965512272918</v>
+        <v>0.876965512272919</v>
       </c>
       <c r="G23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>2182.97523299182</v>
+        <v>2182.97523299183</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>2152.12367377394</v>
+        <v>2152.12522050155</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>2304.50087021601</v>
+        <v>2304.50086995363</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>2165.86755871243</v>
+        <v>2165.86755871242</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>2165.86755871243</v>
+        <v>2165.86755871242</v>
       </c>
       <c r="M23" s="13" t="n">
         <v>2192.56423378053</v>
@@ -2917,19 +2917,19 @@
         <v>2192.56423378053</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>-0.0194299580493674</v>
+        <v>-0.0194299580493702</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>-0.0665033445179642</v>
+        <v>-0.066503344517964</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>-0.0192424130425264</v>
+        <v>-0.0192424130425292</v>
       </c>
       <c r="R23" s="18" t="n">
         <v>1.00439262921713</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>1.01879100188312</v>
+        <v>1.01879026968029</v>
       </c>
     </row>
     <row r="24">
@@ -2949,25 +2949,25 @@
         <v>2098.32520367766</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.953469200357188</v>
+        <v>0.953469200357192</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>2183.98489379689</v>
+        <v>2183.98489379688</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>2131.77593083526</v>
+        <v>2131.77753405208</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>2291.47747233905</v>
+        <v>2291.47747213602</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>2200.72678057308</v>
+        <v>2200.72678057307</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>2200.72678057308</v>
+        <v>2200.72678057307</v>
       </c>
       <c r="M24" s="13" t="n">
         <v>2197.21465100989</v>
@@ -2976,19 +2976,19 @@
         <v>2197.21465100989</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>0.00211874861631585</v>
+        <v>0.00211874861631252</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>-0.0595955249273128</v>
+        <v>-0.0595955249273145</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>0.00212099475021632</v>
+        <v>0.00212099475021299</v>
       </c>
       <c r="R24" s="18" t="n">
         <v>1.00605762304061</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>1.0306968097482</v>
+        <v>1.03069603460612</v>
       </c>
     </row>
     <row r="25">
@@ -3008,7 +3008,7 @@
         <v>2070.99836436598</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.940611665725696</v>
+        <v>0.9406116657257</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>0.612021987566334</v>
@@ -3017,37 +3017,37 @@
         <v>2252.74044292679</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>2106.91936249128</v>
+        <v>2106.92099284425</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>2271.21716830906</v>
+        <v>2271.21716820987</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>2201.75704791858</v>
+        <v>2201.75704791857</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>2221.53748418098</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>2249.24029580153</v>
+        <v>2249.24029580154</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>2249.24029580153</v>
+        <v>2249.24029580154</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>0.0234020223899084</v>
+        <v>0.0234020223899127</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>-0.0188145443442825</v>
+        <v>-0.0188145443442819</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>0.0236779983092352</v>
+        <v>0.0236779983092397</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>0.998446271457394</v>
+        <v>0.998446271457396</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>1.06754930247637</v>
+        <v>1.06754847639785</v>
       </c>
     </row>
     <row r="26">
@@ -3067,46 +3067,46 @@
         <v>2878.0472386878</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>1.21923217155116</v>
+        <v>1.21923217155114</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>0.834599830389825</v>
+        <v>0.834599830389808</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>2315.91367766712</v>
+        <v>2315.91367766713</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>2077.72641614864</v>
+        <v>2077.72803622252</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>2242.34645704983</v>
+        <v>2242.34645711049</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>2360.54076150748</v>
+        <v>2360.54076150752</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>2353.15943427108</v>
+        <v>2353.15943427111</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>2308.71789463233</v>
+        <v>2308.71789463234</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>2308.71789463233</v>
+        <v>2308.71789463234</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>0.0260998335916476</v>
+        <v>0.0260998335916515</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>0.0327143699689634</v>
+        <v>0.0327143699689656</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>0.0264434168913932</v>
+        <v>0.0264434168913972</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>0.996892896698103</v>
+        <v>0.996892896698104</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>1.11117511751709</v>
+        <v>1.11117425109678</v>
       </c>
     </row>
     <row r="27">
@@ -3126,7 +3126,7 @@
         <v>2048.28319054732</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.887849879634648</v>
+        <v>0.887849879634652</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>1</v>
@@ -3135,37 +3135,37 @@
         <v>2316.98853854445</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>2044.44117554006</v>
+        <v>2044.44273883844</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>2203.24343906454</v>
+        <v>2203.24343935308</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>2307.01522580619</v>
+        <v>2307.01522580618</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>2307.01522580619</v>
+        <v>2307.01522580618</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>2313.57323878202</v>
+        <v>2313.57323878201</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>2313.57323878202</v>
+        <v>2313.57323878201</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>0.00210083951672846</v>
+        <v>0.00210083951672225</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>0.0551906316527087</v>
+        <v>0.0551906316527073</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.00210304782622983</v>
+        <v>0.00210304782622361</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>0.998525974684114</v>
+        <v>0.998525974684113</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>1.13164089359082</v>
+        <v>1.13164002827317</v>
       </c>
     </row>
     <row r="28">
@@ -3185,46 +3185,46 @@
         <v>2180.06020796427</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.953197185242857</v>
+        <v>0.953197185242865</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>2292.52747883233</v>
+        <v>2292.52747883232</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>2007.47987003456</v>
+        <v>2007.48131996731</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>2152.84027974246</v>
+        <v>2152.84028033862</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>2287.10306924461</v>
+        <v>2287.1030692446</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>2287.10306924461</v>
+        <v>2287.1030692446</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>2311.23685247287</v>
+        <v>2311.23685247284</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>2311.23685247287</v>
+        <v>2311.23685247284</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>-0.00101037078790605</v>
+        <v>-0.00101037078791494</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>0.0518939746786078</v>
+        <v>0.0518939746786007</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>-0.00100986053520413</v>
+        <v>-0.00100986053521301</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>1.00816102481357</v>
+        <v>1.00816102481356</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>1.15131259195794</v>
+        <v>1.15131176040556</v>
       </c>
     </row>
     <row r="29">
@@ -3244,46 +3244,46 @@
         <v>2112.86602822575</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.952874437844264</v>
+        <v>0.952874437844268</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>2363.72604559605</v>
+        <v>2363.72604559601</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>1967.42283778259</v>
+        <v>1967.42410668882</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>2090.58800340656</v>
+        <v>2090.58800440037</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>2217.36038276543</v>
+        <v>2217.36038276542</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>2363.72604559605</v>
+        <v>2363.72604559601</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>2368.44945259945</v>
+        <v>2368.44945259941</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>2368.44945259945</v>
+        <v>2368.44945259941</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>0.0244526864185115</v>
+        <v>0.0244526864185055</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>0.0529997426332931</v>
+        <v>0.0529997426332751</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>0.0247541051733253</v>
+        <v>0.0247541051733191</v>
       </c>
       <c r="R29" s="18" t="n">
         <v>1.00199828868163</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>1.20383346534131</v>
+        <v>1.20383268891907</v>
       </c>
     </row>
     <row r="30">
@@ -3303,46 +3303,46 @@
         <v>2935.63493973013</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>1.19162939212286</v>
+        <v>1.19162939212284</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>0.872461918319202</v>
+        <v>0.872461918316871</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>2429.79789895382</v>
+        <v>2429.79789895375</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>1925.02518143412</v>
+        <v>1925.02618967593</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>2016.60894832734</v>
+        <v>2016.60894981612</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>2463.54693760982</v>
+        <v>2463.54693760987</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>2459.24264996107</v>
+        <v>2459.24264996101</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>2400.54154181533</v>
+        <v>2400.54154181529</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>2400.54154181533</v>
+        <v>2400.54154181529</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>0.0134588526940031</v>
+        <v>0.0134588526940009</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>0.0397725713464117</v>
+        <v>0.0397725713463877</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>0.0135498307471444</v>
+        <v>0.0135498307471422</v>
       </c>
       <c r="R30" s="18" t="n">
-        <v>0.987959345445528</v>
+        <v>0.987959345445538</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>1.2470182546012</v>
+        <v>1.24701760146931</v>
       </c>
     </row>
     <row r="31">
@@ -3362,46 +3362,46 @@
         <v>2085.81764439801</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.899076837552717</v>
+        <v>0.899076837552728</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>2307.53924736264</v>
+        <v>2307.53924736258</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>1881.28969314399</v>
+        <v>1881.29034831345</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>1932.39114298624</v>
+        <v>1932.39114506962</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>2319.95482174316</v>
+        <v>2319.95482174313</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>2319.95482174316</v>
+        <v>2319.95482174313</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>2268.47340378077</v>
+        <v>2268.47340378073</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>2268.47340378077</v>
+        <v>2268.47340378073</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>-0.0565872584137494</v>
+        <v>-0.0565872584137486</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>-0.0194935843159186</v>
+        <v>-0.0194935843159345</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>-0.0550159769094</v>
+        <v>-0.0550159769093992</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>0.983070344902466</v>
+        <v>0.983070344902474</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>1.2058075968033</v>
+        <v>1.20580717687431</v>
       </c>
     </row>
     <row r="32">
@@ -3421,46 +3421,46 @@
         <v>1894.04001281739</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.959133225211585</v>
+        <v>0.959133225211607</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>1984.39953936687</v>
+        <v>1984.39953936685</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>1837.55305098486</v>
+        <v>1837.55324727382</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>1841.63578437285</v>
+        <v>1841.63578714537</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>1974.74132167569</v>
+        <v>1974.74132167564</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>1974.74132167569</v>
+        <v>1974.74132167564</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>1973.19864809586</v>
+        <v>1973.19864809583</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>1973.19864809586</v>
+        <v>1973.19864809583</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>-0.139451190665424</v>
+        <v>-0.139451190665419</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>-0.146258573203058</v>
+        <v>-0.146258573203061</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>-0.130164521740827</v>
+        <v>-0.130164521740823</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>0.994355526168593</v>
+        <v>0.994355526168591</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>1.07381860188379</v>
+        <v>1.07381848717758</v>
       </c>
     </row>
     <row r="33">
@@ -3480,25 +3480,25 @@
         <v>1574.64834843281</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.969995031877284</v>
+        <v>0.969995031877271</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>1620.24163556227</v>
+        <v>1620.24163556229</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>1795.42609873477</v>
+        <v>1795.42571652543</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>1749.98188787058</v>
+        <v>1749.98189141122</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>1623.3571272889</v>
+        <v>1623.35712728892</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>1623.3571272889</v>
+        <v>1623.35712728892</v>
       </c>
       <c r="M33" s="13" t="n">
         <v>1644.4417714242</v>
@@ -3507,19 +3507,19 @@
         <v>1644.4417714242</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>-0.182254927297115</v>
+        <v>-0.1822549272971</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>-0.30568846651155</v>
+        <v>-0.305688466511537</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>-0.166611140236138</v>
+        <v>-0.166611140236126</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>1.01493612763107</v>
+        <v>1.01493612763106</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>0.91590613090844</v>
+        <v>0.915906325886091</v>
       </c>
     </row>
     <row r="34">
@@ -3539,46 +3539,46 @@
         <v>1475.19763584073</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>1.1553972786314</v>
+        <v>1.15539727863137</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>1356.31150944332</v>
+        <v>1356.31150944334</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>1756.60542284096</v>
+        <v>1756.60432858311</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>1663.73399654932</v>
+        <v>1663.73400090767</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>1276.78822092098</v>
+        <v>1276.78822092102</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>1356.31150944332</v>
+        <v>1356.31150944334</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>1393.05245164078</v>
+        <v>1393.05245164079</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>1393.05245164078</v>
+        <v>1393.05245164079</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>-0.165903630132128</v>
+        <v>-0.165903630132125</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>-0.419692420491366</v>
+        <v>-0.419692420491352</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>-0.152872132143481</v>
+        <v>-0.152872132143478</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>1.02708886707932</v>
+        <v>1.02708886707931</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.793036633911672</v>
+        <v>0.79303712792535</v>
       </c>
     </row>
     <row r="35">
@@ -3598,46 +3598,46 @@
         <v>1124.55064572027</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.909661595862126</v>
+        <v>0.909661595862145</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>1226.10512660257</v>
+        <v>1226.10512660255</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1722.68006664348</v>
+        <v>1722.67811309348</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>1588.56352967608</v>
+        <v>1588.56353485462</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>1236.22966038759</v>
+        <v>1236.22966038756</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>1236.22966038759</v>
+        <v>1236.22966038756</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>1255.1439916979</v>
+        <v>1255.14399169789</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>1255.1439916979</v>
+        <v>1255.14399169789</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>-0.104247047392222</v>
+        <v>-0.10424704739224</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.446701032683034</v>
+        <v>-0.446701032683031</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>-0.0989973204386141</v>
+        <v>-0.0989973204386306</v>
       </c>
       <c r="R35" s="18" t="n">
         <v>1.02368382976735</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.728599590836075</v>
+        <v>0.728600417081968</v>
       </c>
     </row>
     <row r="36">
@@ -3657,46 +3657,46 @@
         <v>1152.15904543455</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.966734418302176</v>
+        <v>0.966734418302199</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>1196.4517387552</v>
+        <v>1196.45173875525</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>1694.98888978654</v>
+        <v>1694.98591669114</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>1528.60479408233</v>
+        <v>1528.60480001465</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>1191.80513657311</v>
+        <v>1191.80513657308</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>1191.80513657311</v>
+        <v>1191.80513657308</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>1209.78595673259</v>
+        <v>1209.78595673258</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>1209.78595673259</v>
+        <v>1209.78595673258</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>-0.0368068517243785</v>
+        <v>-0.0368068517243733</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>-0.386890945876109</v>
+        <v>-0.386890945876106</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>-0.0361377142904145</v>
+        <v>-0.0361377142904095</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>1.01114480220595</v>
+        <v>1.0111448022059</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>0.713742705938883</v>
+        <v>0.713743957881527</v>
       </c>
     </row>
     <row r="37">
@@ -3716,46 +3716,46 @@
         <v>1203.71436422561</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.987214402204921</v>
+        <v>0.987214402204881</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>1210.93719858977</v>
+        <v>1210.93719858975</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>1674.56672041044</v>
+        <v>1674.5625557278</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>1486.23042725308</v>
+        <v>1486.23043377799</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>1219.30389339656</v>
+        <v>1219.30389339661</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>1219.30389339656</v>
+        <v>1219.30389339661</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>1224.92526010863</v>
+        <v>1224.92526010845</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>1224.92526010863</v>
+        <v>1224.92526010845</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>0.0124363812806392</v>
+        <v>0.012436381280492</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>-0.25511180669671</v>
+        <v>-0.255111806696827</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>0.0125140346453769</v>
+        <v>0.0125140346452279</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>1.01155143432306</v>
+        <v>1.01155143432292</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>0.731487879926578</v>
+        <v>0.731489699156725</v>
       </c>
     </row>
     <row r="38">
@@ -3775,46 +3775,46 @@
         <v>1425.89524509937</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>1.12338185942588</v>
+        <v>1.12338185942661</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>1282.77625807608</v>
+        <v>1282.77625807403</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>1662.13389680969</v>
+        <v>1662.12835856756</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>1462.12906838582</v>
+        <v>1462.12907521768</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>1269.28811706831</v>
+        <v>1269.28811706749</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>1269.28811706831</v>
+        <v>1269.28811706749</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>1291.0366340799</v>
+        <v>1291.0366340788</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>1291.0366340799</v>
+        <v>1291.0366340788</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>0.0525656579969944</v>
+        <v>0.0525656579962992</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>-0.0732318567335534</v>
+        <v>-0.0732318567343461</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>0.0539717614815129</v>
+        <v>0.0539717614807802</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>1.00643945189335</v>
+        <v>1.00643945189411</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>0.77673443550963</v>
+        <v>0.776737023602337</v>
       </c>
     </row>
     <row r="39">
@@ -3834,46 +3834,46 @@
         <v>1290.38528816145</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.917596609077105</v>
+        <v>0.917596609078922</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>1403.09826440097</v>
+        <v>1403.09826440125</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>1658.12621801194</v>
+        <v>1658.11911691057</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>1455.65472400874</v>
+        <v>1455.65473070483</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>1406.26640878641</v>
+        <v>1406.26640878363</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>1406.26640878641</v>
+        <v>1406.26640878363</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>1398.2181674282</v>
+        <v>1398.21816742928</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>1398.2181674282</v>
+        <v>1398.21816742928</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>0.079753200475461</v>
+        <v>0.0797532004770873</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>0.113990248669996</v>
+        <v>0.113990248670875</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>0.0830197459305138</v>
+        <v>0.083019745932275</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>0.996521913613187</v>
+        <v>0.996521913613763</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>0.843251950448397</v>
+        <v>0.843255561780425</v>
       </c>
     </row>
     <row r="40">
@@ -3893,46 +3893,46 @@
         <v>1470.49652561565</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.973160939156016</v>
+        <v>0.973160939149098</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>1495.26012876762</v>
+        <v>1495.26012878051</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>1662.73395443251</v>
+        <v>1662.72509730606</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>1465.19719589346</v>
+        <v>1465.19720181982</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>1511.05173507165</v>
+        <v>1511.05173508239</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>1511.05173507165</v>
+        <v>1511.05173508239</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>1483.99351265599</v>
+        <v>1483.99351266427</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>1483.99351265599</v>
+        <v>1483.99351266427</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>0.0595380847584065</v>
+        <v>0.0595380847632135</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>0.226657909523085</v>
+        <v>0.226657909529943</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>0.0613461813227334</v>
+        <v>0.0613461813278353</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>0.992465112996145</v>
+        <v>0.992465112993132</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>0.892502079902778</v>
+        <v>0.892506834153546</v>
       </c>
     </row>
     <row r="41">
@@ -3952,46 +3952,46 @@
         <v>1506.23806134637</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.999093853430819</v>
+        <v>0.999093853421243</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>1520.18026157934</v>
+        <v>1520.18026157801</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>1675.98996410593</v>
+        <v>1675.97915836065</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>1488.89934423545</v>
+        <v>1488.89934853342</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>1507.60417169423</v>
+        <v>1507.60417170868</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>1507.60417169423</v>
+        <v>1507.60417170868</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>1515.30262778008</v>
+        <v>1515.30262777842</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>1515.30262778008</v>
+        <v>1515.30262777842</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>0.0208784001133644</v>
+        <v>0.0208784001066833</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.237057212491231</v>
+        <v>0.237057212490065</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>0.0210978787016802</v>
+        <v>0.0210978786948581</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>0.996791410911894</v>
+        <v>0.996791410911673</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>0.904123926892625</v>
+        <v>0.904129756160336</v>
       </c>
     </row>
     <row r="42">
@@ -4011,46 +4011,46 @@
         <v>1689.82206595359</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>1.10089683028068</v>
+        <v>1.10089683031388</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>1524.68175928561</v>
+        <v>1524.68175925254</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>1697.83230367964</v>
+        <v>1697.8193628296</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>1525.13330192613</v>
+        <v>1525.13330348269</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>1534.95043266021</v>
+        <v>1534.95043261392</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>1534.95043266021</v>
+        <v>1534.95043261392</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>1534.58697549591</v>
+        <v>1534.58697547355</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>1534.58697549591</v>
+        <v>1534.58697547355</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>0.0126461001714211</v>
+        <v>0.0126461001579471</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0.188647118901925</v>
+        <v>0.188647118885615</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>0.0127264002333833</v>
+        <v>0.0127264002197378</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>1.00649657946649</v>
+        <v>1.00649657947365</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>0.903850734946002</v>
+        <v>0.903857624120856</v>
       </c>
     </row>
     <row r="43">
@@ -4070,46 +4070,46 @@
         <v>1445.19764128156</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.925908477859672</v>
+        <v>0.925908477866382</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>1576.54392873646</v>
+        <v>1576.54392873864</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>1728.09378868083</v>
+        <v>1728.0785391015</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>1572.36472599416</v>
+        <v>1572.36472342061</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>1560.84286496898</v>
+        <v>1560.84286495767</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>1560.84286496898</v>
+        <v>1560.84286495767</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>1587.37988247282</v>
+        <v>1587.37988248048</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>1587.37988247282</v>
+        <v>1587.37988248048</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>0.0338235108431487</v>
+        <v>0.0338235108625443</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.135287696477697</v>
+        <v>0.135287696482292</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>0.0344020298750765</v>
+        <v>0.0344020298951393</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>1.00687323298695</v>
+        <v>1.00687323299041</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>0.918572760847996</v>
+        <v>0.91858086687763</v>
       </c>
     </row>
     <row r="44">
@@ -4129,46 +4129,46 @@
         <v>1649.16622342598</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.974175926876139</v>
+        <v>0.974175926818855</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>1690.86540275746</v>
+        <v>1690.86540285764</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>1766.50543346729</v>
+        <v>1766.48772248355</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>1629.1083591219</v>
+        <v>1629.10835074577</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>1692.88336729312</v>
+        <v>1692.88336739267</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>1692.88336729312</v>
+        <v>1692.88336739267</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>1692.86247568537</v>
+        <v>1692.86247575298</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>1692.86247568537</v>
+        <v>1692.86247575298</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>0.0643360843768011</v>
+        <v>0.0643360844119153</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.140747894952423</v>
+        <v>0.140747894991613</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>0.0664507559767129</v>
+        <v>0.0664507560141605</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>1.00118109515083</v>
+        <v>1.0011810951315</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>0.958311502253706</v>
+        <v>0.958321110419573</v>
       </c>
     </row>
     <row r="45">
@@ -4188,46 +4188,46 @@
         <v>1834.94060897935</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>1.00553489846507</v>
+        <v>1.00553489841952</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>1815.76599813348</v>
+        <v>1815.76599813184</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>1812.69372056949</v>
+        <v>1812.67342598662</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>1693.82133468657</v>
+        <v>1693.82131856448</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>1824.84030318625</v>
+        <v>1824.84030326891</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>1824.84030318625</v>
+        <v>1824.84030326891</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>1806.07089441468</v>
+        <v>1806.07089443793</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>1806.07089441468</v>
+        <v>1806.07089443793</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>0.0647328404457326</v>
+        <v>0.0647328404186689</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.19188791816495</v>
+        <v>0.191887918181603</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>0.0668739607353399</v>
+        <v>0.0668739607064663</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>0.994660598486388</v>
+        <v>0.994660598500093</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>0.996346417445121</v>
+        <v>0.996357572492635</v>
       </c>
     </row>
     <row r="46">
@@ -4247,46 +4247,46 @@
         <v>1933.00273454338</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>1.08672517802431</v>
+        <v>1.08672517818172</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>1881.71960399311</v>
+        <v>1881.71960382125</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>1866.23911872655</v>
+        <v>1866.21615989963</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>1765.27966110626</v>
+        <v>1765.27963506627</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>1778.741096307</v>
+        <v>1778.74109604935</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>1881.71960399311</v>
+        <v>1881.71960382125</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>1868.43026789247</v>
+        <v>1868.43026782004</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>1868.43026789247</v>
+        <v>1868.43026782004</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0.0339449402537448</v>
+        <v>0.0339449402021037</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0.217546022302632</v>
+        <v>0.217546022273174</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>0.0345276443303739</v>
+        <v>0.0345276442769498</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>0.992937664000291</v>
+        <v>0.992937664052485</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>1.00117409883007</v>
+        <v>1.00118641557606</v>
       </c>
     </row>
     <row r="47">
@@ -4306,46 +4306,46 @@
         <v>1888.09456688716</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.935898062546897</v>
+        <v>0.935898062565543</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>1885.44156039742</v>
+        <v>1885.44156036875</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>1926.72968829174</v>
+        <v>1926.70403880985</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>1842.91444164155</v>
+        <v>1842.91440336419</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>2017.41476176264</v>
+        <v>2017.41476172244</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>1885.44156039742</v>
+        <v>1885.44156036875</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>1882.13005534214</v>
+        <v>1882.13005537053</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>1882.13005534214</v>
+        <v>1882.13005537053</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>0.00730549421899846</v>
+        <v>0.00730549427284955</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>0.185683449893641</v>
+        <v>0.185683449905806</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>0.00733224444341696</v>
+        <v>0.0073322444976629</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>0.998243644817831</v>
+        <v>0.998243644848068</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>0.976852158753445</v>
+        <v>0.976865163231374</v>
       </c>
     </row>
     <row r="48">
@@ -4365,46 +4365,46 @@
         <v>1827.0050126273</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>0.97392610067209</v>
+        <v>0.973926100494134</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>1899.24725088796</v>
+        <v>1899.24725122733</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>1993.7631649216</v>
+        <v>1993.73486695694</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>1926.73897926745</v>
+        <v>1926.73892641507</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>1875.9174965806</v>
+        <v>1875.91749692337</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>1875.9174965806</v>
+        <v>1875.91749692337</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>1901.01907186328</v>
+        <v>1901.01907210635</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>1901.01907186328</v>
+        <v>1901.01907210635</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>0.00998595236523152</v>
+        <v>0.00998595247800682</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>0.122961315031594</v>
+        <v>0.122961315130327</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>0.0100359783679822</v>
+        <v>0.0100359784818893</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>1.000932906958</v>
+        <v>1.00093290690713</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>0.953482893710716</v>
+        <v>0.953496427038914</v>
       </c>
     </row>
     <row r="49">
@@ -4424,46 +4424,46 @@
         <v>1977.85475412658</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1.00562081641642</v>
+        <v>1.00562081625516</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>1942.45703125003</v>
+        <v>1942.45703142052</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>2066.91147919273</v>
+        <v>2066.88065953157</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>2016.97921255276</v>
+        <v>2016.97914296076</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>1966.7997338945</v>
+        <v>1966.79973420989</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>1966.7997338945</v>
+        <v>1966.79973420989</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>1953.47061651255</v>
+        <v>1953.47061660227</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>1953.47061651255</v>
+        <v>1953.47061660227</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>0.0272174979437882</v>
+        <v>0.0272174978618555</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>0.0816134751707167</v>
+        <v>0.0816134752064666</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>0.0275912774498661</v>
+        <v>0.0275912773656728</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>1.00566992478358</v>
+        <v>1.0056699247415</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>0.945115761452692</v>
+        <v>0.945129854301791</v>
       </c>
     </row>
     <row r="50">
@@ -4483,46 +4483,46 @@
         <v>2160.36159801246</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>1.07782816866538</v>
+        <v>1.07782816899592</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>2031.37413006628</v>
+        <v>2031.37412934923</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>2145.67290813903</v>
+        <v>2145.63979586813</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>2113.60697265283</v>
+        <v>2113.60688459564</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>2004.36550168059</v>
+        <v>2004.36550106591</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>2004.36550168059</v>
+        <v>2004.36550106591</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>2032.5743526221</v>
+        <v>2032.57435215072</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>2032.5743526221</v>
+        <v>2032.57435215072</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>0.039695549684374</v>
+        <v>0.0396955494065331</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>0.0878513303655597</v>
+        <v>0.087851330155444</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>0.0404939472551562</v>
+        <v>0.0404939469660643</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>1.00059084269021</v>
+        <v>1.00059084281135</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>0.947289936370116</v>
+        <v>0.947304555063186</v>
       </c>
     </row>
     <row r="51">
@@ -4542,46 +4542,46 @@
         <v>2033.21078101257</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0.943587445578132</v>
+        <v>0.943587446003581</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>2130.76088732823</v>
+        <v>2130.76088721351</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>2229.48315895359</v>
+        <v>2229.44810472267</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>2216.34319332974</v>
+        <v>2216.34308587037</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>2154.76667323273</v>
+        <v>2154.76667226118</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>2154.76667323273</v>
+        <v>2154.76667226118</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>2132.55554347028</v>
+        <v>2132.55554335949</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>2132.55554347028</v>
+        <v>2132.55554335949</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>0.0480179025938594</v>
+        <v>0.0480179027738232</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>0.133054295274307</v>
+        <v>0.133054295198353</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>0.0491894383687341</v>
+        <v>0.0491894385575502</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>1.00084226069322</v>
+        <v>1.00084226069511</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>0.956524625407439</v>
+        <v>0.956539665059738</v>
       </c>
     </row>
     <row r="52">
@@ -4601,46 +4601,46 @@
         <v>2167.47837936594</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0.977961272255745</v>
+        <v>0.97796127132265</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>2221.35218889344</v>
+        <v>2221.35218985207</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>2317.68962170046</v>
+        <v>2317.65311841702</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>2324.36260099069</v>
+        <v>2324.36247441793</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>2216.32332573505</v>
+        <v>2216.3233278497</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>2216.32332573505</v>
+        <v>2216.3233278497</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>2225.42620061018</v>
+        <v>2225.42620138575</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>2225.42620061018</v>
+        <v>2225.42620138575</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>0.0426274018902406</v>
+        <v>0.0426274022906919</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>0.17064906583443</v>
+        <v>0.170649066092723</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>0.0435489980198962</v>
+        <v>0.0435489984377868</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>1.00183402332017</v>
+        <v>1.00183402323697</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.960191640750163</v>
+        <v>0.960206764205394</v>
       </c>
     </row>
     <row r="53">
@@ -4660,46 +4660,46 @@
         <v>2312.92176137013</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>0.999408148722431</v>
+        <v>0.999408148789573</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>2327.80013633988</v>
+        <v>2327.8001369125</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>2409.59298864011</v>
+        <v>2409.5556933777</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>2436.53203944241</v>
+        <v>2436.53189580326</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>2314.2914777379</v>
+        <v>2314.29147758242</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>2314.2914777379</v>
+        <v>2314.29147758242</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>2337.5862755447</v>
+        <v>2337.58627578624</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>2337.5862755447</v>
+        <v>2337.58627578624</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>0.0491704427127876</v>
+        <v>0.0491704424676108</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>0.196632422205512</v>
+        <v>0.196632422274195</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>0.0503993684013275</v>
+        <v>0.050399368143794</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>1.00420402896797</v>
+        <v>1.00420402882471</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>0.970116648979775</v>
+        <v>0.970131664609679</v>
       </c>
     </row>
     <row r="54">
@@ -4719,46 +4719,46 @@
         <v>2696.86049566001</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>1.07640245416892</v>
+        <v>1.07640245452876</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>2491.07623389076</v>
+        <v>2491.07623199219</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>2504.43059809804</v>
+        <v>2504.39335491212</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>2551.17815611533</v>
+        <v>2551.17799985847</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>2505.43882096797</v>
+        <v>2505.43882013041</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>2505.43882096797</v>
+        <v>2505.43882013041</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>2496.93177551397</v>
+        <v>2496.93177433051</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>2496.93177551397</v>
+        <v>2496.93177433051</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>0.0659437975193464</v>
+        <v>0.0659437969420579</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>0.228457779314603</v>
+        <v>0.228457779017254</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>0.0681666818616704</v>
+        <v>0.0681666812450301</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>1.00235060715668</v>
+        <v>1.00235060744554</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>0.997005777445073</v>
+        <v>0.997020603585704</v>
       </c>
     </row>
     <row r="55">
@@ -4778,46 +4778,46 @@
         <v>2516.13485121782</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.945006594360355</v>
+        <v>0.945006595390775</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>2671.90894111614</v>
+        <v>2671.90894083506</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>2601.38022495544</v>
+        <v>2601.34408819285</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>2666.01639563139</v>
+        <v>2666.01623432455</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>2662.55798238203</v>
+        <v>2662.55797947882</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>2662.55798238203</v>
+        <v>2662.55797947882</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>2671.1502830015</v>
+        <v>2671.15028262202</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>2671.1502830015</v>
+        <v>2671.15028262202</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>0.0674465088976016</v>
+        <v>0.0674465092294979</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>0.252558364156262</v>
+        <v>0.252558364043385</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>0.0697730347284613</v>
+        <v>0.0697730350835151</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>0.999716061388559</v>
+        <v>0.9997160613517</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>1.02682039994644</v>
+        <v>1.02683466395161</v>
       </c>
     </row>
     <row r="56">
@@ -4837,46 +4837,46 @@
         <v>2803.88411969971</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.982424172389578</v>
+        <v>0.98242417062508</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>2842.79402571247</v>
+        <v>2842.79402753187</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>2699.62027423276</v>
+        <v>2699.58653180817</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>2778.53350593676</v>
+        <v>2778.53335104386</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>2854.04634627397</v>
+        <v>2854.04635140003</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>2854.04634627397</v>
+        <v>2854.04635140003</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>2847.90020489601</v>
+        <v>2847.90020648769</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>2847.90020489601</v>
+        <v>2847.90020648769</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>0.0640727552796136</v>
+        <v>0.0640727559805762</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>0.279710018743892</v>
+        <v>0.279710019013135</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>0.0661699654337293</v>
+        <v>0.0661699661810746</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>1.00179618331028</v>
+        <v>1.00179618322902</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>1.05492621761606</v>
+        <v>1.05493940384277</v>
       </c>
     </row>
     <row r="57">
@@ -4896,46 +4896,46 @@
         <v>3010.33905330945</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>0.996487498688655</v>
+        <v>0.996487499012638</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>3034.64093815868</v>
+        <v>3034.64093968749</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>2798.3673870489</v>
+        <v>2798.33758302846</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>2886.19894291138</v>
+        <v>2886.19881058453</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>3020.95014465405</v>
+        <v>3020.95014367187</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>3020.95014465405</v>
+        <v>3020.95014367187</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>3038.37703366664</v>
+        <v>3038.37703435034</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>3038.37703366664</v>
+        <v>3038.37703435034</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>0.0647415498340633</v>
+        <v>0.064741549500191</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>0.299792467749081</v>
+        <v>0.299792467907264</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>0.066883252595427</v>
+        <v>0.0668832522392242</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>1.00123114911586</v>
+        <v>1.00123114883675</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>1.08576774005033</v>
+        <v>1.08577930439047</v>
       </c>
     </row>
     <row r="58">
@@ -4955,46 +4955,46 @@
         <v>3500.76983696121</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>1.07465963050739</v>
+        <v>1.07465963064821</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>3256.79647442638</v>
+        <v>3256.79647329729</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>2896.93472081772</v>
+        <v>2896.91067651132</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>2986.85972663688</v>
+        <v>2986.85963851648</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>3257.56149908446</v>
+        <v>3257.5614986576</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>3257.56149908446</v>
+        <v>3257.5614986576</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>3251.94752631711</v>
+        <v>3251.94752420705</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>3251.94752631711</v>
+        <v>3251.94752420705</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0.0679305533823994</v>
+        <v>0.0679305525085143</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>0.302377405024506</v>
+        <v>0.302377404796722</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>0.0702909778095402</v>
+        <v>0.0702909768742288</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>0.99851112952641</v>
+        <v>0.998511129224685</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>1.12254774087529</v>
+        <v>1.12255705727292</v>
       </c>
     </row>
     <row r="59">
@@ -5014,46 +5014,46 @@
         <v>3286.26557559881</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>0.946582227510843</v>
+        <v>0.946582229311556</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>3484.64703377109</v>
+        <v>3484.64702324328</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>2994.77454717665</v>
+        <v>2994.75837976477</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>3079.0366332036</v>
+        <v>3079.03661707504</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>3471.71696244547</v>
+        <v>3471.71695584112</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>3471.71696244547</v>
+        <v>3471.71695584112</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>3446.62982254225</v>
+        <v>3446.62981382275</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>3446.62982254225</v>
+        <v>3446.62981382275</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>0.0581428348338555</v>
+        <v>0.0581428329528561</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>0.290316701563254</v>
+        <v>0.290316698482243</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>0.0598663707361899</v>
+        <v>0.059866368742582</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>0.989090082622314</v>
+        <v>0.989090083108291</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.15088123270969</v>
+        <v>1.15088744291066</v>
       </c>
     </row>
     <row r="60">
@@ -5073,46 +5073,46 @@
         <v>3537.71845126756</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>0.98147910341908</v>
+        <v>0.981479099042537</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>0.742575131382382</v>
+        <v>0.74257472500752</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>3530.85229927458</v>
+        <v>3530.85228661603</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>3091.56452949947</v>
+        <v>3091.55866706065</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>3162.60394756411</v>
+        <v>3162.60403779627</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>3604.47658940834</v>
+        <v>3604.47660548117</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>3585.52386619359</v>
+        <v>3585.52384495117</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>3493.08787355111</v>
+        <v>3493.08786101514</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>3493.08787355111</v>
+        <v>3493.08786101514</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>0.0133892319808456</v>
+        <v>0.013389230921915</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0.226548552349523</v>
+        <v>0.226548547262183</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>0.0134792691414103</v>
+        <v>0.0134792680682061</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>0.989304444784838</v>
+        <v>0.989304444781211</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.12987707040249</v>
+        <v>1.12987920890282</v>
       </c>
     </row>
     <row r="61">
@@ -5132,46 +5132,46 @@
         <v>3321.73023465199</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>0.997640378463397</v>
+        <v>0.997640378779409</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>3366.34119010791</v>
+        <v>3366.34117248951</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>3187.28042016956</v>
+        <v>3187.28761178087</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>3239.39935631719</v>
+        <v>3239.39959391006</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>3329.58679937178</v>
+        <v>3329.5867983171</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>3329.58679937178</v>
+        <v>3329.5867983171</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>3348.60872454175</v>
+        <v>3348.60870977978</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>3348.60872454175</v>
+        <v>3348.60870977978</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>-0.0422411690846658</v>
+        <v>-0.0422411699042642</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>0.102104408846436</v>
+        <v>0.10210440373993</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>-0.0413614412919064</v>
+        <v>-0.0413614420776051</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>0.994732421770478</v>
+        <v>0.994732422591434</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>1.0506162882159</v>
+        <v>1.05061391303459</v>
       </c>
     </row>
     <row r="62">
@@ -5191,46 +5191,46 @@
         <v>3386.00448971788</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>1.07501166732039</v>
+        <v>1.07501167950355</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>3121.46614936826</v>
+        <v>3121.46612131112</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>3282.2066961557</v>
+        <v>3282.23001554349</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>3313.37514565478</v>
+        <v>3313.37557768206</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>3149.73743322986</v>
+        <v>3149.73739753374</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>3149.73743322986</v>
+        <v>3149.73739753374</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>3160.84312145752</v>
+        <v>3160.84311165646</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>3160.84312145752</v>
+        <v>3160.84311165646</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>-0.0577061508675421</v>
+        <v>-0.0577061495599252</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>-0.0280153366935699</v>
+        <v>-0.0280153390767903</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>-0.0560727210999938</v>
+        <v>-0.0560727198656986</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>1.01261489639964</v>
+        <v>1.01261490236159</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>0.963023786758971</v>
+        <v>0.963016941740162</v>
       </c>
     </row>
     <row r="63">
@@ -5250,46 +5250,46 @@
         <v>2696.05052423399</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>0.94959865465256</v>
+        <v>0.949598657368717</v>
       </c>
       <c r="G63" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>3014.31081999856</v>
+        <v>3014.31085324126</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>3376.71677591369</v>
+        <v>3376.7596169582</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>3388.93453898408</v>
+        <v>3388.93521739996</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>2839.14737139179</v>
+        <v>2839.14736327091</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>3014.31081999856</v>
+        <v>3014.31085324126</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>3076.24956546887</v>
+        <v>3076.24960782439</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>3076.24956546887</v>
+        <v>3076.24960782439</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>-0.0271276211294257</v>
+        <v>-0.0271276042600945</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>-0.10746157148962</v>
+        <v>-0.107461556942654</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>-0.0267629720103414</v>
+        <v>-0.0267629555924834</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>1.02054822782686</v>
+        <v>1.02054823062344</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>0.911017941277141</v>
+        <v>0.911006395710065</v>
       </c>
     </row>
     <row r="64">
@@ -5309,46 +5309,46 @@
         <v>3036.48849479411</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>0.97116690209037</v>
+        <v>0.971166859029569</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>3133.76534396598</v>
+        <v>3133.76543934477</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>3471.10128460997</v>
+        <v>3471.16734674839</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>3469.66257115017</v>
+        <v>3469.66355045072</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>3126.6391886485</v>
+        <v>3126.6393272813</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>3126.6391886485</v>
+        <v>3126.6393272813</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>3166.13353624204</v>
+        <v>3166.13360834461</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>3166.13353624204</v>
+        <v>3166.13360834461</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>0.02879995731896</v>
+        <v>0.0287999663234681</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>-0.0936003756975855</v>
+        <v>-0.0936003518032074</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>0.0292186862152304</v>
+        <v>0.0292186954828384</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>1.01032885003288</v>
+        <v>1.01032884229096</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>0.912140924921989</v>
+        <v>0.912123586121677</v>
       </c>
     </row>
     <row r="65">
@@ -5368,46 +5368,46 @@
         <v>3418.10930449306</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.00623040913128</v>
+        <v>1.00623041567708</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>3353.10023119716</v>
+        <v>3353.10017275911</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>3565.42434368858</v>
+        <v>3565.51760516016</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>3557.27115840321</v>
+        <v>3557.27249240048</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>3396.94494767262</v>
+        <v>3396.94492557458</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>3396.94494767262</v>
+        <v>3396.94492557458</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>3351.26137129933</v>
+        <v>3351.26132339571</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>3351.26137129933</v>
+        <v>3351.26132339571</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>0.0568256649253215</v>
+        <v>0.056825627858051</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>0.000792163843489124</v>
+        <v>0.000792153949843666</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>0.058471265642515</v>
+        <v>0.0584712264078751</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>0.999451594115582</v>
+        <v>0.999451597247724</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>0.939933384712437</v>
+        <v>0.939908785906885</v>
       </c>
     </row>
     <row r="66">
@@ -5427,46 +5427,46 @@
         <v>3735.59369195447</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>1.0720551324322</v>
+        <v>1.07205522043944</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>3532.2334807144</v>
+        <v>3532.2332618115</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>3659.53478578355</v>
+        <v>3659.65946242742</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>3651.75710008084</v>
+        <v>3651.75883769957</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>3484.51640120357</v>
+        <v>3484.51611515238</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>3484.51640120357</v>
+        <v>3484.51611515238</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>3513.09723640087</v>
+        <v>3513.09710496147</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>3513.09723640087</v>
+        <v>3513.09710496147</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>0.0471612482077777</v>
+        <v>0.0471612250878732</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>0.111443086989058</v>
+        <v>0.111443048851739</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>0.0482910305019866</v>
+        <v>0.0482910062655983</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>0.994582395411286</v>
+        <v>0.994582419837071</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>0.959984654346899</v>
+        <v>0.959951913840437</v>
       </c>
     </row>
     <row r="67">
@@ -5486,46 +5486,46 @@
         <v>3551.93509050901</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>0.956071136652159</v>
+        <v>0.956071133078347</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>0.680771274598217</v>
+        <v>0.680771368515559</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>3625.1523417104</v>
+        <v>3625.15250002222</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>3753.1761439064</v>
+        <v>3753.33663085936</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>3752.31556446706</v>
+        <v>3752.31774296416</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>3715.13682856978</v>
+        <v>3715.13684245704</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>3686.41119552373</v>
+        <v>3686.41126396654</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>3624.61575107763</v>
+        <v>3624.61589297286</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>3624.61575107763</v>
+        <v>3624.61589297286</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>0.0312502310638873</v>
+        <v>0.0312503076256594</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>0.178258029440851</v>
+        <v>0.178258059343986</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>0.0317436458977727</v>
+        <v>0.0317437248898975</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>0.999851981218389</v>
+        <v>0.999851976696331</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>0.965746240544157</v>
+        <v>0.965704984512135</v>
       </c>
     </row>
     <row r="68">
@@ -5545,46 +5545,46 @@
         <v>3501.98814428698</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>0.961787607434078</v>
+        <v>0.961787418108546</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>3682.59068640353</v>
+        <v>3682.59115582795</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>3845.98256457832</v>
+        <v>3846.1833581731</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>3857.30551635146</v>
+        <v>3857.3081511977</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>3641.12421205948</v>
+        <v>3641.12492880599</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>3641.12421205948</v>
+        <v>3641.12492880599</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>3693.38068702193</v>
+        <v>3693.38102731178</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>3693.38068702193</v>
+        <v>3693.38102731178</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.018793930979115</v>
+        <v>0.0187939839665086</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>0.166527136251393</v>
+        <v>0.166527217164041</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.0189716484909768</v>
+        <v>0.01897170248363</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>1.00293000269029</v>
+        <v>1.00292996725057</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>0.960321744835283</v>
+        <v>0.96027169881628</v>
       </c>
     </row>
     <row r="69">
@@ -5604,46 +5604,46 @@
         <v>3831.21508377001</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1.0069258615712</v>
+        <v>1.00692589882653</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>3803.1164493572</v>
+        <v>3803.11627358847</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>3937.54646622772</v>
+        <v>3937.79206373146</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>3964.75639867893</v>
+        <v>3964.75947300864</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>3804.86312844503</v>
+        <v>3804.86298766861</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>3804.86312844503</v>
+        <v>3804.86298766861</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>3827.81265395562</v>
+        <v>3827.81249593353</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>3827.81265395562</v>
+        <v>3827.81249593353</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>0.0357513174554632</v>
+        <v>0.0357511840377989</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>0.142200571622834</v>
+        <v>0.142200540796665</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>0.0363980803295103</v>
+        <v>0.0363979420557083</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>1.0064936756282</v>
+        <v>1.00649368059467</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>0.972131424171552</v>
+        <v>0.972070752843736</v>
       </c>
     </row>
     <row r="70">
@@ -5663,46 +5663,46 @@
         <v>4375.22212253129</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>1.07753471684332</v>
+        <v>1.07753500007494</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>4057.13949596517</v>
+        <v>4057.13858979235</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>4027.33223081271</v>
+        <v>4027.62700537892</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>4071.61674787291</v>
+        <v>4071.62020289349</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>4060.40014687292</v>
+        <v>4060.39907959092</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>4060.40014687292</v>
+        <v>4060.39907959092</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>4060.53359852201</v>
+        <v>4060.53300058404</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>4060.53359852201</v>
+        <v>4060.53300058404</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>0.0590208617649748</v>
+        <v>0.0590207557915653</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0.155827272996854</v>
+        <v>0.155827146038588</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>0.0607973706147558</v>
+        <v>0.0607972581984475</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>1.00083657526694</v>
+        <v>1.00083665142725</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>1.0082440101304</v>
+        <v>1.00817007015823</v>
       </c>
     </row>
     <row r="71">
@@ -5722,46 +5722,46 @@
         <v>4129.41074094782</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>0.956663618922213</v>
+        <v>0.956663644722589</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>4305.68043739183</v>
+        <v>4305.68071809192</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>4114.72131320528</v>
+        <v>4115.06936028742</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>4174.03563400565</v>
+        <v>4174.03935292203</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>4316.47097189716</v>
+        <v>4316.47085548574</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>4316.47097189716</v>
+        <v>4316.47085548574</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>4304.89008968019</v>
+        <v>4304.89038066416</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>4304.89008968019</v>
+        <v>4304.89038066416</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>0.0584372135162203</v>
+        <v>0.058437428366058</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>0.187681780724014</v>
+        <v>0.187681814508998</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>0.0601784187297751</v>
+        <v>0.0601786465089609</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>0.999816440694302</v>
+        <v>0.999816443094715</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>1.0462166844361</v>
+        <v>1.04612826753508</v>
       </c>
     </row>
     <row r="72">
@@ -5781,46 +5781,46 @@
         <v>4333.19154339499</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>0.957353641997135</v>
+        <v>0.957353120820965</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>4565.45027665089</v>
+        <v>4565.45239992308</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>4199.11583572495</v>
+        <v>4199.52078817524</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>4268.10604414442</v>
+        <v>4268.10982954756</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>4526.21826805351</v>
+        <v>4526.22073209426</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>4526.21826805351</v>
+        <v>4526.22073209426</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>4539.66225278623</v>
+        <v>4539.6637102036</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>4539.66225278623</v>
+        <v>4539.6637102036</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>0.0531010089251677</v>
+        <v>0.0531012623722224</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>0.229134670232621</v>
+        <v>0.229134951588731</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>0.0545361573037244</v>
+        <v>0.0545364245728415</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>0.994351482920195</v>
+        <v>0.994351339700769</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>1.08109955294969</v>
+        <v>1.08099565145293</v>
       </c>
     </row>
     <row r="73">
@@ -5840,46 +5840,46 @@
         <v>4811.64490558585</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>1.00457298216005</v>
+        <v>1.00457276865072</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>4727.16775207854</v>
+        <v>4727.16729410256</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>4280.04401422794</v>
+        <v>4280.50882469521</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>4350.63314204592</v>
+        <v>4350.63669673618</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>4789.74150314074</v>
+        <v>4789.74252114016</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>4789.74150314074</v>
+        <v>4789.74252114016</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>4694.63470650351</v>
+        <v>4694.63446409654</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>4694.63470650351</v>
+        <v>4694.63446409654</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>0.0335676892152024</v>
+        <v>0.033567316539431</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>0.226453625323626</v>
+        <v>0.226453612627024</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>0.0341374413090247</v>
+        <v>0.0341370559111278</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>0.993117856763022</v>
+        <v>0.993117901698422</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>1.09686598803596</v>
+        <v>1.09674682528679</v>
       </c>
     </row>
     <row r="74">
@@ -5899,46 +5899,46 @@
         <v>5066.12763917827</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>1.08416515300385</v>
+        <v>1.08416642204643</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>4698.72800139924</v>
+        <v>4698.72539565374</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>4357.23850359065</v>
+        <v>4357.76519296509</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>4419.71265258642</v>
+        <v>4419.71557296672</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>4672.83755167907</v>
+        <v>4672.83208201159</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>4672.83755167907</v>
+        <v>4672.83208201159</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>4682.22869752653</v>
+        <v>4682.22673901443</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>4682.22869752653</v>
+        <v>4682.22673901443</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>-0.00264609084746818</v>
+        <v>-0.00264645749895483</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0.153106749130413</v>
+        <v>0.153106436603511</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>-0.00264259303493841</v>
+        <v>-0.00264295871744735</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>0.996488559485078</v>
+        <v>0.996488695284349</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>1.07458627607097</v>
+        <v>1.07445594970861</v>
       </c>
     </row>
     <row r="75">
@@ -5958,46 +5958,46 @@
         <v>4383.03555041862</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>0.954182493433938</v>
+        <v>0.954182059853283</v>
       </c>
       <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>4617.37007192823</v>
+        <v>4617.37046737778</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>4430.75051962008</v>
+        <v>4431.33988716292</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>4475.63584244766</v>
+        <v>4475.63760584005</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>4593.49818360724</v>
+        <v>4593.50027089438</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>4593.49818360724</v>
+        <v>4593.50027089438</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>4619.23645503496</v>
+        <v>4619.23707406685</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>4619.23645503496</v>
+        <v>4619.23707406685</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>-0.0135447920320336</v>
+        <v>-0.0135442397339241</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>0.0730207644809178</v>
+        <v>0.0730208357487128</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>-0.0134534740955401</v>
+        <v>-0.0134529292276084</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>1.00040420912287</v>
+        <v>1.00040425751026</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>1.0425404081273</v>
+        <v>1.04240189010287</v>
       </c>
     </row>
     <row r="76">
@@ -6017,46 +6017,46 @@
         <v>4429.87614408065</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>0.959447429221911</v>
+        <v>0.959446645553423</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>4562.08375906755</v>
+        <v>4562.08829656908</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>4500.82852752827</v>
+        <v>4501.47981827239</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>4519.95960280684</v>
+        <v>4519.95952550224</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>4617.1119012463</v>
+        <v>4617.11567246706</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>4617.1119012463</v>
+        <v>4617.11567246706</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>4577.9192023042</v>
+        <v>4577.9222861633</v>
       </c>
       <c r="N76" s="14" t="n">
-        <v>4577.9192023042</v>
+        <v>4577.9222861633</v>
       </c>
       <c r="O76" s="15" t="n">
-        <v>-0.00898484971290129</v>
+        <v>-0.00898431008712427</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>0.00842726779828062</v>
+        <v>0.0084276233663978</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>-0.0089446065671136</v>
+        <v>-0.00894407176793255</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>1.00347109875069</v>
+        <v>1.00347077666299</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.01712810748164</v>
+        <v>1.016981630703</v>
       </c>
     </row>
     <row r="77">
@@ -6076,46 +6076,46 @@
         <v>4465.28611985202</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>0.995836554113189</v>
+        <v>0.995835953205919</v>
       </c>
       <c r="G77" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>4554.38623603062</v>
+        <v>4554.38624023972</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>4567.82270981725</v>
+        <v>4568.53324751702</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>4554.83013654696</v>
+        <v>4554.82737542465</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>4483.95482311697</v>
+        <v>4483.95752882472</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>4483.95482311697</v>
+        <v>4483.95752882472</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>4567.18887598509</v>
+        <v>4567.18906622118</v>
       </c>
       <c r="N77" s="14" t="n">
-        <v>4567.18887598509</v>
+        <v>4567.18906622118</v>
       </c>
       <c r="O77" s="15" t="n">
-        <v>-0.00234668221556364</v>
+        <v>-0.00234731420029296</v>
       </c>
       <c r="P77" s="16" t="n">
-        <v>-0.0271471240013353</v>
+        <v>-0.0271470332461524</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>-0.00234393090942109</v>
+        <v>-0.00234456141262263</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>1.00281105714162</v>
+        <v>1.0028110979847</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>0.999861239397318</v>
+        <v>0.999705773992873</v>
       </c>
     </row>
     <row r="78">
@@ -6135,46 +6135,46 @@
         <v>5131.88191643965</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>1.09568177102831</v>
+        <v>1.0956837411468</v>
       </c>
       <c r="G78" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>4645.69566136202</v>
+        <v>4645.69110930167</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>4632.15592609762</v>
+        <v>4632.92070852923</v>
       </c>
       <c r="J78" s="10" t="n">
-        <v>4582.8794080432</v>
+        <v>4582.87297981346</v>
       </c>
       <c r="K78" s="11" t="n">
-        <v>4683.73395646012</v>
+        <v>4683.72553476823</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>4683.73395646012</v>
+        <v>4683.72553476823</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>4649.59256955151</v>
+        <v>4649.58900223759</v>
       </c>
       <c r="N78" s="14" t="n">
-        <v>4649.59256955151</v>
+        <v>4649.58900223759</v>
       </c>
       <c r="O78" s="15" t="n">
-        <v>0.0178817062754435</v>
+        <v>0.0178808973908653</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>-0.00697021228208139</v>
+        <v>-0.00697055879521802</v>
       </c>
       <c r="Q78" s="17" t="n">
-        <v>0.0180425412226137</v>
+        <v>0.0180417177440353</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>1.00083882123874</v>
+        <v>1.0008390340305</v>
       </c>
       <c r="S78" s="19" t="n">
-        <v>1.00376426090401</v>
+        <v>1.00359779386633</v>
       </c>
     </row>
     <row r="79">
@@ -6194,46 +6194,46 @@
         <v>4499.44907972728</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>0.947861555190371</v>
+        <v>0.947861581463955</v>
       </c>
       <c r="G79" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>4743.10978284322</v>
+        <v>4743.1062120753</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>4694.19861855082</v>
+        <v>4695.00987511721</v>
       </c>
       <c r="J79" s="10" t="n">
-        <v>4606.38500510362</v>
+        <v>4606.37381364184</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>4746.94754216885</v>
+        <v>4746.94741058917</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>4746.94754216885</v>
+        <v>4746.94741058917</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>4724.94205355565</v>
+        <v>4724.94097102942</v>
       </c>
       <c r="N79" s="14" t="n">
-        <v>4724.94205355565</v>
+        <v>4724.94097102942</v>
       </c>
       <c r="O79" s="15" t="n">
-        <v>0.0160757007635902</v>
+        <v>0.0160762388864782</v>
       </c>
       <c r="P79" s="16" t="n">
-        <v>0.0228837816703391</v>
+        <v>0.0228834102401911</v>
       </c>
       <c r="Q79" s="17" t="n">
-        <v>0.0162056100350758</v>
+        <v>0.0162061568787206</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>0.996169658700862</v>
+        <v>0.996170180418978</v>
       </c>
       <c r="S79" s="19" t="n">
-        <v>1.00654924035028</v>
+        <v>1.0063750868919</v>
       </c>
     </row>
     <row r="80">
@@ -6253,46 +6253,46 @@
         <v>4539.76782551238</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>0.961379505936897</v>
+        <v>0.961378619355652</v>
       </c>
       <c r="G80" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>4739.22273086162</v>
+        <v>4739.22986968411</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>4754.35346562722</v>
+        <v>4755.20017410558</v>
       </c>
       <c r="J80" s="10" t="n">
-        <v>4628.12878827834</v>
+        <v>4628.11161465774</v>
       </c>
       <c r="K80" s="11" t="n">
-        <v>4722.13917342478</v>
+        <v>4722.14352817112</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>4722.13917342478</v>
+        <v>4722.14352817112</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>4718.82629073957</v>
+        <v>4718.8417789891</v>
       </c>
       <c r="N80" s="14" t="n">
-        <v>4718.82629073957</v>
+        <v>4718.8417789891</v>
       </c>
       <c r="O80" s="15" t="n">
-        <v>-0.00129519561430605</v>
+        <v>-0.00129168428579694</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>0.0307797237584375</v>
+        <v>0.0307824126354708</v>
       </c>
       <c r="Q80" s="17" t="n">
-        <v>-0.00129435721047111</v>
+        <v>-0.00129085042071864</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>0.995696247827892</v>
+        <v>0.995698016079484</v>
       </c>
       <c r="S80" s="19" t="n">
-        <v>0.992527443501098</v>
+        <v>0.992353971697245</v>
       </c>
     </row>
     <row r="81">
@@ -6312,46 +6312,46 @@
         <v>4837.70906203481</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>0.989625084763068</v>
+        <v>0.989622736038117</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>0.00696110715682074</v>
+        <v>0.00704851441233645</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>4682.64682256079</v>
+        <v>4682.68237989658</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>4813.05611385449</v>
+        <v>4813.92349327863</v>
       </c>
       <c r="J81" s="10" t="n">
-        <v>4651.59543080282</v>
+        <v>4651.57098859386</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>4888.42606813371</v>
+        <v>4888.43767009864</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>4684.07927393987</v>
+        <v>4684.13264902498</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>4661.88039821074</v>
+        <v>4661.92460825817</v>
       </c>
       <c r="N81" s="14" t="n">
-        <v>4661.88039821074</v>
+        <v>4661.92460825817</v>
       </c>
       <c r="O81" s="15" t="n">
-        <v>-0.0121412157834242</v>
+        <v>-0.0121350147400354</v>
       </c>
       <c r="P81" s="16" t="n">
-        <v>0.0207329989621294</v>
+        <v>0.0207426363707286</v>
       </c>
       <c r="Q81" s="17" t="n">
-        <v>-0.0120678086075319</v>
+        <v>-0.0120616823781534</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>0.995565237965417</v>
+        <v>0.995567119451124</v>
       </c>
       <c r="S81" s="19" t="n">
-        <v>0.968590493842656</v>
+        <v>0.968425155648469</v>
       </c>
     </row>
     <row r="82">
@@ -6371,46 +6371,46 @@
         <v>4964.35954377805</v>
       </c>
       <c r="F82" s="6" t="n">
-        <v>1.1078069976233</v>
+        <v>1.10780903367625</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>0.42021881289975</v>
+        <v>0.419851049233782</v>
       </c>
       <c r="H82" s="8" t="n">
-        <v>4612.28923909565</v>
+        <v>4612.32543939119</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>4870.72207582766</v>
+        <v>4871.59106001692</v>
       </c>
       <c r="J82" s="10" t="n">
-        <v>4680.73965783825</v>
+        <v>4680.70670075044</v>
       </c>
       <c r="K82" s="11" t="n">
-        <v>4481.24949059596</v>
+        <v>4481.24125446413</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>4557.22387153843</v>
+        <v>4557.28960681161</v>
       </c>
       <c r="M82" s="13" t="n">
-        <v>4592.42757054202</v>
+        <v>4592.47015350171</v>
       </c>
       <c r="N82" s="14" t="n">
-        <v>4592.42757054202</v>
+        <v>4592.47015350171</v>
       </c>
       <c r="O82" s="15" t="n">
-        <v>-0.0150101189405884</v>
+        <v>-0.0150103298173186</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>-0.0122946254224182</v>
+        <v>-0.0122847091879281</v>
       </c>
       <c r="Q82" s="17" t="n">
-        <v>-0.014898028635693</v>
+        <v>-0.0148982363707537</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>0.99569375042977</v>
+        <v>0.995695168055596</v>
       </c>
       <c r="S82" s="19" t="n">
-        <v>0.942863809317564</v>
+        <v>0.942704364328512</v>
       </c>
     </row>
     <row r="83">
@@ -6430,46 +6430,46 @@
         <v>4294.14828388207</v>
       </c>
       <c r="F83" s="6" t="n">
-        <v>0.939395345756259</v>
+        <v>0.939398328404692</v>
       </c>
       <c r="G83" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H83" s="8" t="n">
-        <v>4536.19369422288</v>
+        <v>4536.19987637636</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>4927.68625361681</v>
+        <v>4928.53298242337</v>
       </c>
       <c r="J83" s="10" t="n">
-        <v>4719.6786137615</v>
+        <v>4719.6363247299</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>4571.18326515134</v>
+        <v>4571.16875135864</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>4571.18326515134</v>
+        <v>4571.16875135864</v>
       </c>
       <c r="M83" s="13" t="n">
-        <v>4543.89115450122</v>
+        <v>4543.90149811923</v>
       </c>
       <c r="N83" s="14" t="n">
-        <v>4543.89115450122</v>
+        <v>4543.90149811923</v>
       </c>
       <c r="O83" s="15" t="n">
-        <v>-0.0106250392773921</v>
+        <v>-0.0106320352873205</v>
       </c>
       <c r="P83" s="16" t="n">
-        <v>-0.0383181205192107</v>
+        <v>-0.0383157110364384</v>
       </c>
       <c r="Q83" s="17" t="n">
-        <v>-0.0105687929303742</v>
+        <v>-0.0105757149767089</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>1.00169689850064</v>
+        <v>1.00169781357805</v>
       </c>
       <c r="S83" s="19" t="n">
-        <v>0.92211454233031</v>
+        <v>0.921958220493633</v>
       </c>
     </row>
     <row r="84">
@@ -6489,46 +6489,46 @@
         <v>4320.30298531754</v>
       </c>
       <c r="F84" s="6" t="n">
-        <v>0.965220704291804</v>
+        <v>0.965219697924945</v>
       </c>
       <c r="G84" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H84" s="8" t="n">
-        <v>4523.06761794701</v>
+        <v>4523.07036580422</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>4984.08761291434</v>
+        <v>4984.88293019265</v>
       </c>
       <c r="J84" s="10" t="n">
-        <v>4771.91186401794</v>
+        <v>4771.86034866496</v>
       </c>
       <c r="K84" s="11" t="n">
-        <v>4475.97421616376</v>
+        <v>4475.97888294804</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>4475.97421616376</v>
+        <v>4475.97888294804</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>4520.61930445801</v>
+        <v>4520.6252867477</v>
       </c>
       <c r="N84" s="14" t="n">
-        <v>4520.61930445801</v>
+        <v>4520.6252867477</v>
       </c>
       <c r="O84" s="15" t="n">
-        <v>-0.00513472873788401</v>
+        <v>-0.00513568178098053</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>-0.0420034504492219</v>
+        <v>-0.0420053270537639</v>
       </c>
       <c r="Q84" s="17" t="n">
-        <v>-0.00512156855257362</v>
+        <v>-0.00512251671414277</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>0.999458705087829</v>
+        <v>0.999459420513329</v>
       </c>
       <c r="S84" s="19" t="n">
-        <v>0.90701040100992</v>
+        <v>0.906866891370102</v>
       </c>
     </row>
     <row r="85">
@@ -6548,46 +6548,46 @@
         <v>4458.85316814996</v>
       </c>
       <c r="F85" s="6" t="n">
-        <v>0.977959040008133</v>
+        <v>0.97795279621672</v>
       </c>
       <c r="G85" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>4495.80515311878</v>
+        <v>4495.82715265267</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>5039.84230504487</v>
+        <v>5040.551220375</v>
       </c>
       <c r="J85" s="10" t="n">
-        <v>4840.1964973099</v>
+        <v>4840.13692282147</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>4559.34552035316</v>
+        <v>4559.37462973607</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>4559.34552035316</v>
+        <v>4559.37462973607</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>4510.13303734554</v>
+        <v>4510.14827057273</v>
       </c>
       <c r="N85" s="14" t="n">
-        <v>4510.13303734554</v>
+        <v>4510.14827057273</v>
       </c>
       <c r="O85" s="15" t="n">
-        <v>-0.00232234733686418</v>
+        <v>-0.00232029311973034</v>
       </c>
       <c r="P85" s="16" t="n">
-        <v>-0.032550676530321</v>
+        <v>-0.0325565834798327</v>
       </c>
       <c r="Q85" s="17" t="n">
-        <v>-0.00231965277459445</v>
+        <v>-0.00231760332042608</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>1.00318694510522</v>
+        <v>1.00318542449116</v>
       </c>
       <c r="S85" s="19" t="n">
-        <v>0.89489566624553</v>
+        <v>0.894772828087081</v>
       </c>
     </row>
     <row r="86">
@@ -6607,46 +6607,46 @@
         <v>5009.75394783902</v>
       </c>
       <c r="F86" s="6" t="n">
-        <v>1.12683399412535</v>
+        <v>1.12683448903526</v>
       </c>
       <c r="G86" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>4494.70913503942</v>
+        <v>4494.7029390206</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>5094.54891046004</v>
+        <v>5095.13010499114</v>
       </c>
       <c r="J86" s="10" t="n">
-        <v>4925.80991410043</v>
+        <v>4925.74479013671</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>4445.86689251206</v>
+        <v>4445.86493987074</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>4445.86689251206</v>
+        <v>4445.86493987074</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>4519.13665997677</v>
+        <v>4519.12984686168</v>
       </c>
       <c r="N86" s="14" t="n">
-        <v>4519.13665997677</v>
+        <v>4519.12984686168</v>
       </c>
       <c r="O86" s="15" t="n">
-        <v>0.00199431978825235</v>
+        <v>0.00198943462244615</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>-0.015959078164971</v>
+        <v>-0.015969686070602</v>
       </c>
       <c r="Q86" s="17" t="n">
-        <v>0.00199630976662579</v>
+        <v>0.00199141486047161</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>1.00543472874516</v>
+        <v>1.00543459894291</v>
       </c>
       <c r="S86" s="19" t="n">
-        <v>0.887053346508884</v>
+        <v>0.886950824363598</v>
       </c>
     </row>
     <row r="87">
@@ -6666,46 +6666,46 @@
         <v>4294.11901736909</v>
       </c>
       <c r="F87" s="6" t="n">
-        <v>0.928364359058997</v>
+        <v>0.928374887585103</v>
       </c>
       <c r="G87" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H87" s="8" t="n">
-        <v>4627.08106135998</v>
+        <v>4627.02579155106</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>5147.50569912106</v>
+        <v>5147.91110069264</v>
       </c>
       <c r="J87" s="10" t="n">
-        <v>5028.6252599678</v>
+        <v>5028.55888208253</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>4625.46733452981</v>
+        <v>4625.41487796917</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>4625.46733452981</v>
+        <v>4625.41487796917</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>4654.92314576653</v>
+        <v>4654.88929210415</v>
       </c>
       <c r="N87" s="14" t="n">
-        <v>4654.92314576653</v>
+        <v>4654.88929210415</v>
       </c>
       <c r="O87" s="15" t="n">
-        <v>0.0296044293827724</v>
+        <v>0.0295986643141318</v>
       </c>
       <c r="P87" s="16" t="n">
-        <v>0.0244354425513305</v>
+        <v>0.0244256602021098</v>
       </c>
       <c r="Q87" s="17" t="n">
-        <v>0.0300469970276267</v>
+        <v>0.030041058753103</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>1.00601720264619</v>
+        <v>1.00602190301251</v>
       </c>
       <c r="S87" s="19" t="n">
-        <v>0.904306555029432</v>
+        <v>0.904228764066622</v>
       </c>
     </row>
     <row r="88">
@@ -6725,46 +6725,46 @@
         <v>4771.89666477564</v>
       </c>
       <c r="F88" s="6" t="n">
-        <v>0.969328113082425</v>
+        <v>0.969333734453903</v>
       </c>
       <c r="G88" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H88" s="8" t="n">
-        <v>4905.31899872709</v>
+        <v>4905.3535401569</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>5197.60551472792</v>
+        <v>5197.77993340288</v>
       </c>
       <c r="J88" s="10" t="n">
-        <v>5146.11596538232</v>
+        <v>5146.05473087944</v>
       </c>
       <c r="K88" s="11" t="n">
-        <v>4922.89102149446</v>
+        <v>4922.86247260753</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>4922.89102149446</v>
+        <v>4922.86247260753</v>
       </c>
       <c r="M88" s="13" t="n">
-        <v>4903.03852086714</v>
+        <v>4903.06161669108</v>
       </c>
       <c r="N88" s="14" t="n">
-        <v>4903.03852086714</v>
+        <v>4903.06161669108</v>
       </c>
       <c r="O88" s="15" t="n">
-        <v>0.0519297186762073</v>
+        <v>0.0519417018616386</v>
       </c>
       <c r="P88" s="16" t="n">
-        <v>0.0845944306860806</v>
+        <v>0.0845981043959791</v>
       </c>
       <c r="Q88" s="17" t="n">
-        <v>0.0533017124732249</v>
+        <v>0.0533143344585862</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>0.999535101007591</v>
+        <v>0.999532770992538</v>
       </c>
       <c r="S88" s="19" t="n">
-        <v>0.943326404240164</v>
+        <v>0.943299193023194</v>
       </c>
     </row>
     <row r="89">
@@ -6784,46 +6784,46 @@
         <v>4952.78741323696</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>0.96340774562595</v>
+        <v>0.963369903913917</v>
       </c>
       <c r="G89" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>5156.20666685382</v>
+        <v>5156.30398867296</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>5243.41492700275</v>
+        <v>5243.29576890601</v>
       </c>
       <c r="J89" s="10" t="n">
-        <v>5273.73967118715</v>
+        <v>5273.6921487274</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>5140.90470594983</v>
+        <v>5141.1066435801</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>5140.90470594983</v>
+        <v>5141.1066435801</v>
       </c>
       <c r="M89" s="13" t="n">
-        <v>5131.5724471664</v>
+        <v>5131.6442638132</v>
       </c>
       <c r="N89" s="14" t="n">
-        <v>5131.5724471664</v>
+        <v>5131.6442638132</v>
       </c>
       <c r="O89" s="15" t="n">
-        <v>0.0455570129009924</v>
+        <v>0.0455662973583076</v>
       </c>
       <c r="P89" s="16" t="n">
-        <v>0.137787378925438</v>
+        <v>0.13779945934273</v>
       </c>
       <c r="Q89" s="17" t="n">
-        <v>0.0466106732236824</v>
+        <v>0.0466203904809133</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>0.995222414212802</v>
+        <v>0.995217557980691</v>
       </c>
       <c r="S89" s="19" t="n">
-        <v>0.978669916191378</v>
+        <v>0.978705854101359</v>
       </c>
     </row>
     <row r="90">
@@ -6843,46 +6843,46 @@
         <v>6108.57642446564</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>1.14788571921931</v>
+        <v>1.14790471434224</v>
       </c>
       <c r="G90" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H90" s="8" t="n">
-        <v>5268.6798431953</v>
+        <v>5268.63207687357</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>5283.3288091094</v>
+        <v>5282.84594957322</v>
       </c>
       <c r="J90" s="10" t="n">
-        <v>5405.83789350598</v>
+        <v>5405.814986535</v>
       </c>
       <c r="K90" s="11" t="n">
-        <v>5321.58935527149</v>
+        <v>5321.50129548506</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>5321.58935527149</v>
+        <v>5321.50129548506</v>
       </c>
       <c r="M90" s="13" t="n">
-        <v>5270.6778047779</v>
+        <v>5270.63405024202</v>
       </c>
       <c r="N90" s="14" t="n">
-        <v>5270.6778047779</v>
+        <v>5270.63405024202</v>
       </c>
       <c r="O90" s="15" t="n">
-        <v>0.0267468378598365</v>
+        <v>0.026724541365943</v>
       </c>
       <c r="P90" s="16" t="n">
-        <v>0.166301929184189</v>
+        <v>0.16629400544935</v>
       </c>
       <c r="Q90" s="17" t="n">
-        <v>0.0271077450515791</v>
+        <v>0.0270848444053167</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>1.00037921483978</v>
+        <v>1.00037997972514</v>
       </c>
       <c r="S90" s="19" t="n">
-        <v>0.997605486088678</v>
+        <v>0.99768838625094</v>
       </c>
     </row>
     <row r="91">
@@ -6902,46 +6902,46 @@
         <v>4881.31680020904</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>0.921241684082154</v>
+        <v>0.921276603631135</v>
       </c>
       <c r="G91" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H91" s="8" t="n">
-        <v>5383.55961332773</v>
+        <v>5383.36765094198</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>5315.67796532356</v>
+        <v>5314.75394957233</v>
       </c>
       <c r="J91" s="10" t="n">
-        <v>5536.08797363631</v>
+        <v>5536.1041676851</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>5298.62780261877</v>
+        <v>5298.42696641784</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>5298.62780261877</v>
+        <v>5298.42696641784</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>5386.28125153158</v>
+        <v>5386.16195716155</v>
       </c>
       <c r="N91" s="14" t="n">
-        <v>5386.28125153158</v>
+        <v>5386.16195716155</v>
       </c>
       <c r="O91" s="15" t="n">
-        <v>0.0216962420352326</v>
+        <v>0.0216823955084661</v>
       </c>
       <c r="P91" s="16" t="n">
-        <v>0.157114969004416</v>
+        <v>0.157097756609984</v>
       </c>
       <c r="Q91" s="17" t="n">
-        <v>0.0219333169348519</v>
+        <v>0.0219191668057908</v>
       </c>
       <c r="R91" s="18" t="n">
-        <v>1.00050554621836</v>
+        <v>1.0005190628619</v>
       </c>
       <c r="S91" s="19" t="n">
-        <v>1.01328208493227</v>
+        <v>1.0134358068627</v>
       </c>
     </row>
     <row r="92">
@@ -6961,46 +6961,46 @@
         <v>5446.86304040468</v>
       </c>
       <c r="F92" s="6" t="n">
-        <v>0.968110900318167</v>
+        <v>0.968108740041283</v>
       </c>
       <c r="G92" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>5538.81333099249</v>
+        <v>5538.95726313622</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>5338.81711276227</v>
+        <v>5337.36740266239</v>
       </c>
       <c r="J92" s="10" t="n">
-        <v>5657.7460101845</v>
+        <v>5657.81904710531</v>
       </c>
       <c r="K92" s="11" t="n">
-        <v>5626.28004561728</v>
+        <v>5626.29260032547</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>5626.28004561728</v>
+        <v>5626.29260032547</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>5563.32590033218</v>
+        <v>5563.42702022374</v>
       </c>
       <c r="N92" s="14" t="n">
-        <v>5563.32590033218</v>
+        <v>5563.42702022374</v>
       </c>
       <c r="O92" s="15" t="n">
-        <v>0.0323409009094382</v>
+        <v>0.0323812249644306</v>
       </c>
       <c r="P92" s="16" t="n">
-        <v>0.134669017315464</v>
+        <v>0.134684296294509</v>
       </c>
       <c r="Q92" s="17" t="n">
-        <v>0.0328695514647064</v>
+        <v>0.0329112017930491</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>1.00442559946957</v>
+        <v>1.00441775517034</v>
       </c>
       <c r="S92" s="19" t="n">
-        <v>1.04205215927574</v>
+        <v>1.04235414212793</v>
       </c>
     </row>
     <row r="93">
@@ -7020,46 +7020,46 @@
         <v>5439.60580468164</v>
       </c>
       <c r="F93" s="6" t="n">
-        <v>0.953962719057138</v>
+        <v>0.95386566053668</v>
       </c>
       <c r="G93" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H93" s="8" t="n">
-        <v>5795.45395931855</v>
+        <v>5795.77370899857</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>5351.0903121909</v>
+        <v>5349.02373823797</v>
       </c>
       <c r="J93" s="10" t="n">
-        <v>5762.88080090179</v>
+        <v>5763.0305937169</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>5702.1157074754</v>
+        <v>5702.69591382619</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>5702.1157074754</v>
+        <v>5702.69591382619</v>
       </c>
       <c r="M93" s="13" t="n">
-        <v>5786.35730588156</v>
+        <v>5786.58579188053</v>
       </c>
       <c r="N93" s="14" t="n">
-        <v>5786.35730588156</v>
+        <v>5786.58579188053</v>
       </c>
       <c r="O93" s="15" t="n">
-        <v>0.0393068452348065</v>
+        <v>0.0393281554808918</v>
       </c>
       <c r="P93" s="16" t="n">
-        <v>0.127599262303453</v>
+        <v>0.127628006618811</v>
       </c>
       <c r="Q93" s="17" t="n">
-        <v>0.0400895812226394</v>
+        <v>0.0401117460237339</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>0.998430381208989</v>
+        <v>0.998414721212498</v>
       </c>
       <c r="S93" s="19" t="n">
-        <v>1.08134173940197</v>
+        <v>1.08180222692126</v>
       </c>
     </row>
     <row r="94">
@@ -7079,46 +7079,46 @@
         <v>7098.31965039088</v>
       </c>
       <c r="F94" s="6" t="n">
-        <v>1.16082013291982</v>
+        <v>1.16086930648887</v>
       </c>
       <c r="G94" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>6023.70576122433</v>
+        <v>6023.50843250802</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>5351.02128870782</v>
+        <v>5348.24096394216</v>
       </c>
       <c r="J94" s="10" t="n">
-        <v>5843.40381371658</v>
+        <v>5843.65214420722</v>
       </c>
       <c r="K94" s="11" t="n">
-        <v>6114.91776295818</v>
+        <v>6114.65873954429</v>
       </c>
       <c r="L94" s="12" t="n">
-        <v>6114.91776295818</v>
+        <v>6114.65873954429</v>
       </c>
       <c r="M94" s="13" t="n">
-        <v>6028.56058092293</v>
+        <v>6028.39634457253</v>
       </c>
       <c r="N94" s="14" t="n">
-        <v>6028.56058092293</v>
+        <v>6028.39634457253</v>
       </c>
       <c r="O94" s="15" t="n">
-        <v>0.0410053144422218</v>
+        <v>0.0409385847865122</v>
       </c>
       <c r="P94" s="16" t="n">
-        <v>0.14379227951631</v>
+        <v>0.143770614143799</v>
       </c>
       <c r="Q94" s="17" t="n">
-        <v>0.0418576424230108</v>
+        <v>0.0417881219407983</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>1.00080595233085</v>
+        <v>1.0008114726026</v>
       </c>
       <c r="S94" s="19" t="n">
-        <v>1.12661868747278</v>
+        <v>1.12717366050183</v>
       </c>
     </row>
     <row r="95">
@@ -7138,46 +7138,46 @@
         <v>5694.02546550393</v>
       </c>
       <c r="F95" s="6" t="n">
-        <v>0.921021896629531</v>
+        <v>0.92112903950243</v>
       </c>
       <c r="G95" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H95" s="8" t="n">
-        <v>6254.91541155322</v>
+        <v>6254.47962521761</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>5337.35315828349</v>
+        <v>5333.75813252781</v>
       </c>
       <c r="J95" s="10" t="n">
-        <v>5890.92269109017</v>
+        <v>5891.2953618642</v>
       </c>
       <c r="K95" s="11" t="n">
-        <v>6182.29109029996</v>
+        <v>6181.57198537535</v>
       </c>
       <c r="L95" s="12" t="n">
-        <v>6182.29109029996</v>
+        <v>6181.57198537535</v>
       </c>
       <c r="M95" s="13" t="n">
-        <v>6235.89027658375</v>
+        <v>6235.50241038185</v>
       </c>
       <c r="N95" s="14" t="n">
-        <v>6235.89027658375</v>
+        <v>6235.50241038185</v>
       </c>
       <c r="O95" s="15" t="n">
-        <v>0.0338130832689147</v>
+        <v>0.0337781257410718</v>
       </c>
       <c r="P95" s="16" t="n">
-        <v>0.157735733686499</v>
+        <v>0.157689363961847</v>
       </c>
       <c r="Q95" s="17" t="n">
-        <v>0.0343912436273595</v>
+        <v>0.0343550844986804</v>
       </c>
       <c r="R95" s="18" t="n">
-        <v>0.996958370542576</v>
+        <v>0.996965820344311</v>
       </c>
       <c r="S95" s="19" t="n">
-        <v>1.16834882228202</v>
+        <v>1.16906358620853</v>
       </c>
     </row>
     <row r="96">
@@ -7197,46 +7197,46 @@
         <v>6209.22803193611</v>
       </c>
       <c r="F96" s="6" t="n">
-        <v>0.960576930752417</v>
+        <v>0.960555269655066</v>
       </c>
       <c r="G96" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H96" s="8" t="n">
-        <v>6403.85863792402</v>
+        <v>6403.65678070529</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>5309.30647218475</v>
+        <v>5304.79330785751</v>
       </c>
       <c r="J96" s="10" t="n">
-        <v>5898.40264523003</v>
+        <v>5898.92694295244</v>
       </c>
       <c r="K96" s="11" t="n">
-        <v>6464.06116277688</v>
+        <v>6464.20693123243</v>
       </c>
       <c r="L96" s="12" t="n">
-        <v>6464.06116277688</v>
+        <v>6464.20693123243</v>
       </c>
       <c r="M96" s="13" t="n">
-        <v>6405.49045688812</v>
+        <v>6405.35981410067</v>
       </c>
       <c r="N96" s="14" t="n">
-        <v>6405.49045688812</v>
+        <v>6405.35981410067</v>
       </c>
       <c r="O96" s="15" t="n">
-        <v>0.0268341506013583</v>
+        <v>0.0268759558992221</v>
       </c>
       <c r="P96" s="16" t="n">
-        <v>0.15137789366351</v>
+        <v>0.151333483986831</v>
       </c>
       <c r="Q96" s="17" t="n">
-        <v>0.0271974285598373</v>
+        <v>0.0272403717519234</v>
       </c>
       <c r="R96" s="18" t="n">
-        <v>1.00025481808022</v>
+        <v>1.00026594701336</v>
       </c>
       <c r="S96" s="19" t="n">
-        <v>1.20646462780897</v>
+        <v>1.20746642562171</v>
       </c>
     </row>
     <row r="97">
@@ -7256,46 +7256,46 @@
         <v>6200.06740637572</v>
       </c>
       <c r="F97" s="6" t="n">
-        <v>0.957356014586085</v>
+        <v>0.957086614786144</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>0.728032346993902</v>
+        <v>0.738222036138048</v>
       </c>
       <c r="H97" s="8" t="n">
-        <v>6606.06552339389</v>
+        <v>6605.61534687007</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>5266.62986788596</v>
+        <v>5261.09443745191</v>
       </c>
       <c r="J97" s="10" t="n">
-        <v>5860.26573033972</v>
+        <v>5860.9649668541</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>6476.24009450271</v>
+        <v>6478.06302020126</v>
       </c>
       <c r="L97" s="12" t="n">
-        <v>6511.54841169875</v>
+        <v>6511.45340856247</v>
       </c>
       <c r="M97" s="13" t="n">
-        <v>6565.21402934404</v>
+        <v>6564.93642479668</v>
       </c>
       <c r="N97" s="14" t="n">
-        <v>6565.21402934404</v>
+        <v>6564.93642479668</v>
       </c>
       <c r="O97" s="15" t="n">
-        <v>0.0246296023166415</v>
+        <v>0.0246077129112449</v>
       </c>
       <c r="P97" s="16" t="n">
-        <v>0.134602251864193</v>
+        <v>0.13450947776637</v>
       </c>
       <c r="Q97" s="17" t="n">
-        <v>0.02493541650416</v>
+        <v>0.0249129815228679</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>0.99381606284328</v>
+        <v>0.993841766446079</v>
       </c>
       <c r="S97" s="19" t="n">
-        <v>1.24656833573523</v>
+        <v>1.24782713993179</v>
       </c>
     </row>
     <row r="98">
@@ -7315,46 +7315,46 @@
         <v>7870.36784763967</v>
       </c>
       <c r="F98" s="6" t="n">
-        <v>1.16190117941428</v>
+        <v>1.16208409149945</v>
       </c>
       <c r="G98" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H98" s="8" t="n">
-        <v>6749.42291573928</v>
+        <v>6748.32024038277</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>5209.79370454309</v>
+        <v>5203.13410234622</v>
       </c>
       <c r="J98" s="10" t="n">
-        <v>5773.76229321051</v>
+        <v>5774.65391289274</v>
       </c>
       <c r="K98" s="11" t="n">
-        <v>6773.6981312018</v>
+        <v>6772.63195082935</v>
       </c>
       <c r="L98" s="12" t="n">
-        <v>6773.6981312018</v>
+        <v>6772.63195082935</v>
       </c>
       <c r="M98" s="13" t="n">
-        <v>6654.80314926119</v>
+        <v>6653.939128881</v>
       </c>
       <c r="N98" s="14" t="n">
-        <v>6654.80314926119</v>
+        <v>6653.939128881</v>
       </c>
       <c r="O98" s="15" t="n">
-        <v>0.0135537632358947</v>
+        <v>0.0134662057583299</v>
       </c>
       <c r="P98" s="16" t="n">
-        <v>0.103879285931035</v>
+        <v>0.103766034705342</v>
       </c>
       <c r="Q98" s="17" t="n">
-        <v>0.0136460318759932</v>
+        <v>0.0135572834716484</v>
       </c>
       <c r="R98" s="18" t="n">
-        <v>0.985981058283155</v>
+        <v>0.98601413268194</v>
       </c>
       <c r="S98" s="19" t="n">
-        <v>1.277364042929</v>
+        <v>1.27883291070291</v>
       </c>
     </row>
     <row r="99">
@@ -7374,46 +7374,46 @@
         <v>6054.57948367958</v>
       </c>
       <c r="F99" s="6" t="n">
-        <v>0.922916495911036</v>
+        <v>0.923089387662846</v>
       </c>
       <c r="G99" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H99" s="8" t="n">
-        <v>6442.61308790661</v>
+        <v>6441.2237605388</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>5140.046415402</v>
+        <v>5132.16635793263</v>
       </c>
       <c r="J99" s="10" t="n">
-        <v>5639.39909404048</v>
+        <v>5640.49070260046</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>6560.26792294241</v>
+        <v>6559.03920530282</v>
       </c>
       <c r="L99" s="12" t="n">
-        <v>6560.26792294241</v>
+        <v>6559.03920530282</v>
       </c>
       <c r="M99" s="13" t="n">
-        <v>6370.89462276965</v>
+        <v>6369.89496040189</v>
       </c>
       <c r="N99" s="14" t="n">
-        <v>6370.89462276965</v>
+        <v>6369.89496040189</v>
       </c>
       <c r="O99" s="15" t="n">
-        <v>-0.0435989691770592</v>
+        <v>-0.0436260497900103</v>
       </c>
       <c r="P99" s="16" t="n">
-        <v>0.0216495705020421</v>
+        <v>0.0215528021922144</v>
       </c>
       <c r="Q99" s="17" t="n">
-        <v>-0.0426621975321787</v>
+        <v>-0.0426881224756376</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>0.988868109234809</v>
+        <v>0.98892620365498</v>
       </c>
       <c r="S99" s="19" t="n">
-        <v>1.23946246938149</v>
+        <v>1.24117078756735</v>
       </c>
     </row>
     <row r="100">
@@ -7433,46 +7433,46 @@
         <v>5310.71118746629</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>0.950149194448802</v>
+        <v>0.95022995371549</v>
       </c>
       <c r="G100" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H100" s="8" t="n">
-        <v>5710.1091081212</v>
+        <v>5710.89599757455</v>
       </c>
       <c r="I100" s="9" t="n">
-        <v>5059.61387397524</v>
+        <v>5050.42619575865</v>
       </c>
       <c r="J100" s="10" t="n">
-        <v>5462.68257221763</v>
+        <v>5463.96214769905</v>
       </c>
       <c r="K100" s="11" t="n">
-        <v>5589.34451399195</v>
+        <v>5588.86948017256</v>
       </c>
       <c r="L100" s="12" t="n">
-        <v>5589.34451399195</v>
+        <v>5588.86948017256</v>
       </c>
       <c r="M100" s="13" t="n">
-        <v>5725.22185769866</v>
+        <v>5725.67014302872</v>
       </c>
       <c r="N100" s="14" t="n">
-        <v>5725.22185769866</v>
+        <v>5725.67014302872</v>
       </c>
       <c r="O100" s="15" t="n">
-        <v>-0.106858601731916</v>
+        <v>-0.106623381574582</v>
       </c>
       <c r="P100" s="16" t="n">
-        <v>-0.106200860616057</v>
+        <v>-0.106112644847162</v>
       </c>
       <c r="Q100" s="17" t="n">
-        <v>-0.101347268052958</v>
+        <v>-0.101135861953448</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>1.00264666564006</v>
+        <v>1.00258701006995</v>
       </c>
       <c r="S100" s="19" t="n">
-        <v>1.13155311853876</v>
+        <v>1.13370038905571</v>
       </c>
     </row>
     <row r="101">
@@ -7492,46 +7492,46 @@
         <v>5041.77244509139</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>0.976722267910126</v>
+        <v>0.975971291826929</v>
       </c>
       <c r="G101" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H101" s="8" t="n">
-        <v>5126.68487591752</v>
+        <v>5128.27075548834</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>4971.60959221753</v>
+        <v>4961.04040290133</v>
       </c>
       <c r="J101" s="10" t="n">
-        <v>5253.7235112745</v>
+        <v>5255.14780242379</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>5161.93047986832</v>
+        <v>5165.90240646695</v>
       </c>
       <c r="L101" s="12" t="n">
-        <v>5161.93047986832</v>
+        <v>5165.90240646695</v>
       </c>
       <c r="M101" s="13" t="n">
-        <v>5211.88377791921</v>
+        <v>5213.17673925916</v>
       </c>
       <c r="N101" s="14" t="n">
-        <v>5211.88377791921</v>
+        <v>5213.17673925916</v>
       </c>
       <c r="O101" s="15" t="n">
-        <v>-0.0939399410529781</v>
+        <v>-0.0937701893692805</v>
       </c>
       <c r="P101" s="16" t="n">
-        <v>-0.206136501472146</v>
+        <v>-0.205905982643143</v>
       </c>
       <c r="Q101" s="17" t="n">
-        <v>-0.0896625654932778</v>
+        <v>-0.0895080210643199</v>
       </c>
       <c r="R101" s="18" t="n">
-        <v>1.01661871249429</v>
+        <v>1.01655645495705</v>
       </c>
       <c r="S101" s="19" t="n">
-        <v>1.04832925458946</v>
+        <v>1.05082327815963</v>
       </c>
     </row>
     <row r="102">
@@ -7551,46 +7551,46 @@
         <v>5651.60509658883</v>
       </c>
       <c r="F102" s="6" t="n">
-        <v>1.14536431719605</v>
+        <v>1.1458977427139</v>
       </c>
       <c r="G102" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H102" s="8" t="n">
-        <v>4978.83814186341</v>
+        <v>4978.46339520441</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>4879.47816373363</v>
+        <v>4867.47229349055</v>
       </c>
       <c r="J102" s="10" t="n">
-        <v>5023.2660044525</v>
+        <v>5024.75175767235</v>
       </c>
       <c r="K102" s="11" t="n">
-        <v>4934.32963794825</v>
+        <v>4932.03266393019</v>
       </c>
       <c r="L102" s="12" t="n">
-        <v>4934.32963794825</v>
+        <v>4932.03266393019</v>
       </c>
       <c r="M102" s="13" t="n">
-        <v>5018.36177998537</v>
+        <v>5017.90747832376</v>
       </c>
       <c r="N102" s="14" t="n">
-        <v>5018.36177998537</v>
+        <v>5017.90747832376</v>
       </c>
       <c r="O102" s="15" t="n">
-        <v>-0.0378378182776554</v>
+        <v>-0.0381763989557725</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>-0.245903797989501</v>
+        <v>-0.245874153470408</v>
       </c>
       <c r="Q102" s="17" t="n">
-        <v>-0.0371309120041624</v>
+        <v>-0.0374568656889903</v>
       </c>
       <c r="R102" s="18" t="n">
-        <v>1.0079383255683</v>
+        <v>1.00792294328353</v>
       </c>
       <c r="S102" s="19" t="n">
-        <v>1.02846280106016</v>
+        <v>1.03090622314058</v>
       </c>
     </row>
     <row r="103">
@@ -7610,46 +7610,46 @@
         <v>4665.68219017201</v>
       </c>
       <c r="F103" s="6" t="n">
-        <v>0.925206059428922</v>
+        <v>0.925425390387284</v>
       </c>
       <c r="G103" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H103" s="8" t="n">
-        <v>5028.71327006441</v>
+        <v>5026.4316080737</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>4786.78313268305</v>
+        <v>4773.31322040837</v>
       </c>
       <c r="J103" s="10" t="n">
-        <v>4781.59517983601</v>
+        <v>4783.03187736261</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>5042.85736417667</v>
+        <v>5041.66217896773</v>
       </c>
       <c r="L103" s="12" t="n">
-        <v>5042.85736417667</v>
+        <v>5041.66217896773</v>
       </c>
       <c r="M103" s="13" t="n">
-        <v>5009.42749163177</v>
+        <v>5008.05188991002</v>
       </c>
       <c r="N103" s="14" t="n">
-        <v>5009.42749163177</v>
+        <v>5008.05188991002</v>
       </c>
       <c r="O103" s="15" t="n">
-        <v>-0.00178190635554926</v>
+        <v>-0.00196601466777626</v>
       </c>
       <c r="P103" s="16" t="n">
-        <v>-0.213701090938151</v>
+        <v>-0.213793646356446</v>
       </c>
       <c r="Q103" s="17" t="n">
-        <v>-0.00178031970298131</v>
+        <v>-0.00196408332682818</v>
       </c>
       <c r="R103" s="18" t="n">
-        <v>0.996164868148788</v>
+        <v>0.99634338640276</v>
       </c>
       <c r="S103" s="19" t="n">
-        <v>1.04651231375588</v>
+        <v>1.04917730277955</v>
       </c>
     </row>
     <row r="104">
@@ -7669,46 +7669,46 @@
         <v>4755.00405694119</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>0.947652640847067</v>
+        <v>0.947806601200958</v>
       </c>
       <c r="G104" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>4978.70927609164</v>
+        <v>4979.21195515049</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>4697.12232539672</v>
+        <v>4682.1948867684</v>
       </c>
       <c r="J104" s="10" t="n">
-        <v>4538.55148367689</v>
+        <v>4539.78242994373</v>
       </c>
       <c r="K104" s="11" t="n">
-        <v>5017.66560022551</v>
+        <v>5016.85053777444</v>
       </c>
       <c r="L104" s="12" t="n">
-        <v>5017.66560022551</v>
+        <v>5016.85053777444</v>
       </c>
       <c r="M104" s="13" t="n">
-        <v>4914.93098590942</v>
+        <v>4915.61161283322</v>
       </c>
       <c r="N104" s="14" t="n">
-        <v>4914.93098590942</v>
+        <v>4915.61161283322</v>
       </c>
       <c r="O104" s="15" t="n">
-        <v>-0.0190439234631884</v>
+        <v>-0.0186308112776512</v>
       </c>
       <c r="P104" s="16" t="n">
-        <v>-0.1415300388228</v>
+        <v>-0.141478378942557</v>
       </c>
       <c r="Q104" s="17" t="n">
-        <v>-0.0188637336063263</v>
+        <v>-0.018458330526296</v>
       </c>
       <c r="R104" s="18" t="n">
-        <v>0.987189794252802</v>
+        <v>0.987226825672387</v>
       </c>
       <c r="S104" s="19" t="n">
-        <v>1.04637065961324</v>
+        <v>1.04985198858861</v>
       </c>
     </row>
     <row r="105">
@@ -7728,46 +7728,46 @@
         <v>4573.30287832837</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>0.998203113148627</v>
+        <v>0.996995842914409</v>
       </c>
       <c r="G105" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H105" s="8" t="n">
-        <v>4620.9802064394</v>
+        <v>4625.71630906119</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>4614.25361460023</v>
+        <v>4597.91671378333</v>
       </c>
       <c r="J105" s="10" t="n">
-        <v>4305.28167314868</v>
+        <v>4306.09083537291</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>4581.53537901001</v>
+        <v>4587.08319681628</v>
       </c>
       <c r="L105" s="12" t="n">
-        <v>4581.53537901001</v>
+        <v>4587.08319681628</v>
       </c>
       <c r="M105" s="13" t="n">
-        <v>4552.35712366993</v>
+        <v>4556.73280206019</v>
       </c>
       <c r="N105" s="14" t="n">
-        <v>4552.35712366993</v>
+        <v>4556.73280206019</v>
       </c>
       <c r="O105" s="15" t="n">
-        <v>-0.0766325639965777</v>
+        <v>-0.0758103079223922</v>
       </c>
       <c r="P105" s="16" t="n">
-        <v>-0.126542855203995</v>
+        <v>-0.125920138531934</v>
       </c>
       <c r="Q105" s="17" t="n">
-        <v>-0.0737698786165984</v>
+        <v>-0.0730079670729277</v>
       </c>
       <c r="R105" s="18" t="n">
-        <v>0.985149669614718</v>
+        <v>0.985086956831773</v>
       </c>
       <c r="S105" s="19" t="n">
-        <v>0.986585806481367</v>
+        <v>0.991042919155173</v>
       </c>
     </row>
     <row r="106">
@@ -7787,46 +7787,46 @@
         <v>4670.88465711875</v>
       </c>
       <c r="F106" s="6" t="n">
-        <v>1.12039712922521</v>
+        <v>1.12125284700462</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>0.496050501651822</v>
+        <v>0.517259165555896</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>3890.62826780361</v>
+        <v>3896.77019088394</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>4542.13521256594</v>
+        <v>4524.48728244776</v>
       </c>
       <c r="J106" s="10" t="n">
-        <v>4095.3280760077</v>
+        <v>4095.4298541465</v>
       </c>
       <c r="K106" s="11" t="n">
-        <v>4168.95450307769</v>
+        <v>4165.77284026241</v>
       </c>
       <c r="L106" s="12" t="n">
-        <v>4028.69213643418</v>
+        <v>4035.91427683377</v>
       </c>
       <c r="M106" s="13" t="n">
-        <v>3920.56059610933</v>
+        <v>3926.40547632595</v>
       </c>
       <c r="N106" s="14" t="n">
-        <v>3920.56059610933</v>
+        <v>3926.40547632595</v>
       </c>
       <c r="O106" s="15" t="n">
-        <v>-0.149410495190852</v>
+        <v>-0.14888150566956</v>
       </c>
       <c r="P106" s="16" t="n">
-        <v>-0.218756883621737</v>
+        <v>-0.217521348632445</v>
       </c>
       <c r="Q106" s="17" t="n">
-        <v>-0.138784482499313</v>
+        <v>-0.138328787996799</v>
       </c>
       <c r="R106" s="18" t="n">
-        <v>1.00769344338379</v>
+        <v>1.00760508934074</v>
       </c>
       <c r="S106" s="19" t="n">
-        <v>0.863153651891075</v>
+        <v>0.867812247270092</v>
       </c>
     </row>
     <row r="107">
@@ -7846,46 +7846,46 @@
         <v>2175.26624692192</v>
       </c>
       <c r="F107" s="6" t="n">
-        <v>0.928461838199844</v>
+        <v>0.928719611116047</v>
       </c>
       <c r="G107" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="8" t="n">
-        <v>3043.32273255897</v>
+        <v>3046.71015481996</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>4484.70488266898</v>
+        <v>4465.90840280817</v>
       </c>
       <c r="J107" s="10" t="n">
-        <v>3923.61428853955</v>
+        <v>3922.67720856805</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>2342.87092632633</v>
+        <v>2342.22064537637</v>
       </c>
       <c r="L107" s="12" t="n">
-        <v>3043.32273255897</v>
+        <v>3046.71015481996</v>
       </c>
       <c r="M107" s="13" t="n">
-        <v>3157.6667754024</v>
+        <v>3160.98412839761</v>
       </c>
       <c r="N107" s="14" t="n">
-        <v>3157.6667754024</v>
+        <v>3160.98412839761</v>
       </c>
       <c r="O107" s="15" t="n">
-        <v>-0.216401260128338</v>
+        <v>-0.216840958127437</v>
       </c>
       <c r="P107" s="16" t="n">
-        <v>-0.369655159062135</v>
+        <v>-0.368819613317864</v>
       </c>
       <c r="Q107" s="17" t="n">
-        <v>-0.194587942720235</v>
+        <v>-0.194942002944781</v>
       </c>
       <c r="R107" s="18" t="n">
-        <v>1.03757210552142</v>
+        <v>1.03750733340908</v>
       </c>
       <c r="S107" s="19" t="n">
-        <v>0.704096893332962</v>
+        <v>0.707803170886796</v>
       </c>
     </row>
     <row r="108">
@@ -7905,46 +7905,46 @@
         <v>2405.16348217783</v>
       </c>
       <c r="F108" s="6" t="n">
-        <v>0.956202152490509</v>
+        <v>0.956478819268072</v>
       </c>
       <c r="G108" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>2523.66070974813</v>
+        <v>2520.51656766497</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>4445.5794863619</v>
+        <v>4425.8765267825</v>
       </c>
       <c r="J108" s="10" t="n">
-        <v>3804.73072733198</v>
+        <v>3802.41304305457</v>
       </c>
       <c r="K108" s="11" t="n">
-        <v>2515.32950005748</v>
+        <v>2514.60192711674</v>
       </c>
       <c r="L108" s="12" t="n">
-        <v>2515.32950005748</v>
+        <v>2514.60192711674</v>
       </c>
       <c r="M108" s="13" t="n">
-        <v>2628.10691579873</v>
+        <v>2624.2850934869</v>
       </c>
       <c r="N108" s="14" t="n">
-        <v>2628.10691579873</v>
+        <v>2624.2850934869</v>
       </c>
       <c r="O108" s="15" t="n">
-        <v>-0.183569609533085</v>
+        <v>-0.1860748985383</v>
       </c>
       <c r="P108" s="16" t="n">
-        <v>-0.465281013439816</v>
+        <v>-0.466132538495177</v>
       </c>
       <c r="Q108" s="17" t="n">
-        <v>-0.16770606187101</v>
+        <v>-0.169788588967948</v>
       </c>
       <c r="R108" s="18" t="n">
-        <v>1.04138678612666</v>
+        <v>1.04116954720836</v>
       </c>
       <c r="S108" s="19" t="n">
-        <v>0.591173079653893</v>
+        <v>0.5929413253186</v>
       </c>
     </row>
     <row r="109">
@@ -7964,46 +7964,46 @@
         <v>2776.70598703957</v>
       </c>
       <c r="F109" s="6" t="n">
-        <v>1.00701032459566</v>
+        <v>1.00535229645862</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>0.0323632386211981</v>
+        <v>0</v>
       </c>
       <c r="H109" s="8" t="n">
-        <v>2427.77911142296</v>
+        <v>2421.22636489416</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>4427.47502125339</v>
+        <v>4407.20110738375</v>
       </c>
       <c r="J109" s="10" t="n">
-        <v>3748.86635119281</v>
+        <v>3744.83766675432</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>2757.37588703918</v>
+        <v>2761.92335445056</v>
       </c>
       <c r="L109" s="12" t="n">
-        <v>2438.44593052101</v>
+        <v>2421.22636489416</v>
       </c>
       <c r="M109" s="13" t="n">
-        <v>2475.32470479515</v>
+        <v>2465.83794901746</v>
       </c>
       <c r="N109" s="14" t="n">
-        <v>2475.32470479515</v>
+        <v>2465.83794901746</v>
       </c>
       <c r="O109" s="15" t="n">
-        <v>-0.0598922018555522</v>
+        <v>-0.062276825134492</v>
       </c>
       <c r="P109" s="16" t="n">
-        <v>-0.456254279365578</v>
+        <v>-0.458858340804489</v>
       </c>
       <c r="Q109" s="17" t="n">
-        <v>-0.0581339404744684</v>
+        <v>-0.060377260406151</v>
       </c>
       <c r="R109" s="18" t="n">
-        <v>1.01958398651199</v>
+        <v>1.01842520169536</v>
       </c>
       <c r="S109" s="19" t="n">
-        <v>0.559082703552871</v>
+        <v>0.559502026101382</v>
       </c>
     </row>
     <row r="110">
@@ -8023,46 +8023,46 @@
         <v>2640.35379506736</v>
       </c>
       <c r="F110" s="6" t="n">
-        <v>1.09526481034905</v>
+        <v>1.09632835378491</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>0.496024245864342</v>
+        <v>0.492393251756519</v>
       </c>
       <c r="H110" s="8" t="n">
-        <v>2605.9037332208</v>
+        <v>2601.29861135991</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>4431.90107871074</v>
+        <v>4411.49705100006</v>
       </c>
       <c r="J110" s="10" t="n">
-        <v>3759.76311279351</v>
+        <v>3753.71233323585</v>
       </c>
       <c r="K110" s="11" t="n">
-        <v>2410.69901097791</v>
+        <v>2408.36040220244</v>
       </c>
       <c r="L110" s="12" t="n">
-        <v>2509.07745808111</v>
+        <v>2506.29713916478</v>
       </c>
       <c r="M110" s="13" t="n">
-        <v>2633.93666191386</v>
+        <v>2627.72920679092</v>
       </c>
       <c r="N110" s="14" t="n">
-        <v>2633.93666191386</v>
+        <v>2627.72920679092</v>
       </c>
       <c r="O110" s="15" t="n">
-        <v>0.0621079754097625</v>
+        <v>0.0635883652792078</v>
       </c>
       <c r="P110" s="16" t="n">
-        <v>-0.328173459548689</v>
+        <v>-0.330754497304297</v>
       </c>
       <c r="Q110" s="17" t="n">
-        <v>0.0640772327006038</v>
+        <v>0.0656536484232342</v>
       </c>
       <c r="R110" s="18" t="n">
-        <v>1.01075746902531</v>
+        <v>1.01016053878459</v>
       </c>
       <c r="S110" s="19" t="n">
-        <v>0.594313053277824</v>
+        <v>0.595654757650859</v>
       </c>
     </row>
     <row r="111">
@@ -8082,46 +8082,46 @@
         <v>2885.42830497867</v>
       </c>
       <c r="F111" s="6" t="n">
-        <v>0.937087261040908</v>
+        <v>0.937711443678087</v>
       </c>
       <c r="G111" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H111" s="8" t="n">
-        <v>3010.2754621773</v>
+        <v>3009.01857983908</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>4459.1241069195</v>
+        <v>4439.13802980557</v>
       </c>
       <c r="J111" s="10" t="n">
-        <v>3834.61086270218</v>
+        <v>3826.18023955846</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>3079.14580097222</v>
+        <v>3077.09618393996</v>
       </c>
       <c r="L111" s="12" t="n">
-        <v>3079.14580097222</v>
+        <v>3077.09618393996</v>
       </c>
       <c r="M111" s="13" t="n">
-        <v>3053.8732642964</v>
+        <v>3052.29669024517</v>
       </c>
       <c r="N111" s="14" t="n">
-        <v>3053.8732642964</v>
+        <v>3052.29669024517</v>
       </c>
       <c r="O111" s="15" t="n">
-        <v>0.147931150987733</v>
+        <v>0.149774266685016</v>
       </c>
       <c r="P111" s="16" t="n">
-        <v>-0.0328703180191554</v>
+        <v>-0.0343840505796955</v>
       </c>
       <c r="Q111" s="17" t="n">
-        <v>0.15943306779344</v>
+        <v>0.161572007631923</v>
       </c>
       <c r="R111" s="18" t="n">
-        <v>1.01448299421993</v>
+        <v>1.01438279932735</v>
       </c>
       <c r="S111" s="19" t="n">
-        <v>0.684859445727809</v>
+        <v>0.687587696023694</v>
       </c>
     </row>
     <row r="112">
@@ -8141,46 +8141,46 @@
         <v>3444.49013745048</v>
       </c>
       <c r="F112" s="6" t="n">
-        <v>0.970791928412725</v>
+        <v>0.970635106624008</v>
       </c>
       <c r="G112" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>3630.00058270531</v>
+        <v>3632.30105709357</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>4508.20878930236</v>
+        <v>4489.30696602952</v>
       </c>
       <c r="J112" s="10" t="n">
-        <v>3964.34602321338</v>
+        <v>3953.14750681104</v>
       </c>
       <c r="K112" s="11" t="n">
-        <v>3548.12399716006</v>
+        <v>3548.69725393598</v>
       </c>
       <c r="L112" s="12" t="n">
-        <v>3548.12399716006</v>
+        <v>3548.69725393598</v>
       </c>
       <c r="M112" s="13" t="n">
-        <v>3623.36745397481</v>
+        <v>3624.97037740167</v>
       </c>
       <c r="N112" s="14" t="n">
-        <v>3623.36745397481</v>
+        <v>3624.97037740167</v>
       </c>
       <c r="O112" s="15" t="n">
-        <v>0.170993121671425</v>
+        <v>0.171951796079718</v>
       </c>
       <c r="P112" s="16" t="n">
-        <v>0.378698648899372</v>
+        <v>0.381317291478098</v>
       </c>
       <c r="Q112" s="17" t="n">
-        <v>0.186482587976556</v>
+        <v>0.187620583866145</v>
       </c>
       <c r="R112" s="18" t="n">
-        <v>0.998172692103107</v>
+        <v>0.99798180834224</v>
       </c>
       <c r="S112" s="19" t="n">
-        <v>0.803726629204216</v>
+        <v>0.807467701547642</v>
       </c>
     </row>
     <row r="113">
@@ -8200,46 +8200,46 @@
         <v>4318.55493831423</v>
       </c>
       <c r="F113" s="6" t="n">
-        <v>1.00011090997589</v>
+        <v>0.998419592640646</v>
       </c>
       <c r="G113" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H113" s="8" t="n">
-        <v>4195.16526455592</v>
+        <v>4198.90382675011</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>4577.35732284081</v>
+        <v>4560.3355057475</v>
       </c>
       <c r="J113" s="10" t="n">
-        <v>4136.12769131298</v>
+        <v>4121.77483580443</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>4318.0760206069</v>
+        <v>4325.39081779476</v>
       </c>
       <c r="L113" s="12" t="n">
-        <v>4318.0760206069</v>
+        <v>4325.39081779476</v>
       </c>
       <c r="M113" s="13" t="n">
-        <v>4208.45185312498</v>
+        <v>4211.20674711855</v>
       </c>
       <c r="N113" s="14" t="n">
-        <v>4208.45185312498</v>
+        <v>4211.20674711855</v>
       </c>
       <c r="O113" s="15" t="n">
-        <v>0.149691019874508</v>
+        <v>0.149903128369843</v>
       </c>
       <c r="P113" s="16" t="n">
-        <v>0.700161536372359</v>
+        <v>0.707819748980889</v>
       </c>
       <c r="Q113" s="17" t="n">
-        <v>0.161475314491865</v>
+        <v>0.161721699402433</v>
       </c>
       <c r="R113" s="18" t="n">
-        <v>1.00316711922682</v>
+        <v>1.00293003147394</v>
       </c>
       <c r="S113" s="19" t="n">
-        <v>0.919406451431046</v>
+        <v>0.923442308534332</v>
       </c>
     </row>
     <row r="114">
@@ -8259,46 +8259,46 @@
         <v>5038.84746379941</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>1.08373232877615</v>
+        <v>1.08470826221608</v>
       </c>
       <c r="G114" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>4791.75322792124</v>
+        <v>4789.41758565675</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>4664.1718515212</v>
+        <v>4649.96741396498</v>
       </c>
       <c r="J114" s="10" t="n">
-        <v>4335.03385385663</v>
+        <v>4317.20067608507</v>
       </c>
       <c r="K114" s="11" t="n">
-        <v>4649.53137412606</v>
+        <v>4645.34809894869</v>
       </c>
       <c r="L114" s="12" t="n">
-        <v>4649.53137412606</v>
+        <v>4645.34809894869</v>
       </c>
       <c r="M114" s="13" t="n">
-        <v>4773.52144223532</v>
+        <v>4771.36492268739</v>
       </c>
       <c r="N114" s="14" t="n">
-        <v>4773.52144223532</v>
+        <v>4771.36492268739</v>
       </c>
       <c r="O114" s="15" t="n">
-        <v>0.125989431161879</v>
+        <v>0.124883166390005</v>
       </c>
       <c r="P114" s="16" t="n">
-        <v>0.812314438406731</v>
+        <v>0.815774970402812</v>
       </c>
       <c r="Q114" s="17" t="n">
-        <v>0.134270180301754</v>
+        <v>0.133016070975883</v>
       </c>
       <c r="R114" s="18" t="n">
-        <v>0.996195174329996</v>
+        <v>0.996230718527567</v>
       </c>
       <c r="S114" s="19" t="n">
-        <v>1.02344458870624</v>
+        <v>1.02610717407563</v>
       </c>
     </row>
     <row r="115">
@@ -8318,46 +8318,46 @@
         <v>5155.69426033944</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>0.941344559343373</v>
+        <v>0.942648191419015</v>
       </c>
       <c r="G115" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H115" s="8" t="n">
-        <v>5420.90270298966</v>
+        <v>5412.64326316968</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>4766.09246851601</v>
+        <v>4755.79961525752</v>
       </c>
       <c r="J115" s="10" t="n">
-        <v>4547.05223934642</v>
+        <v>4525.58155710935</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>5476.94700008226</v>
+        <v>5469.37267505741</v>
       </c>
       <c r="L115" s="12" t="n">
-        <v>5476.94700008226</v>
+        <v>5469.37267505741</v>
       </c>
       <c r="M115" s="13" t="n">
-        <v>5350.31975395624</v>
+        <v>5345.06809322883</v>
       </c>
       <c r="N115" s="14" t="n">
-        <v>5350.31975395624</v>
+        <v>5345.06809322883</v>
       </c>
       <c r="O115" s="15" t="n">
-        <v>0.114072045839132</v>
+        <v>0.11354187272653</v>
       </c>
       <c r="P115" s="16" t="n">
-        <v>0.751978320943496</v>
+        <v>0.751162693427255</v>
       </c>
       <c r="Q115" s="17" t="n">
-        <v>0.120832873320209</v>
+        <v>0.120238795363049</v>
       </c>
       <c r="R115" s="18" t="n">
-        <v>0.986979484248169</v>
+        <v>0.987515310606064</v>
       </c>
       <c r="S115" s="19" t="n">
-        <v>1.12257993089717</v>
+        <v>1.12390523689872</v>
       </c>
     </row>
     <row r="116">
@@ -8377,46 +8377,46 @@
         <v>5721.03663102072</v>
       </c>
       <c r="F116" s="6" t="n">
-        <v>0.986750784813992</v>
+        <v>0.987035891434982</v>
       </c>
       <c r="G116" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H116" s="8" t="n">
-        <v>5653.8198995903</v>
+        <v>5657.07980504644</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>4880.55011669934</v>
+        <v>4875.42614712878</v>
       </c>
       <c r="J116" s="10" t="n">
-        <v>4759.74306388578</v>
+        <v>4734.71474544799</v>
       </c>
       <c r="K116" s="11" t="n">
-        <v>5797.85364153439</v>
+        <v>5796.1789238518</v>
       </c>
       <c r="L116" s="12" t="n">
-        <v>5797.85364153439</v>
+        <v>5796.1789238518</v>
       </c>
       <c r="M116" s="13" t="n">
-        <v>5611.42656889312</v>
+        <v>5614.70307693081</v>
       </c>
       <c r="N116" s="14" t="n">
-        <v>5611.42656889312</v>
+        <v>5614.70307693081</v>
       </c>
       <c r="O116" s="15" t="n">
-        <v>0.0476486513470144</v>
+        <v>0.0492144224509366</v>
       </c>
       <c r="P116" s="16" t="n">
-        <v>0.548677201573201</v>
+        <v>0.548896264624195</v>
       </c>
       <c r="Q116" s="17" t="n">
-        <v>0.048802095378282</v>
+        <v>0.0504455657063669</v>
       </c>
       <c r="R116" s="18" t="n">
-        <v>0.99250182505809</v>
+        <v>0.992509080731399</v>
       </c>
       <c r="S116" s="19" t="n">
-        <v>1.14975288332621</v>
+        <v>1.15163329470951</v>
       </c>
     </row>
     <row r="117">
@@ -8436,46 +8436,46 @@
         <v>5275.14336147936</v>
       </c>
       <c r="F117" s="6" t="n">
-        <v>0.981777836678263</v>
+        <v>0.977406600762914</v>
       </c>
       <c r="G117" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H117" s="8" t="n">
-        <v>5626.23257134936</v>
+        <v>5642.64498098043</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>5005.42002302753</v>
+        <v>5006.88703024474</v>
       </c>
       <c r="J117" s="10" t="n">
-        <v>4965.31601738185</v>
+        <v>4937.11646326144</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>5373.05199242145</v>
+        <v>5397.08178496222</v>
       </c>
       <c r="L117" s="12" t="n">
-        <v>5373.05199242145</v>
+        <v>5397.08178496222</v>
       </c>
       <c r="M117" s="13" t="n">
-        <v>5617.22569083646</v>
+        <v>5632.03405364325</v>
       </c>
       <c r="N117" s="14" t="n">
-        <v>5617.22569083646</v>
+        <v>5632.03405364325</v>
       </c>
       <c r="O117" s="15" t="n">
-        <v>0.00103291513973272</v>
+        <v>0.00308195883470447</v>
       </c>
       <c r="P117" s="16" t="n">
-        <v>0.334748712086464</v>
+        <v>0.337391961935109</v>
       </c>
       <c r="Q117" s="17" t="n">
-        <v>0.00103344878029499</v>
+        <v>0.00308671295257779</v>
       </c>
       <c r="R117" s="18" t="n">
-        <v>0.998399127586945</v>
+        <v>0.998119511794035</v>
       </c>
       <c r="S117" s="19" t="n">
-        <v>1.12222863715618</v>
+        <v>1.12485742530683</v>
       </c>
     </row>
     <row r="118">
@@ -8483,58 +8483,58 @@
         <v>169</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>6464.88884607211</v>
+        <v>6493.81689277761</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>6464.88884607211</v>
+        <v>6493.81689277761</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>6464.88884607211</v>
+        <v>6493.81689277761</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>6464.88884607211</v>
+        <v>6493.81689277761</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>1.09113058376433</v>
+        <v>1.09364137558929</v>
       </c>
       <c r="G118" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H118" s="8" t="n">
-        <v>5740.85003355712</v>
+        <v>5756.91378782402</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>5139.15072915994</v>
+        <v>5148.79775575692</v>
       </c>
       <c r="J118" s="10" t="n">
-        <v>5161.17134262999</v>
+        <v>5130.61025360219</v>
       </c>
       <c r="K118" s="11" t="n">
-        <v>5924.94513696854</v>
+        <v>5937.79372079675</v>
       </c>
       <c r="L118" s="12" t="n">
-        <v>5924.94513696854</v>
+        <v>5937.79372079675</v>
       </c>
       <c r="M118" s="13" t="n">
-        <v>5737.7000162805</v>
+        <v>5753.08989006544</v>
       </c>
       <c r="N118" s="14" t="n">
-        <v>5737.7000162805</v>
+        <v>5753.08989006544</v>
       </c>
       <c r="O118" s="15" t="n">
-        <v>0.0212205433010803</v>
+        <v>0.0212664173678209</v>
       </c>
       <c r="P118" s="16" t="n">
-        <v>0.201984758152397</v>
+        <v>0.205753486326322</v>
       </c>
       <c r="Q118" s="17" t="n">
-        <v>0.0214473001575459</v>
+        <v>0.0214941591739639</v>
       </c>
       <c r="R118" s="18" t="n">
-        <v>0.999451297759356</v>
+        <v>0.999335772968032</v>
       </c>
       <c r="S118" s="19" t="n">
-        <v>1.11646852148631</v>
+        <v>1.11736567699379</v>
       </c>
     </row>
     <row r="119">
@@ -8542,58 +8542,58 @@
         <v>170</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>5373.68391411676</v>
+        <v>5401.39020454682</v>
       </c>
       <c r="C119" s="3" t="n">
-        <v>5373.68391411676</v>
+        <v>5401.39020454682</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>5373.68391411676</v>
+        <v>5401.39020454682</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>5373.68391411676</v>
+        <v>5401.39020454682</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>0.938166432008283</v>
+        <v>0.94105951549815</v>
       </c>
       <c r="G119" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H119" s="8" t="n">
-        <v>5791.18602541094</v>
+        <v>5799.02042505393</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>5280.42054673678</v>
+        <v>5300.01768653847</v>
       </c>
       <c r="J119" s="10" t="n">
-        <v>5346.74796230076</v>
+        <v>5315.31948613121</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>5727.85779876349</v>
+        <v>5739.69033370604</v>
       </c>
       <c r="L119" s="12" t="n">
-        <v>5727.85779876349</v>
+        <v>5739.69033370604</v>
       </c>
       <c r="M119" s="13" t="n">
-        <v>5735.99385392081</v>
+        <v>5751.18350868386</v>
       </c>
       <c r="N119" s="14" t="n">
-        <v>5735.99385392081</v>
+        <v>5751.18350868386</v>
       </c>
       <c r="O119" s="15" t="n">
-        <v>-0.000297404199827523</v>
+        <v>-0.000331421434966943</v>
       </c>
       <c r="P119" s="16" t="n">
-        <v>0.072084308546118</v>
+        <v>0.0759794652512473</v>
       </c>
       <c r="Q119" s="17" t="n">
-        <v>-0.000297359979582357</v>
+        <v>-0.000331366520949894</v>
       </c>
       <c r="R119" s="18" t="n">
-        <v>0.990469625522656</v>
+        <v>0.991750862583032</v>
       </c>
       <c r="S119" s="19" t="n">
-        <v>1.08627595153677</v>
+        <v>1.08512534274957</v>
       </c>
     </row>
     <row r="120">
@@ -8601,58 +8601,58 @@
         <v>171</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>5519.15105764071</v>
+        <v>5551.08998343361</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>5519.15105764071</v>
+        <v>5551.08998343361</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>5519.15105764071</v>
+        <v>5551.08998343361</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>5519.15105764071</v>
+        <v>5551.08998343361</v>
       </c>
       <c r="F120" s="6" t="n">
-        <v>0.992061634820627</v>
+        <v>0.993473060620363</v>
       </c>
       <c r="G120" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>5562.18299070868</v>
+        <v>5614.71876408106</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>5428.39890890316</v>
+        <v>5459.89930794071</v>
       </c>
       <c r="J120" s="10" t="n">
-        <v>5525.30366803642</v>
+        <v>5495.40344784545</v>
       </c>
       <c r="K120" s="11" t="n">
-        <v>5563.31468118774</v>
+        <v>5587.55964652659</v>
       </c>
       <c r="L120" s="12" t="n">
-        <v>5563.31468118774</v>
+        <v>5587.55964652659</v>
       </c>
       <c r="M120" s="13" t="n">
-        <v>5551.21437860507</v>
+        <v>5593.24499238622</v>
       </c>
       <c r="N120" s="14" t="n">
-        <v>5551.21437860507</v>
+        <v>5593.24499238622</v>
       </c>
       <c r="O120" s="15" t="n">
-        <v>-0.0327443210250967</v>
+        <v>-0.0278460429521086</v>
       </c>
       <c r="P120" s="16" t="n">
-        <v>-0.0107302821392753</v>
+        <v>-0.00382176657439925</v>
       </c>
       <c r="Q120" s="17" t="n">
-        <v>-0.0322140295163387</v>
+        <v>-0.0274619156316549</v>
       </c>
       <c r="R120" s="18" t="n">
-        <v>0.998028002292997</v>
+        <v>0.996175450169968</v>
       </c>
       <c r="S120" s="19" t="n">
-        <v>1.02262462132259</v>
+        <v>1.02442273692696</v>
       </c>
     </row>
     <row r="121">
@@ -8660,58 +8660,58 @@
         <v>172</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>5214.52990895346</v>
+        <v>5250.36031896855</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>5214.52990895346</v>
+        <v>5250.36031896855</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>5214.52990895346</v>
+        <v>5250.36031896855</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>5214.52990895346</v>
+        <v>5250.36031896855</v>
       </c>
       <c r="F121" s="6" t="n">
-        <v>0.974611020292353</v>
+        <v>0.961926797669157</v>
       </c>
       <c r="G121" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>5287.15221622173</v>
+        <v>5343.59371324115</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>5582.53489708671</v>
+        <v>5628.06990071946</v>
       </c>
       <c r="J121" s="10" t="n">
-        <v>5702.00180066154</v>
+        <v>5677.14327997974</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>5350.37035328131</v>
+        <v>5458.17034278564</v>
       </c>
       <c r="L121" s="12" t="n">
-        <v>5350.37035328131</v>
+        <v>5458.17034278564</v>
       </c>
       <c r="M121" s="13" t="n">
-        <v>5321.88682958975</v>
+        <v>5365.57753071063</v>
       </c>
       <c r="N121" s="14" t="n">
-        <v>5321.88682958975</v>
+        <v>5365.57753071063</v>
       </c>
       <c r="O121" s="15" t="n">
-        <v>-0.0421888030893391</v>
+        <v>-0.041555600136562</v>
       </c>
       <c r="P121" s="16" t="n">
-        <v>-0.0525773535730455</v>
+        <v>-0.0473108863324874</v>
       </c>
       <c r="Q121" s="17" t="n">
-        <v>-0.04131123991521</v>
+        <v>-0.0407040031297564</v>
       </c>
       <c r="R121" s="18" t="n">
-        <v>1.00656962613285</v>
+        <v>1.00411405107671</v>
       </c>
       <c r="S121" s="19" t="n">
-        <v>0.953310087209133</v>
+        <v>0.953360143950011</v>
       </c>
     </row>
     <row r="122">
@@ -8719,58 +8719,58 @@
         <v>173</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>5530.3441739009</v>
+        <v>5507.50065379131</v>
       </c>
       <c r="C122" s="3" t="n">
-        <v>5530.3441739009</v>
+        <v>5507.50065379131</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>5530.3441739009</v>
+        <v>5507.50065379131</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>5530.3441739009</v>
+        <v>5507.50065379131</v>
       </c>
       <c r="F122" s="6" t="n">
-        <v>1.10089639842038</v>
+        <v>1.11073930679783</v>
       </c>
       <c r="G122" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>5105.7120640064</v>
+        <v>5071.79381763342</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>5742.36191507272</v>
+        <v>5804.23653334215</v>
       </c>
       <c r="J122" s="10" t="n">
-        <v>5882.19575606645</v>
+        <v>5867.28090476231</v>
       </c>
       <c r="K122" s="11" t="n">
-        <v>5023.49193060864</v>
+        <v>4958.40979074467</v>
       </c>
       <c r="L122" s="12" t="n">
-        <v>5023.49193060864</v>
+        <v>4958.40979074467</v>
       </c>
       <c r="M122" s="13" t="n">
-        <v>5193.86789055865</v>
+        <v>5157.64496418412</v>
       </c>
       <c r="N122" s="14" t="n">
-        <v>5193.86789055865</v>
+        <v>5157.64496418412</v>
       </c>
       <c r="O122" s="15" t="n">
-        <v>-0.0243492297829269</v>
+        <v>-0.0395239451178418</v>
       </c>
       <c r="P122" s="16" t="n">
-        <v>-0.0947822514559405</v>
+        <v>-0.103500021251111</v>
       </c>
       <c r="Q122" s="17" t="n">
-        <v>-0.0240551787609078</v>
+        <v>-0.038753063456149</v>
       </c>
       <c r="R122" s="18" t="n">
-        <v>1.01726611791795</v>
+        <v>1.01692717599288</v>
       </c>
       <c r="S122" s="19" t="n">
-        <v>0.904482853462376</v>
+        <v>0.88860006558249</v>
       </c>
     </row>
     <row r="123">
@@ -8778,58 +8778,58 @@
         <v>174</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>5009.70362811794</v>
+        <v>4914.98939569154</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>5009.70362811794</v>
+        <v>4914.98939569154</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>5009.70362811794</v>
+        <v>4914.98939569154</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>5009.70362811794</v>
+        <v>4914.98939569154</v>
       </c>
       <c r="F123" s="6" t="n">
-        <v>0.931497642056257</v>
+        <v>0.935192710780913</v>
       </c>
       <c r="G123" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>5370.23089987216</v>
+        <v>5255.18652323692</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>5907.26826380662</v>
+        <v>5988.00008705247</v>
       </c>
       <c r="J123" s="10" t="n">
-        <v>6069.48077290456</v>
+        <v>6071.46337973542</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>5378.11734773601</v>
+        <v>5255.58993246149</v>
       </c>
       <c r="L123" s="12" t="n">
-        <v>5378.11734773601</v>
+        <v>5255.58993246149</v>
       </c>
       <c r="M123" s="13" t="n">
-        <v>5467.41281333041</v>
+        <v>5360.6074760561</v>
       </c>
       <c r="N123" s="14" t="n">
-        <v>5467.41281333041</v>
+        <v>5360.6074760561</v>
       </c>
       <c r="O123" s="15" t="n">
-        <v>0.0513268491842704</v>
+        <v>0.038597230725523</v>
       </c>
       <c r="P123" s="16" t="n">
-        <v>-0.0468238020176421</v>
+        <v>-0.0679122883208327</v>
       </c>
       <c r="Q123" s="17" t="n">
-        <v>0.0526669003786193</v>
+        <v>0.0393517803729033</v>
       </c>
       <c r="R123" s="18" t="n">
-        <v>1.01809641247652</v>
+        <v>1.02006036367178</v>
       </c>
       <c r="S123" s="19" t="n">
-        <v>0.925539956739197</v>
+        <v>0.895225016386866</v>
       </c>
     </row>
     <row r="124">
@@ -8837,58 +8837,58 @@
         <v>175</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>6033.85596798828</v>
+        <v>5928.99236351443</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>6033.85596798828</v>
+        <v>5928.99236351443</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>6033.85596798828</v>
+        <v>5928.99236351443</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>6033.85596798828</v>
+        <v>5928.99236351443</v>
       </c>
       <c r="F124" s="6" t="n">
-        <v>0.990793209656172</v>
+        <v>0.992658788245188</v>
       </c>
       <c r="G124" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>6111.75012769553</v>
+        <v>5971.12455846846</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>6076.19295049354</v>
+        <v>6178.43280138002</v>
       </c>
       <c r="J124" s="10" t="n">
-        <v>6263.15857070203</v>
+        <v>6290.79340687125</v>
       </c>
       <c r="K124" s="11" t="n">
-        <v>6089.924627241</v>
+        <v>5972.84024855675</v>
       </c>
       <c r="L124" s="12" t="n">
-        <v>6089.924627241</v>
+        <v>5972.84024855675</v>
       </c>
       <c r="M124" s="13" t="n">
-        <v>6117.81787231287</v>
+        <v>5981.31064303143</v>
       </c>
       <c r="N124" s="14" t="n">
-        <v>6117.81787231287</v>
+        <v>5981.31064303143</v>
       </c>
       <c r="O124" s="15" t="n">
-        <v>0.112399949039653</v>
+        <v>0.10956241127769</v>
       </c>
       <c r="P124" s="16" t="n">
-        <v>0.102068386314092</v>
+        <v>0.0693811286960366</v>
       </c>
       <c r="Q124" s="17" t="n">
-        <v>0.118960298259658</v>
+        <v>0.115789706623323</v>
       </c>
       <c r="R124" s="18" t="n">
-        <v>1.0009927998512</v>
+        <v>1.00170589048398</v>
       </c>
       <c r="S124" s="19" t="n">
-        <v>1.00685049374806</v>
+        <v>0.968095119800516</v>
       </c>
     </row>
     <row r="125">
@@ -8896,58 +8896,58 @@
         <v>176</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>6342.86762614381</v>
+        <v>5702.27255722485</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>6342.86762614381</v>
+        <v>5702.27255722485</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>6342.86762614381</v>
+        <v>5702.27255722485</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>6342.86762614381</v>
+        <v>5702.27255722485</v>
       </c>
       <c r="F125" s="6" t="n">
-        <v>0.972781684428456</v>
+        <v>0.949905591257464</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>0.0372866130238805</v>
+        <v>0</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>6928.52470058822</v>
+        <v>6723.97214255071</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>6247.74426301607</v>
+        <v>6374.14915950777</v>
       </c>
       <c r="J125" s="10" t="n">
-        <v>6459.07405185914</v>
+        <v>6522.2943209056</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>6520.34030623271</v>
+        <v>6002.98872825489</v>
       </c>
       <c r="L125" s="12" t="n">
-        <v>6913.3048870335</v>
+        <v>6723.97214255071</v>
       </c>
       <c r="M125" s="13" t="n">
-        <v>6814.51322450653</v>
+        <v>6645.08811343644</v>
       </c>
       <c r="N125" s="14" t="n">
-        <v>6814.51322450653</v>
+        <v>6645.08811343644</v>
       </c>
       <c r="O125" s="15" t="n">
-        <v>0.107849159394666</v>
+        <v>0.105238237164562</v>
       </c>
       <c r="P125" s="16" t="n">
-        <v>0.280469397924389</v>
+        <v>0.238466516493769</v>
       </c>
       <c r="Q125" s="17" t="n">
-        <v>0.113879714423447</v>
+        <v>0.11097525442494</v>
       </c>
       <c r="R125" s="18" t="n">
-        <v>0.983544624431805</v>
+        <v>0.988268239748485</v>
       </c>
       <c r="S125" s="19" t="n">
-        <v>1.09071577478699</v>
+        <v>1.04250590112479</v>
       </c>
     </row>
     <row r="126">
@@ -8955,58 +8955,58 @@
         <v>177</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>9133.82917570275</v>
+        <v>9211.04255893011</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>9133.82917570275</v>
+        <v>9211.04255893011</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>9133.82917570275</v>
+        <v>9211.04255893011</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>9133.82917570275</v>
+        <v>9211.04255893011</v>
       </c>
       <c r="F126" s="6" t="n">
-        <v>1.11139909622694</v>
+        <v>1.13089488910937</v>
       </c>
       <c r="G126" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>7341.51849671811</v>
+        <v>7159.56792008758</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>6420.53907155476</v>
+        <v>6573.63514927317</v>
       </c>
       <c r="J126" s="10" t="n">
-        <v>6652.20594905888</v>
+        <v>6761.39969078269</v>
       </c>
       <c r="K126" s="11" t="n">
-        <v>8218.31618066899</v>
+        <v>8144.91483482096</v>
       </c>
       <c r="L126" s="12" t="n">
-        <v>7341.51849671811</v>
+        <v>7159.56792008758</v>
       </c>
       <c r="M126" s="13" t="n">
-        <v>7197.53453661084</v>
+        <v>7067.3867107934</v>
       </c>
       <c r="N126" s="14" t="n">
-        <v>7197.53453661084</v>
+        <v>7067.3867107934</v>
       </c>
       <c r="O126" s="15" t="n">
-        <v>0.0546839063845197</v>
+        <v>0.061612828667796</v>
       </c>
       <c r="P126" s="16" t="n">
-        <v>0.385775435238627</v>
+        <v>0.370273983546943</v>
       </c>
       <c r="Q126" s="17" t="n">
-        <v>0.0562067017093584</v>
+        <v>0.0635504887441702</v>
       </c>
       <c r="R126" s="18" t="n">
-        <v>0.980387714044222</v>
+        <v>0.987124752453909</v>
       </c>
       <c r="S126" s="19" t="n">
-        <v>1.12101716949258</v>
+        <v>1.07511088618522</v>
       </c>
     </row>
     <row r="127">
@@ -9014,58 +9014,58 @@
         <v>178</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>6663.08011470637</v>
+        <v>6724.14325832842</v>
       </c>
       <c r="C127" s="3" t="n">
-        <v>6663.08011470637</v>
+        <v>6724.14325832842</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>6663.08011470637</v>
+        <v>6724.14325832842</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>6663.08011470637</v>
+        <v>6724.14325832842</v>
       </c>
       <c r="F127" s="6" t="n">
-        <v>0.926225857440869</v>
+        <v>0.930491959896248</v>
       </c>
       <c r="G127" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H127" s="8" t="n">
-        <v>7257.0129439313</v>
+        <v>7272.46208154932</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>6593.61022168018</v>
+        <v>6775.59539787808</v>
       </c>
       <c r="J127" s="10" t="n">
-        <v>6839.80414916011</v>
+        <v>7004.55147455499</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>7193.79626597365</v>
+        <v>7226.43886044773</v>
       </c>
       <c r="L127" s="12" t="n">
-        <v>7193.79626597365</v>
+        <v>7226.43886044773</v>
       </c>
       <c r="M127" s="13" t="n">
-        <v>7183.14038955146</v>
+        <v>7223.09387188955</v>
       </c>
       <c r="N127" s="14" t="n">
-        <v>7183.14038955146</v>
+        <v>7223.09387188955</v>
       </c>
       <c r="O127" s="15" t="n">
-        <v>-0.00200187431262255</v>
+        <v>0.0217925943749924</v>
       </c>
       <c r="P127" s="16" t="n">
-        <v>0.313809773433942</v>
+        <v>0.347439428115657</v>
       </c>
       <c r="Q127" s="17" t="n">
-        <v>-0.00199987189865736</v>
+        <v>0.0220317873448681</v>
       </c>
       <c r="R127" s="18" t="n">
-        <v>0.989820528783593</v>
+        <v>0.993211623641872</v>
       </c>
       <c r="S127" s="19" t="n">
-        <v>1.08940931417706</v>
+        <v>1.06604563108234</v>
       </c>
     </row>
     <row r="128">
@@ -9073,58 +9073,58 @@
         <v>179</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>6896.80805983389</v>
+        <v>7175.59727581782</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>6896.80805983389</v>
+        <v>7175.59727581782</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>6896.80805983389</v>
+        <v>7175.59727581782</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>6896.80805983389</v>
+        <v>7175.59727581782</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>0.984772867423462</v>
+        <v>0.985668464812691</v>
       </c>
       <c r="G128" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>6965.07257856779</v>
+        <v>7191.79622619522</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>6766.56617110362</v>
+        <v>6979.10074050611</v>
       </c>
       <c r="J128" s="10" t="n">
-        <v>7022.56510175999</v>
+        <v>7250.18247142148</v>
       </c>
       <c r="K128" s="11" t="n">
-        <v>7003.45052954043</v>
+        <v>7279.92984657515</v>
       </c>
       <c r="L128" s="12" t="n">
-        <v>7003.45052954043</v>
+        <v>7279.92984657515</v>
       </c>
       <c r="M128" s="13" t="n">
-        <v>6982.37126951723</v>
+        <v>7250.86360622431</v>
       </c>
       <c r="N128" s="14" t="n">
-        <v>6982.37126951723</v>
+        <v>7250.86360622431</v>
       </c>
       <c r="O128" s="15" t="n">
-        <v>-0.0283480850898006</v>
+        <v>0.00383720464158265</v>
       </c>
       <c r="P128" s="16" t="n">
-        <v>0.141317282607746</v>
+        <v>0.212253306835349</v>
       </c>
       <c r="Q128" s="17" t="n">
-        <v>-0.0279500481887092</v>
+        <v>0.003844576136943</v>
       </c>
       <c r="R128" s="18" t="n">
-        <v>1.00248363398289</v>
+        <v>1.00821316096443</v>
       </c>
       <c r="S128" s="19" t="n">
-        <v>1.03189285273455</v>
+        <v>1.03893952470709</v>
       </c>
     </row>
     <row r="129">
@@ -9132,92 +9132,118 @@
         <v>180</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>6578.69950141729</v>
+        <v>6831.01219133661</v>
       </c>
       <c r="C129" s="3" t="n">
-        <v>6578.69950141729</v>
+        <v>6831.01219133661</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>6578.69950141729</v>
+        <v>6831.01219133661</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>6578.69950141729</v>
+        <v>6831.01219133661</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>0.977694607542064</v>
+        <v>0.946496419524731</v>
       </c>
       <c r="G129" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H129" s="8" t="n">
-        <v>6780.85733523067</v>
+        <v>7415.79916705863</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>6939.39049381407</v>
+        <v>7183.503789505</v>
       </c>
       <c r="J129" s="10" t="n">
-        <v>7202.95521703975</v>
+        <v>7497.8349175106</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>6728.78775301443</v>
+        <v>7217.15587129923</v>
       </c>
       <c r="L129" s="12" t="n">
-        <v>6728.78775301443</v>
+        <v>7217.15587129923</v>
       </c>
       <c r="M129" s="13" t="n">
-        <v>6820.34201185643</v>
+        <v>7450.98145509224</v>
       </c>
       <c r="N129" s="14" t="n">
-        <v>6820.34201185643</v>
+        <v>7450.98145509224</v>
       </c>
       <c r="O129" s="15" t="n">
-        <v>-0.0234789635438526</v>
+        <v>0.0272251827807207</v>
       </c>
       <c r="P129" s="16" t="n">
-        <v>0.000855349040771225</v>
+        <v>0.121276547112487</v>
       </c>
       <c r="Q129" s="17" t="n">
-        <v>-0.0232054772521435</v>
+        <v>0.0275991743516097</v>
       </c>
       <c r="R129" s="18" t="n">
-        <v>1.00582296230015</v>
+        <v>1.00474423420066</v>
       </c>
       <c r="S129" s="19" t="n">
-        <v>0.98284453338319</v>
+        <v>1.03723498635555</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
         <v>181</v>
       </c>
-      <c r="B130" s="2"/>
+      <c r="B130" s="2" t="n">
+        <v>9236.94244651634</v>
+      </c>
       <c r="C130" s="3" t="n">
-        <v>7540.24692596969</v>
+        <v>9236.94244651634</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>9586.28014491874</v>
+        <v>9236.94244651634</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>5930.90571578297</v>
+        <v>9236.94244651634</v>
       </c>
       <c r="F130" s="6" t="n">
-        <v>1.1134238859576</v>
-      </c>
-      <c r="G130" s="7"/>
-      <c r="H130" s="8"/>
-      <c r="I130" s="9"/>
-      <c r="J130" s="10"/>
-      <c r="K130" s="11"/>
-      <c r="L130" s="12"/>
-      <c r="M130" s="13"/>
+        <v>1.1418174285341</v>
+      </c>
+      <c r="G130" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" s="8" t="n">
+        <v>7923.74041025814</v>
+      </c>
+      <c r="I130" s="9" t="n">
+        <v>7388.34517541375</v>
+      </c>
+      <c r="J130" s="10" t="n">
+        <v>7747.19978582656</v>
+      </c>
+      <c r="K130" s="11" t="n">
+        <v>8089.68423119536</v>
+      </c>
+      <c r="L130" s="12" t="n">
+        <v>8089.68423119536</v>
+      </c>
+      <c r="M130" s="13" t="n">
+        <v>7798.84144456332</v>
+      </c>
       <c r="N130" s="14" t="n">
-        <v>6772.12607082226</v>
-      </c>
-      <c r="O130" s="15"/>
-      <c r="P130" s="16"/>
-      <c r="Q130" s="17"/>
-      <c r="R130" s="18"/>
-      <c r="S130" s="19"/>
+        <v>7798.84144456332</v>
+      </c>
+      <c r="O130" s="15" t="n">
+        <v>0.0456294272619603</v>
+      </c>
+      <c r="P130" s="16" t="n">
+        <v>0.103497199700821</v>
+      </c>
+      <c r="Q130" s="17" t="n">
+        <v>0.0466864656109616</v>
+      </c>
+      <c r="R130" s="18" t="n">
+        <v>0.984237372853213</v>
+      </c>
+      <c r="S130" s="19" t="n">
+        <v>1.05555997444672</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
@@ -9225,16 +9251,16 @@
       </c>
       <c r="B131" s="2"/>
       <c r="C131" s="3" t="n">
-        <v>6316.22139473634</v>
+        <v>7658.98972803735</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>8869.71535004944</v>
+        <v>9882.14994851058</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>4497.85039686789</v>
+        <v>5935.96777622494</v>
       </c>
       <c r="F131" s="6" t="n">
-        <v>0.925230612440542</v>
+        <v>0.929066261033592</v>
       </c>
       <c r="G131" s="7"/>
       <c r="H131" s="8"/>
@@ -9244,7 +9270,7 @@
       <c r="L131" s="12"/>
       <c r="M131" s="13"/>
       <c r="N131" s="14" t="n">
-        <v>6826.64549768368</v>
+        <v>8243.7497186871</v>
       </c>
       <c r="O131" s="15"/>
       <c r="P131" s="16"/>
@@ -9258,16 +9284,16 @@
       </c>
       <c r="B132" s="2"/>
       <c r="C132" s="3" t="n">
-        <v>6672.53796730296</v>
+        <v>8128.35509063935</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>10113.0591770683</v>
+        <v>11552.520436258</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>4402.50196756056</v>
+        <v>5719.11184611792</v>
       </c>
       <c r="F132" s="6" t="n">
-        <v>0.982287280215694</v>
+        <v>0.981023807567379</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="8"/>
@@ -9277,7 +9303,7 @@
       <c r="L132" s="12"/>
       <c r="M132" s="13"/>
       <c r="N132" s="14" t="n">
-        <v>6792.85795682683</v>
+        <v>8285.58392562871</v>
       </c>
       <c r="O132" s="15"/>
       <c r="P132" s="16"/>
@@ -9291,16 +9317,16 @@
       </c>
       <c r="B133" s="2"/>
       <c r="C133" s="3" t="n">
-        <v>6873.91604554784</v>
+        <v>8307.56626156905</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>11110.4927414235</v>
+        <v>12730.9782207024</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>4252.80164443781</v>
+        <v>5421.08045382803</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>0.978727261095369</v>
+        <v>0.944907245427715</v>
       </c>
       <c r="G133" s="7"/>
       <c r="H133" s="8"/>
@@ -9310,7 +9336,7 @@
       <c r="L133" s="12"/>
       <c r="M133" s="13"/>
       <c r="N133" s="14" t="n">
-        <v>7023.32132636697</v>
+        <v>8791.93836407573</v>
       </c>
       <c r="O133" s="15"/>
       <c r="P133" s="16"/>
@@ -9323,10 +9349,18 @@
         <v>185</v>
       </c>
       <c r="B134" s="2"/>
-      <c r="C134" s="3"/>
-      <c r="D134" s="4"/>
-      <c r="E134" s="5"/>
-      <c r="F134" s="6"/>
+      <c r="C134" s="3" t="n">
+        <v>9725.02491967474</v>
+      </c>
+      <c r="D134" s="4" t="n">
+        <v>15886.5362667497</v>
+      </c>
+      <c r="E134" s="5" t="n">
+        <v>5953.22404457926</v>
+      </c>
+      <c r="F134" s="6" t="n">
+        <v>1.1482396978931</v>
+      </c>
       <c r="G134" s="7"/>
       <c r="H134" s="8"/>
       <c r="I134" s="9"/>
@@ -9334,7 +9368,9 @@
       <c r="K134" s="11"/>
       <c r="L134" s="12"/>
       <c r="M134" s="13"/>
-      <c r="N134" s="14"/>
+      <c r="N134" s="14" t="n">
+        <v>8469.50766248471</v>
+      </c>
       <c r="O134" s="15"/>
       <c r="P134" s="16"/>
       <c r="Q134" s="17"/>
@@ -9832,7 +9868,7 @@
         <v>222</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>-0.0776990570851476</v>
+        <v>-0.0800230812481268</v>
       </c>
     </row>
     <row r="6">
@@ -9840,7 +9876,7 @@
         <v>223</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>0.0439167477028377</v>
+        <v>0.0268663599897096</v>
       </c>
     </row>
     <row r="7">
@@ -9848,7 +9884,7 @@
         <v>224</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>0.22932987864076</v>
+        <v>0.205285041368578</v>
       </c>
     </row>
     <row r="8">
@@ -9856,7 +9892,7 @@
         <v>225</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.436736073625052</v>
+        <v>0.414727493300084</v>
       </c>
     </row>
     <row r="9">
@@ -9864,7 +9900,7 @@
         <v>226</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.577296261064304</v>
+        <v>0.566138820054058</v>
       </c>
     </row>
     <row r="10">
@@ -9872,7 +9908,7 @@
         <v>227</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.560510095456793</v>
+        <v>0.562999802565544</v>
       </c>
     </row>
     <row r="11">
@@ -9880,7 +9916,7 @@
         <v>228</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.406320642893262</v>
+        <v>0.411683231664236</v>
       </c>
     </row>
     <row r="12">
@@ -9888,7 +9924,7 @@
         <v>229</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>0.218546449441727</v>
+        <v>0.226080937367733</v>
       </c>
     </row>
     <row r="13">
@@ -9896,7 +9932,7 @@
         <v>230</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>0.0893269871463753</v>
+        <v>0.0997382216013041</v>
       </c>
     </row>
     <row r="14">
